--- a/public/data.xlsx
+++ b/public/data.xlsx
@@ -16,7 +16,7 @@
     <sheet name="SORT_ORDER" sheetId="21" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DS!$A$1:$J$987</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DS!$A$1:$J$986</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2582" uniqueCount="1232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2577" uniqueCount="1233">
   <si>
     <t>id</t>
   </si>
@@ -3729,6 +3729,9 @@
   </si>
   <si>
     <t>Nguyễn Phước Bảo Đức</t>
+  </si>
+  <si>
+    <t>Cậu bé ốm yếu hihi</t>
   </si>
 </sst>
 </file>
@@ -4060,8 +4063,8 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:K987"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:K986"/>
+  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="24.5" bestFit="1" customWidth="1"/>
@@ -4074,7 +4077,7 @@
     <col min="9" max="9" width="39.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -4106,7 +4109,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <f>IF(B2="", "", SUBTOTAL(3, $B$2:B2) * 1)</f>
         <v>1</v>
@@ -4139,7 +4142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <f>IF(B3="", "", SUBTOTAL(3, $B$2:B3) * 1)</f>
         <v>2</v>
@@ -4170,7 +4173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <f>IF(B4="", "", SUBTOTAL(3, $B$2:B4) * 1)</f>
         <v>3</v>
@@ -4201,7 +4204,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <f>IF(B5="", "", SUBTOTAL(3, $B$2:B5) * 1)</f>
         <v>4</v>
@@ -4232,7 +4235,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <f>IF(B6="", "", SUBTOTAL(3, $B$2:B6) * 1)</f>
         <v>5</v>
@@ -4265,7 +4268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <f>IF(B7="", "", SUBTOTAL(3, $B$2:B7) * 1)</f>
         <v>6</v>
@@ -4296,7 +4299,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <f>IF(B8="", "", SUBTOTAL(3, $B$2:B8) * 1)</f>
         <v>7</v>
@@ -4329,7 +4332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f>IF(B9="", "", SUBTOTAL(3, $B$2:B9) * 1)</f>
         <v>8</v>
@@ -4362,7 +4365,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <f>IF(B10="", "", SUBTOTAL(3, $B$2:B10) * 1)</f>
         <v>9</v>
@@ -4395,7 +4398,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f>IF(B11="", "", SUBTOTAL(3, $B$2:B11) * 1)</f>
         <v>10</v>
@@ -4426,7 +4429,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <f>IF(B12="", "", SUBTOTAL(3, $B$2:B12) * 1)</f>
         <v>11</v>
@@ -4457,7 +4460,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <f>IF(B13="", "", SUBTOTAL(3, $B$2:B13) * 1)</f>
         <v>12</v>
@@ -4488,7 +4491,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <f>IF(B14="", "", SUBTOTAL(3, $B$2:B14) * 1)</f>
         <v>13</v>
@@ -4521,7 +4524,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <f>IF(B15="", "", SUBTOTAL(3, $B$2:B15) * 1)</f>
         <v>14</v>
@@ -4554,7 +4557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <f>IF(B16="", "", SUBTOTAL(3, $B$2:B16) * 1)</f>
         <v>15</v>
@@ -4587,7 +4590,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="17" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <f>IF(B17="", "", SUBTOTAL(3, $B$2:B17) * 1)</f>
         <v>16</v>
@@ -4618,7 +4621,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="18" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <f>IF(B18="", "", SUBTOTAL(3, $B$2:B18) * 1)</f>
         <v>17</v>
@@ -4649,7 +4652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <f>IF(B19="", "", SUBTOTAL(3, $B$2:B19) * 1)</f>
         <v>18</v>
@@ -4682,7 +4685,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <f>IF(B20="", "", SUBTOTAL(3, $B$2:B20) * 1)</f>
         <v>19</v>
@@ -4713,7 +4716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <f>IF(B21="", "", SUBTOTAL(3, $B$2:B21) * 1)</f>
         <v>20</v>
@@ -4744,7 +4747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <f>IF(B22="", "", SUBTOTAL(3, $B$2:B22) * 1)</f>
         <v>21</v>
@@ -4775,7 +4778,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="23" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <f>IF(B23="", "", SUBTOTAL(3, $B$2:B23) * 1)</f>
         <v>22</v>
@@ -4808,7 +4811,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <f>IF(B24="", "", SUBTOTAL(3, $B$2:B24) * 1)</f>
         <v>23</v>
@@ -4839,7 +4842,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <f>IF(B25="", "", SUBTOTAL(3, $B$2:B25) * 1)</f>
         <v>24</v>
@@ -4872,7 +4875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <f>IF(B26="", "", SUBTOTAL(3, $B$2:B26) * 1)</f>
         <v>25</v>
@@ -4905,7 +4908,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <f>IF(B27="", "", SUBTOTAL(3, $B$2:B27) * 1)</f>
         <v>26</v>
@@ -4938,7 +4941,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <f>IF(B28="", "", SUBTOTAL(3, $B$2:B28) * 1)</f>
         <v>27</v>
@@ -4969,7 +4972,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <f>IF(B29="", "", SUBTOTAL(3, $B$2:B29) * 1)</f>
         <v>28</v>
@@ -5000,7 +5003,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <f>IF(B30="", "", SUBTOTAL(3, $B$2:B30) * 1)</f>
         <v>29</v>
@@ -5031,7 +5034,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <f>IF(B31="", "", SUBTOTAL(3, $B$2:B31) * 1)</f>
         <v>30</v>
@@ -5064,7 +5067,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <f>IF(B32="", "", SUBTOTAL(3, $B$2:B32) * 1)</f>
         <v>31</v>
@@ -5095,7 +5098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <f>IF(B33="", "", SUBTOTAL(3, $B$2:B33) * 1)</f>
         <v>32</v>
@@ -5126,7 +5129,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <f>IF(B34="", "", SUBTOTAL(3, $B$2:B34) * 1)</f>
         <v>33</v>
@@ -5157,7 +5160,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <f>IF(B35="", "", SUBTOTAL(3, $B$2:B35) * 1)</f>
         <v>34</v>
@@ -5190,7 +5193,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <f>IF(B36="", "", SUBTOTAL(3, $B$2:B36) * 1)</f>
         <v>35</v>
@@ -5221,7 +5224,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <f>IF(B37="", "", SUBTOTAL(3, $B$2:B37) * 1)</f>
         <v>36</v>
@@ -5252,7 +5255,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <f>IF(B38="", "", SUBTOTAL(3, $B$2:B38) * 1)</f>
         <v>37</v>
@@ -5283,7 +5286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <f>IF(B39="", "", SUBTOTAL(3, $B$2:B39) * 1)</f>
         <v>38</v>
@@ -5316,7 +5319,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <f>IF(B40="", "", SUBTOTAL(3, $B$2:B40) * 1)</f>
         <v>39</v>
@@ -5349,7 +5352,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <f>IF(B41="", "", SUBTOTAL(3, $B$2:B41) * 1)</f>
         <v>40</v>
@@ -5380,7 +5383,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="42" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <f>IF(B42="", "", SUBTOTAL(3, $B$2:B42) * 1)</f>
         <v>41</v>
@@ -5411,7 +5414,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <f>IF(B43="", "", SUBTOTAL(3, $B$2:B43) * 1)</f>
         <v>42</v>
@@ -5442,7 +5445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <f>IF(B44="", "", SUBTOTAL(3, $B$2:B44) * 1)</f>
         <v>43</v>
@@ -5475,7 +5478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <f>IF(B45="", "", SUBTOTAL(3, $B$2:B45) * 1)</f>
         <v>44</v>
@@ -5506,7 +5509,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <f>IF(B46="", "", SUBTOTAL(3, $B$2:B46) * 1)</f>
         <v>45</v>
@@ -5537,7 +5540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <f>IF(B47="", "", SUBTOTAL(3, $B$2:B47) * 1)</f>
         <v>46</v>
@@ -5568,7 +5571,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <f>IF(B48="", "", SUBTOTAL(3, $B$2:B48) * 1)</f>
         <v>47</v>
@@ -5601,7 +5604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <f>IF(B49="", "", SUBTOTAL(3, $B$2:B49) * 1)</f>
         <v>48</v>
@@ -5634,7 +5637,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <f>IF(B50="", "", SUBTOTAL(3, $B$2:B50) * 1)</f>
         <v>49</v>
@@ -5667,7 +5670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <f>IF(B51="", "", SUBTOTAL(3, $B$2:B51) * 1)</f>
         <v>50</v>
@@ -5700,7 +5703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <f>IF(B52="", "", SUBTOTAL(3, $B$2:B52) * 1)</f>
         <v>51</v>
@@ -5731,7 +5734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <f>IF(B53="", "", SUBTOTAL(3, $B$2:B53) * 1)</f>
         <v>52</v>
@@ -5764,7 +5767,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <f>IF(B54="", "", SUBTOTAL(3, $B$2:B54) * 1)</f>
         <v>53</v>
@@ -5797,7 +5800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <f>IF(B55="", "", SUBTOTAL(3, $B$2:B55) * 1)</f>
         <v>54</v>
@@ -5828,7 +5831,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <f>IF(B56="", "", SUBTOTAL(3, $B$2:B56) * 1)</f>
         <v>55</v>
@@ -5859,7 +5862,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <f>IF(B57="", "", SUBTOTAL(3, $B$2:B57) * 1)</f>
         <v>56</v>
@@ -5892,7 +5895,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <f>IF(B58="", "", SUBTOTAL(3, $B$2:B58) * 1)</f>
         <v>57</v>
@@ -5925,7 +5928,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <f>IF(B59="", "", SUBTOTAL(3, $B$2:B59) * 1)</f>
         <v>58</v>
@@ -5958,7 +5961,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <f>IF(B60="", "", SUBTOTAL(3, $B$2:B60) * 1)</f>
         <v>59</v>
@@ -5991,7 +5994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <f>IF(B61="", "", SUBTOTAL(3, $B$2:B61) * 1)</f>
         <v>60</v>
@@ -6024,7 +6027,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <f>IF(B62="", "", SUBTOTAL(3, $B$2:B62) * 1)</f>
         <v>61</v>
@@ -6057,7 +6060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <f>IF(B63="", "", SUBTOTAL(3, $B$2:B63) * 1)</f>
         <v>62</v>
@@ -6088,7 +6091,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <f>IF(B64="", "", SUBTOTAL(3, $B$2:B64) * 1)</f>
         <v>63</v>
@@ -6119,7 +6122,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <f>IF(B65="", "", SUBTOTAL(3, $B$2:B65) * 1)</f>
         <v>64</v>
@@ -6152,7 +6155,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <f>IF(B66="", "", SUBTOTAL(3, $B$2:B66) * 1)</f>
         <v>65</v>
@@ -6183,7 +6186,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <f>IF(B67="", "", SUBTOTAL(3, $B$2:B67) * 1)</f>
         <v>66</v>
@@ -6216,7 +6219,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <f>IF(B68="", "", SUBTOTAL(3, $B$2:B68) * 1)</f>
         <v>67</v>
@@ -6249,7 +6252,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <f>IF(B69="", "", SUBTOTAL(3, $B$2:B69) * 1)</f>
         <v>68</v>
@@ -6280,7 +6283,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="15.75" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <f>IF(B70="", "", SUBTOTAL(3, $B$2:B70) * 1)</f>
         <v>69</v>
@@ -6301,8 +6304,8 @@
       <c r="G70" s="3">
         <v>2024</v>
       </c>
-      <c r="H70" s="3" t="s">
-        <v>23</v>
+      <c r="H70" s="2" t="s">
+        <v>1232</v>
       </c>
       <c r="I70" s="3" t="s">
         <v>1008</v>
@@ -6311,7 +6314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <f>IF(B71="", "", SUBTOTAL(3, $B$2:B71) * 1)</f>
         <v>70</v>
@@ -6342,7 +6345,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <f>IF(B72="", "", SUBTOTAL(3, $B$2:B72) * 1)</f>
         <v>71</v>
@@ -6373,7 +6376,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <f>IF(B73="", "", SUBTOTAL(3, $B$2:B73) * 1)</f>
         <v>72</v>
@@ -6404,7 +6407,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <f>IF(B74="", "", SUBTOTAL(3, $B$2:B74) * 1)</f>
         <v>73</v>
@@ -6437,7 +6440,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <f>IF(B75="", "", SUBTOTAL(3, $B$2:B75) * 1)</f>
         <v>74</v>
@@ -6468,7 +6471,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <f>IF(B76="", "", SUBTOTAL(3, $B$2:B76) * 1)</f>
         <v>75</v>
@@ -6501,7 +6504,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <f>IF(B77="", "", SUBTOTAL(3, $B$2:B77) * 1)</f>
         <v>76</v>
@@ -6534,7 +6537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <f>IF(B78="", "", SUBTOTAL(3, $B$2:B78) * 1)</f>
         <v>77</v>
@@ -6565,7 +6568,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <f>IF(B79="", "", SUBTOTAL(3, $B$2:B79) * 1)</f>
         <v>78</v>
@@ -6598,7 +6601,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <f>IF(B80="", "", SUBTOTAL(3, $B$2:B80) * 1)</f>
         <v>79</v>
@@ -6629,7 +6632,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <f>IF(B81="", "", SUBTOTAL(3, $B$2:B81) * 1)</f>
         <v>80</v>
@@ -6660,7 +6663,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <f>IF(B82="", "", SUBTOTAL(3, $B$2:B82) * 1)</f>
         <v>81</v>
@@ -6691,7 +6694,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <f>IF(B83="", "", SUBTOTAL(3, $B$2:B83) * 1)</f>
         <v>82</v>
@@ -6724,7 +6727,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <f>IF(B84="", "", SUBTOTAL(3, $B$2:B84) * 1)</f>
         <v>83</v>
@@ -6755,7 +6758,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <f>IF(B85="", "", SUBTOTAL(3, $B$2:B85) * 1)</f>
         <v>84</v>
@@ -6786,7 +6789,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <f>IF(B86="", "", SUBTOTAL(3, $B$2:B86) * 1)</f>
         <v>85</v>
@@ -6815,7 +6818,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <f>IF(B87="", "", SUBTOTAL(3, $B$2:B87) * 1)</f>
         <v>86</v>
@@ -6846,7 +6849,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <f>IF(B88="", "", SUBTOTAL(3, $B$2:B88) * 1)</f>
         <v>87</v>
@@ -6879,7 +6882,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <f>IF(B89="", "", SUBTOTAL(3, $B$2:B89) * 1)</f>
         <v>88</v>
@@ -6910,7 +6913,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <f>IF(B90="", "", SUBTOTAL(3, $B$2:B90) * 1)</f>
         <v>89</v>
@@ -6943,7 +6946,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <f>IF(B91="", "", SUBTOTAL(3, $B$2:B91) * 1)</f>
         <v>90</v>
@@ -6972,7 +6975,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <f>IF(B92="", "", SUBTOTAL(3, $B$2:B92) * 1)</f>
         <v>91</v>
@@ -7003,7 +7006,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <f>IF(B93="", "", SUBTOTAL(3, $B$2:B93) * 1)</f>
         <v>92</v>
@@ -7036,7 +7039,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <f>IF(B94="", "", SUBTOTAL(3, $B$2:B94) * 1)</f>
         <v>93</v>
@@ -7067,7 +7070,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <f>IF(B95="", "", SUBTOTAL(3, $B$2:B95) * 1)</f>
         <v>94</v>
@@ -7100,7 +7103,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <f>IF(B96="", "", SUBTOTAL(3, $B$2:B96) * 1)</f>
         <v>95</v>
@@ -7131,7 +7134,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <f>IF(B97="", "", SUBTOTAL(3, $B$2:B97) * 1)</f>
         <v>96</v>
@@ -7164,7 +7167,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <f>IF(B98="", "", SUBTOTAL(3, $B$2:B98) * 1)</f>
         <v>97</v>
@@ -7195,7 +7198,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <f>IF(B99="", "", SUBTOTAL(3, $B$2:B99) * 1)</f>
         <v>98</v>
@@ -7228,7 +7231,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <f>IF(B100="", "", SUBTOTAL(3, $B$2:B100) * 1)</f>
         <v>99</v>
@@ -7261,7 +7264,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <f>IF(B101="", "", SUBTOTAL(3, $B$2:B101) * 1)</f>
         <v>100</v>
@@ -7294,7 +7297,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <f>IF(B102="", "", SUBTOTAL(3, $B$2:B102) * 1)</f>
         <v>101</v>
@@ -7325,7 +7328,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <f>IF(B103="", "", SUBTOTAL(3, $B$2:B103) * 1)</f>
         <v>102</v>
@@ -7356,7 +7359,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <f>IF(B104="", "", SUBTOTAL(3, $B$2:B104) * 1)</f>
         <v>103</v>
@@ -7389,7 +7392,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <f>IF(B105="", "", SUBTOTAL(3, $B$2:B105) * 1)</f>
         <v>104</v>
@@ -7422,7 +7425,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <f>IF(B106="", "", SUBTOTAL(3, $B$2:B106) * 1)</f>
         <v>105</v>
@@ -7455,7 +7458,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <f>IF(B107="", "", SUBTOTAL(3, $B$2:B107) * 1)</f>
         <v>106</v>
@@ -7488,7 +7491,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <f>IF(B108="", "", SUBTOTAL(3, $B$2:B108) * 1)</f>
         <v>107</v>
@@ -7519,7 +7522,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <f>IF(B109="", "", SUBTOTAL(3, $B$2:B109) * 1)</f>
         <v>108</v>
@@ -7552,7 +7555,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <f>IF(B110="", "", SUBTOTAL(3, $B$2:B110) * 1)</f>
         <v>109</v>
@@ -7583,7 +7586,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <f>IF(B111="", "", SUBTOTAL(3, $B$2:B111) * 1)</f>
         <v>110</v>
@@ -7614,7 +7617,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <f>IF(B112="", "", SUBTOTAL(3, $B$2:B112) * 1)</f>
         <v>111</v>
@@ -7647,7 +7650,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <f>IF(B113="", "", SUBTOTAL(3, $B$2:B113) * 1)</f>
         <v>112</v>
@@ -7678,7 +7681,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <f>IF(B114="", "", SUBTOTAL(3, $B$2:B114) * 1)</f>
         <v>113</v>
@@ -7709,7 +7712,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <f>IF(B115="", "", SUBTOTAL(3, $B$2:B115) * 1)</f>
         <v>114</v>
@@ -7740,7 +7743,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <f>IF(B116="", "", SUBTOTAL(3, $B$2:B116) * 1)</f>
         <v>115</v>
@@ -7771,7 +7774,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <f>IF(B117="", "", SUBTOTAL(3, $B$2:B117) * 1)</f>
         <v>116</v>
@@ -7800,7 +7803,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <f>IF(B118="", "", SUBTOTAL(3, $B$2:B118) * 1)</f>
         <v>117</v>
@@ -7829,7 +7832,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <f>IF(B119="", "", SUBTOTAL(3, $B$2:B119) * 1)</f>
         <v>118</v>
@@ -7860,7 +7863,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <f>IF(B120="", "", SUBTOTAL(3, $B$2:B120) * 1)</f>
         <v>119</v>
@@ -7889,7 +7892,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="121" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <f>IF(B121="", "", SUBTOTAL(3, $B$2:B121) * 1)</f>
         <v>120</v>
@@ -7920,7 +7923,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <f>IF(B122="", "", SUBTOTAL(3, $B$2:B122) * 1)</f>
         <v>121</v>
@@ -7949,7 +7952,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <f>IF(B123="", "", SUBTOTAL(3, $B$2:B123) * 1)</f>
         <v>122</v>
@@ -7978,7 +7981,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="124" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <f>IF(B124="", "", SUBTOTAL(3, $B$2:B124) * 1)</f>
         <v>123</v>
@@ -8011,7 +8014,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <f>IF(B125="", "", SUBTOTAL(3, $B$2:B125) * 1)</f>
         <v>124</v>
@@ -8044,7 +8047,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="126" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <f>IF(B126="", "", SUBTOTAL(3, $B$2:B126) * 1)</f>
         <v>125</v>
@@ -8075,7 +8078,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <f>IF(B127="", "", SUBTOTAL(3, $B$2:B127) * 1)</f>
         <v>126</v>
@@ -8106,7 +8109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <f>IF(B128="", "", SUBTOTAL(3, $B$2:B128) * 1)</f>
         <v>127</v>
@@ -8137,7 +8140,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <f>IF(B129="", "", SUBTOTAL(3, $B$2:B129) * 1)</f>
         <v>128</v>
@@ -8170,7 +8173,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <f>IF(B130="", "", SUBTOTAL(3, $B$2:B130) * 1)</f>
         <v>129</v>
@@ -8201,7 +8204,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <f>IF(B131="", "", SUBTOTAL(3, $B$2:B131) * 1)</f>
         <v>130</v>
@@ -8230,7 +8233,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <f>IF(B132="", "", SUBTOTAL(3, $B$2:B132) * 1)</f>
         <v>131</v>
@@ -8263,7 +8266,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <f>IF(B133="", "", SUBTOTAL(3, $B$2:B133) * 1)</f>
         <v>132</v>
@@ -8296,7 +8299,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <f>IF(B134="", "", SUBTOTAL(3, $B$2:B134) * 1)</f>
         <v>133</v>
@@ -8325,7 +8328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <f>IF(B135="", "", SUBTOTAL(3, $B$2:B135) * 1)</f>
         <v>134</v>
@@ -8358,7 +8361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <f>IF(B136="", "", SUBTOTAL(3, $B$2:B136) * 1)</f>
         <v>135</v>
@@ -8387,7 +8390,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <f>IF(B137="", "", SUBTOTAL(3, $B$2:B137) * 1)</f>
         <v>136</v>
@@ -8418,7 +8421,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <f>IF(B138="", "", SUBTOTAL(3, $B$2:B138) * 1)</f>
         <v>137</v>
@@ -8449,7 +8452,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <f>IF(B139="", "", SUBTOTAL(3, $B$2:B139) * 1)</f>
         <v>138</v>
@@ -8482,7 +8485,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <f>IF(B140="", "", SUBTOTAL(3, $B$2:B140) * 1)</f>
         <v>139</v>
@@ -8513,7 +8516,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <f>IF(B141="", "", SUBTOTAL(3, $B$2:B141) * 1)</f>
         <v>140</v>
@@ -8542,7 +8545,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="142" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <f>IF(B142="", "", SUBTOTAL(3, $B$2:B142) * 1)</f>
         <v>141</v>
@@ -8575,7 +8578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="143" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <f>IF(B143="", "", SUBTOTAL(3, $B$2:B143) * 1)</f>
         <v>142</v>
@@ -8608,7 +8611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="144" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <f>IF(B144="", "", SUBTOTAL(3, $B$2:B144) * 1)</f>
         <v>143</v>
@@ -8639,7 +8642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="145" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <f>IF(B145="", "", SUBTOTAL(3, $B$2:B145) * 1)</f>
         <v>144</v>
@@ -8668,7 +8671,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="146" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <f>IF(B146="", "", SUBTOTAL(3, $B$2:B146) * 1)</f>
         <v>145</v>
@@ -8697,7 +8700,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="147" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <f>IF(B147="", "", SUBTOTAL(3, $B$2:B147) * 1)</f>
         <v>146</v>
@@ -8726,7 +8729,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="148" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <f>IF(B148="", "", SUBTOTAL(3, $B$2:B148) * 1)</f>
         <v>147</v>
@@ -8755,7 +8758,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="149" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <f>IF(B149="", "", SUBTOTAL(3, $B$2:B149) * 1)</f>
         <v>148</v>
@@ -8786,7 +8789,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <f>IF(B150="", "", SUBTOTAL(3, $B$2:B150) * 1)</f>
         <v>149</v>
@@ -8819,7 +8822,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="151" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <f>IF(B151="", "", SUBTOTAL(3, $B$2:B151) * 1)</f>
         <v>150</v>
@@ -8850,7 +8853,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="152" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <f>IF(B152="", "", SUBTOTAL(3, $B$2:B152) * 1)</f>
         <v>151</v>
@@ -8883,7 +8886,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="153" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <f>IF(B153="", "", SUBTOTAL(3, $B$2:B153) * 1)</f>
         <v>152</v>
@@ -8914,7 +8917,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="154" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <f>IF(B154="", "", SUBTOTAL(3, $B$2:B154) * 1)</f>
         <v>153</v>
@@ -8947,7 +8950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="155" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <f>IF(B155="", "", SUBTOTAL(3, $B$2:B155) * 1)</f>
         <v>154</v>
@@ -8978,7 +8981,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <f>IF(B156="", "", SUBTOTAL(3, $B$2:B156) * 1)</f>
         <v>155</v>
@@ -9009,7 +9012,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="157" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <f>IF(B157="", "", SUBTOTAL(3, $B$2:B157) * 1)</f>
         <v>156</v>
@@ -9038,7 +9041,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="158" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <f>IF(B158="", "", SUBTOTAL(3, $B$2:B158) * 1)</f>
         <v>157</v>
@@ -9071,7 +9074,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="159" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <f>IF(B159="", "", SUBTOTAL(3, $B$2:B159) * 1)</f>
         <v>158</v>
@@ -9100,7 +9103,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="160" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <f>IF(B160="", "", SUBTOTAL(3, $B$2:B160) * 1)</f>
         <v>159</v>
@@ -9129,7 +9132,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="161" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <f>IF(B161="", "", SUBTOTAL(3, $B$2:B161) * 1)</f>
         <v>160</v>
@@ -9158,7 +9161,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="162" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <f>IF(B162="", "", SUBTOTAL(3, $B$2:B162) * 1)</f>
         <v>161</v>
@@ -9187,7 +9190,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="163" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <f>IF(B163="", "", SUBTOTAL(3, $B$2:B163) * 1)</f>
         <v>162</v>
@@ -9220,7 +9223,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="164" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <f>IF(B164="", "", SUBTOTAL(3, $B$2:B164) * 1)</f>
         <v>163</v>
@@ -9251,7 +9254,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="165" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <f>IF(B165="", "", SUBTOTAL(3, $B$2:B165) * 1)</f>
         <v>164</v>
@@ -9284,7 +9287,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="166" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <f>IF(B166="", "", SUBTOTAL(3, $B$2:B166) * 1)</f>
         <v>165</v>
@@ -9315,7 +9318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="167" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <f>IF(B167="", "", SUBTOTAL(3, $B$2:B167) * 1)</f>
         <v>166</v>
@@ -9348,7 +9351,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="168" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <f>IF(B168="", "", SUBTOTAL(3, $B$2:B168) * 1)</f>
         <v>167</v>
@@ -9377,7 +9380,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="169" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <f>IF(B169="", "", SUBTOTAL(3, $B$2:B169) * 1)</f>
         <v>168</v>
@@ -9408,7 +9411,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="170" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <f>IF(B170="", "", SUBTOTAL(3, $B$2:B170) * 1)</f>
         <v>169</v>
@@ -9439,7 +9442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="171" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <f>IF(B171="", "", SUBTOTAL(3, $B$2:B171) * 1)</f>
         <v>170</v>
@@ -9470,7 +9473,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="172" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <f>IF(B172="", "", SUBTOTAL(3, $B$2:B172) * 1)</f>
         <v>171</v>
@@ -9501,7 +9504,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="173" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <f>IF(B173="", "", SUBTOTAL(3, $B$2:B173) * 1)</f>
         <v>172</v>
@@ -9530,7 +9533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="174" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <f>IF(B174="", "", SUBTOTAL(3, $B$2:B174) * 1)</f>
         <v>173</v>
@@ -9559,7 +9562,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="175" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <f>IF(B175="", "", SUBTOTAL(3, $B$2:B175) * 1)</f>
         <v>174</v>
@@ -9588,7 +9591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="176" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <f>IF(B176="", "", SUBTOTAL(3, $B$2:B176) * 1)</f>
         <v>175</v>
@@ -9619,7 +9622,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="177" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <f>IF(B177="", "", SUBTOTAL(3, $B$2:B177) * 1)</f>
         <v>176</v>
@@ -9650,7 +9653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="178" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <f>IF(B178="", "", SUBTOTAL(3, $B$2:B178) * 1)</f>
         <v>177</v>
@@ -9681,7 +9684,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="179" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <f>IF(B179="", "", SUBTOTAL(3, $B$2:B179) * 1)</f>
         <v>178</v>
@@ -9712,7 +9715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="180" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <f>IF(B180="", "", SUBTOTAL(3, $B$2:B180) * 1)</f>
         <v>179</v>
@@ -9743,7 +9746,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="181" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <f>IF(B181="", "", SUBTOTAL(3, $B$2:B181) * 1)</f>
         <v>180</v>
@@ -9774,7 +9777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="182" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <f>IF(B182="", "", SUBTOTAL(3, $B$2:B182) * 1)</f>
         <v>181</v>
@@ -9805,7 +9808,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="183" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <f>IF(B183="", "", SUBTOTAL(3, $B$2:B183) * 1)</f>
         <v>182</v>
@@ -9838,7 +9841,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="184" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <f>IF(B184="", "", SUBTOTAL(3, $B$2:B184) * 1)</f>
         <v>183</v>
@@ -9869,7 +9872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="185" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <f>IF(B185="", "", SUBTOTAL(3, $B$2:B185) * 1)</f>
         <v>184</v>
@@ -9900,7 +9903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="186" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <f>IF(B186="", "", SUBTOTAL(3, $B$2:B186) * 1)</f>
         <v>185</v>
@@ -9929,7 +9932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="187" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <f>IF(B187="", "", SUBTOTAL(3, $B$2:B187) * 1)</f>
         <v>186</v>
@@ -9958,7 +9961,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="188" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <f>IF(B188="", "", SUBTOTAL(3, $B$2:B188) * 1)</f>
         <v>187</v>
@@ -9989,7 +9992,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="189" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <f>IF(B189="", "", SUBTOTAL(3, $B$2:B189) * 1)</f>
         <v>188</v>
@@ -10022,7 +10025,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="190" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <f>IF(B190="", "", SUBTOTAL(3, $B$2:B190) * 1)</f>
         <v>189</v>
@@ -10055,7 +10058,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="191" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <f>IF(B191="", "", SUBTOTAL(3, $B$2:B191) * 1)</f>
         <v>190</v>
@@ -10086,7 +10089,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="192" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <f>IF(B192="", "", SUBTOTAL(3, $B$2:B192) * 1)</f>
         <v>191</v>
@@ -10117,7 +10120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="193" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <f>IF(B193="", "", SUBTOTAL(3, $B$2:B193) * 1)</f>
         <v>192</v>
@@ -10146,7 +10149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="194" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="194" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <f>IF(B194="", "", SUBTOTAL(3, $B$2:B194) * 1)</f>
         <v>193</v>
@@ -10177,7 +10180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="195" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="195" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <f>IF(B195="", "", SUBTOTAL(3, $B$2:B195) * 1)</f>
         <v>194</v>
@@ -10210,7 +10213,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="196" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="196" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <f>IF(B196="", "", SUBTOTAL(3, $B$2:B196) * 1)</f>
         <v>195</v>
@@ -10241,7 +10244,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="197" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="197" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <f>IF(B197="", "", SUBTOTAL(3, $B$2:B197) * 1)</f>
         <v>196</v>
@@ -10274,7 +10277,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="198" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="198" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <f>IF(B198="", "", SUBTOTAL(3, $B$2:B198) * 1)</f>
         <v>197</v>
@@ -10305,7 +10308,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="199" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="199" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <f>IF(B199="", "", SUBTOTAL(3, $B$2:B199) * 1)</f>
         <v>198</v>
@@ -10338,7 +10341,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="200" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="200" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <f>IF(B200="", "", SUBTOTAL(3, $B$2:B200) * 1)</f>
         <v>199</v>
@@ -10369,7 +10372,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="201" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="201" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <f>IF(B201="", "", SUBTOTAL(3, $B$2:B201) * 1)</f>
         <v>200</v>
@@ -10400,7 +10403,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="202" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="202" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <f>IF(B202="", "", SUBTOTAL(3, $B$2:B202) * 1)</f>
         <v>201</v>
@@ -10429,7 +10432,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="203" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="203" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <f>IF(B203="", "", SUBTOTAL(3, $B$2:B203) * 1)</f>
         <v>202</v>
@@ -10460,7 +10463,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="204" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="204" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <f>IF(B204="", "", SUBTOTAL(3, $B$2:B204) * 1)</f>
         <v>203</v>
@@ -10493,7 +10496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="205" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <f>IF(B205="", "", SUBTOTAL(3, $B$2:B205) * 1)</f>
         <v>204</v>
@@ -10524,7 +10527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="206" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="206" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <f>IF(B206="", "", SUBTOTAL(3, $B$2:B206) * 1)</f>
         <v>205</v>
@@ -10557,7 +10560,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="207" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="207" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <f>IF(B207="", "", SUBTOTAL(3, $B$2:B207) * 1)</f>
         <v>206</v>
@@ -10588,7 +10591,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="208" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="208" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <f>IF(B208="", "", SUBTOTAL(3, $B$2:B208) * 1)</f>
         <v>207</v>
@@ -10619,7 +10622,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="209" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="209" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <f>IF(B209="", "", SUBTOTAL(3, $B$2:B209) * 1)</f>
         <v>208</v>
@@ -10650,7 +10653,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="210" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="210" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <f>IF(B210="", "", SUBTOTAL(3, $B$2:B210) * 1)</f>
         <v>209</v>
@@ -10679,7 +10682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="211" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="211" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <f>IF(B211="", "", SUBTOTAL(3, $B$2:B211) * 1)</f>
         <v>210</v>
@@ -10710,7 +10713,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="212" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="212" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <f>IF(B212="", "", SUBTOTAL(3, $B$2:B212) * 1)</f>
         <v>211</v>
@@ -10741,7 +10744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="213" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="213" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <f>IF(B213="", "", SUBTOTAL(3, $B$2:B213) * 1)</f>
         <v>212</v>
@@ -10772,7 +10775,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="214" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="214" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <f>IF(B214="", "", SUBTOTAL(3, $B$2:B214) * 1)</f>
         <v>213</v>
@@ -10805,7 +10808,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="215" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="215" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <f>IF(B215="", "", SUBTOTAL(3, $B$2:B215) * 1)</f>
         <v>214</v>
@@ -10838,7 +10841,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="216" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="216" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <f>IF(B216="", "", SUBTOTAL(3, $B$2:B216) * 1)</f>
         <v>215</v>
@@ -10869,7 +10872,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="217" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="217" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <f>IF(B217="", "", SUBTOTAL(3, $B$2:B217) * 1)</f>
         <v>216</v>
@@ -10900,7 +10903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="218" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="218" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <f>IF(B218="", "", SUBTOTAL(3, $B$2:B218) * 1)</f>
         <v>217</v>
@@ -10929,7 +10932,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="219" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="219" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <f>IF(B219="", "", SUBTOTAL(3, $B$2:B219) * 1)</f>
         <v>218</v>
@@ -10962,7 +10965,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="220" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="220" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <f>IF(B220="", "", SUBTOTAL(3, $B$2:B220) * 1)</f>
         <v>219</v>
@@ -10993,7 +10996,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="221" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="221" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <f>IF(B221="", "", SUBTOTAL(3, $B$2:B221) * 1)</f>
         <v>220</v>
@@ -11024,7 +11027,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="222" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="222" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <f>IF(B222="", "", SUBTOTAL(3, $B$2:B222) * 1)</f>
         <v>221</v>
@@ -11055,7 +11058,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="223" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="223" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <f>IF(B223="", "", SUBTOTAL(3, $B$2:B223) * 1)</f>
         <v>222</v>
@@ -11086,7 +11089,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="224" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="224" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <f>IF(B224="", "", SUBTOTAL(3, $B$2:B224) * 1)</f>
         <v>223</v>
@@ -11115,7 +11118,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="225" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="225" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <f>IF(B225="", "", SUBTOTAL(3, $B$2:B225) * 1)</f>
         <v>224</v>
@@ -11146,7 +11149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="226" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="226" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <f>IF(B226="", "", SUBTOTAL(3, $B$2:B226) * 1)</f>
         <v>225</v>
@@ -11177,7 +11180,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="227" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="227" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <f>IF(B227="", "", SUBTOTAL(3, $B$2:B227) * 1)</f>
         <v>226</v>
@@ -11208,7 +11211,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="228" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="228" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <f>IF(B228="", "", SUBTOTAL(3, $B$2:B228) * 1)</f>
         <v>227</v>
@@ -11239,7 +11242,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="229" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="229" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <f>IF(B229="", "", SUBTOTAL(3, $B$2:B229) * 1)</f>
         <v>228</v>
@@ -11270,7 +11273,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="230" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="230" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <f>IF(B230="", "", SUBTOTAL(3, $B$2:B230) * 1)</f>
         <v>229</v>
@@ -11303,7 +11306,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="231" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="231" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <f>IF(B231="", "", SUBTOTAL(3, $B$2:B231) * 1)</f>
         <v>230</v>
@@ -11334,7 +11337,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="232" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="232" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <f>IF(B232="", "", SUBTOTAL(3, $B$2:B232) * 1)</f>
         <v>231</v>
@@ -11363,7 +11366,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="233" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="233" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <f>IF(B233="", "", SUBTOTAL(3, $B$2:B233) * 1)</f>
         <v>232</v>
@@ -11394,7 +11397,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="234" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="234" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <f>IF(B234="", "", SUBTOTAL(3, $B$2:B234) * 1)</f>
         <v>233</v>
@@ -11427,7 +11430,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="235" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="235" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <f>IF(B235="", "", SUBTOTAL(3, $B$2:B235) * 1)</f>
         <v>234</v>
@@ -11458,7 +11461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="236" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="236" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <f>IF(B236="", "", SUBTOTAL(3, $B$2:B236) * 1)</f>
         <v>235</v>
@@ -11489,7 +11492,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="237" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="237" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <f>IF(B237="", "", SUBTOTAL(3, $B$2:B237) * 1)</f>
         <v>236</v>
@@ -11520,7 +11523,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="238" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="238" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <f>IF(B238="", "", SUBTOTAL(3, $B$2:B238) * 1)</f>
         <v>237</v>
@@ -11551,7 +11554,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="239" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="239" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <f>IF(B239="", "", SUBTOTAL(3, $B$2:B239) * 1)</f>
         <v>238</v>
@@ -11582,7 +11585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="240" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="240" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <f>IF(B240="", "", SUBTOTAL(3, $B$2:B240) * 1)</f>
         <v>239</v>
@@ -11613,7 +11616,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="241" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="241" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <f>IF(B241="", "", SUBTOTAL(3, $B$2:B241) * 1)</f>
         <v>240</v>
@@ -11644,7 +11647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="242" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="242" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <f>IF(B242="", "", SUBTOTAL(3, $B$2:B242) * 1)</f>
         <v>241</v>
@@ -11673,7 +11676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="243" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="243" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <f>IF(B243="", "", SUBTOTAL(3, $B$2:B243) * 1)</f>
         <v>242</v>
@@ -11704,7 +11707,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="244" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="244" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <f>IF(B244="", "", SUBTOTAL(3, $B$2:B244) * 1)</f>
         <v>243</v>
@@ -11735,7 +11738,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="245" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="245" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <f>IF(B245="", "", SUBTOTAL(3, $B$2:B245) * 1)</f>
         <v>244</v>
@@ -11764,7 +11767,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="246" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="246" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <f>IF(B246="", "", SUBTOTAL(3, $B$2:B246) * 1)</f>
         <v>245</v>
@@ -11797,7 +11800,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="247" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="247" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <f>IF(B247="", "", SUBTOTAL(3, $B$2:B247) * 1)</f>
         <v>246</v>
@@ -11828,7 +11831,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="248" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="248" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <f>IF(B248="", "", SUBTOTAL(3, $B$2:B248) * 1)</f>
         <v>247</v>
@@ -11859,7 +11862,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="249" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="249" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <f>IF(B249="", "", SUBTOTAL(3, $B$2:B249) * 1)</f>
         <v>248</v>
@@ -11890,7 +11893,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="250" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="250" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <f>IF(B250="", "", SUBTOTAL(3, $B$2:B250) * 1)</f>
         <v>249</v>
@@ -11919,7 +11922,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="251" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="251" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <f>IF(B251="", "", SUBTOTAL(3, $B$2:B251) * 1)</f>
         <v>250</v>
@@ -11948,7 +11951,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="252" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="252" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <f>IF(B252="", "", SUBTOTAL(3, $B$2:B252) * 1)</f>
         <v>251</v>
@@ -11977,7 +11980,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="253" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <f>IF(B253="", "", SUBTOTAL(3, $B$2:B253) * 1)</f>
         <v>252</v>
@@ -12010,7 +12013,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="254" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="254" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <f>IF(B254="", "", SUBTOTAL(3, $B$2:B254) * 1)</f>
         <v>253</v>
@@ -12039,7 +12042,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="255" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="255" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <f>IF(B255="", "", SUBTOTAL(3, $B$2:B255) * 1)</f>
         <v>254</v>
@@ -12070,7 +12073,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="256" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="256" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <f>IF(B256="", "", SUBTOTAL(3, $B$2:B256) * 1)</f>
         <v>255</v>
@@ -12099,7 +12102,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="257" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="257" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <f>IF(B257="", "", SUBTOTAL(3, $B$2:B257) * 1)</f>
         <v>256</v>
@@ -12132,7 +12135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="258" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="258" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <f>IF(B258="", "", SUBTOTAL(3, $B$2:B258) * 1)</f>
         <v>257</v>
@@ -12161,7 +12164,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="259" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="259" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <f>IF(B259="", "", SUBTOTAL(3, $B$2:B259) * 1)</f>
         <v>258</v>
@@ -12194,7 +12197,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="260" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="260" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <f>IF(B260="", "", SUBTOTAL(3, $B$2:B260) * 1)</f>
         <v>259</v>
@@ -12223,7 +12226,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="261" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="261" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <f>IF(B261="", "", SUBTOTAL(3, $B$2:B261) * 1)</f>
         <v>260</v>
@@ -12254,7 +12257,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="262" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="262" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <f>IF(B262="", "", SUBTOTAL(3, $B$2:B262) * 1)</f>
         <v>261</v>
@@ -12287,7 +12290,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="263" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="263" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <f>IF(B263="", "", SUBTOTAL(3, $B$2:B263) * 1)</f>
         <v>262</v>
@@ -12320,7 +12323,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="264" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="264" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <f>IF(B264="", "", SUBTOTAL(3, $B$2:B264) * 1)</f>
         <v>263</v>
@@ -12353,7 +12356,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="265" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="265" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <f>IF(B265="", "", SUBTOTAL(3, $B$2:B265) * 1)</f>
         <v>264</v>
@@ -12386,7 +12389,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="266" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="266" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <f>IF(B266="", "", SUBTOTAL(3, $B$2:B266) * 1)</f>
         <v>265</v>
@@ -12417,7 +12420,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="267" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="267" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <f>IF(B267="", "", SUBTOTAL(3, $B$2:B267) * 1)</f>
         <v>266</v>
@@ -12450,7 +12453,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="268" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="268" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <f>IF(B268="", "", SUBTOTAL(3, $B$2:B268) * 1)</f>
         <v>267</v>
@@ -12483,7 +12486,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="269" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="269" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <f>IF(B269="", "", SUBTOTAL(3, $B$2:B269) * 1)</f>
         <v>268</v>
@@ -12516,7 +12519,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="270" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="270" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <f>IF(B270="", "", SUBTOTAL(3, $B$2:B270) * 1)</f>
         <v>269</v>
@@ -12549,7 +12552,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="271" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <f>IF(B271="", "", SUBTOTAL(3, $B$2:B271) * 1)</f>
         <v>270</v>
@@ -12582,7 +12585,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="272" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="272" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <f>IF(B272="", "", SUBTOTAL(3, $B$2:B272) * 1)</f>
         <v>271</v>
@@ -12615,7 +12618,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="273" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="273" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <f>IF(B273="", "", SUBTOTAL(3, $B$2:B273) * 1)</f>
         <v>272</v>
@@ -12648,7 +12651,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="274" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="274" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <f>IF(B274="", "", SUBTOTAL(3, $B$2:B274) * 1)</f>
         <v>273</v>
@@ -12679,7 +12682,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="275" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="275" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <f>IF(B275="", "", SUBTOTAL(3, $B$2:B275) * 1)</f>
         <v>274</v>
@@ -12712,7 +12715,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="276" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="276" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <f>IF(B276="", "", SUBTOTAL(3, $B$2:B276) * 1)</f>
         <v>275</v>
@@ -12745,7 +12748,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="277" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="277" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <f>IF(B277="", "", SUBTOTAL(3, $B$2:B277) * 1)</f>
         <v>276</v>
@@ -12778,7 +12781,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="278" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="278" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <f>IF(B278="", "", SUBTOTAL(3, $B$2:B278) * 1)</f>
         <v>277</v>
@@ -12809,7 +12812,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="279" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="279" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <f>IF(B279="", "", SUBTOTAL(3, $B$2:B279) * 1)</f>
         <v>278</v>
@@ -12840,7 +12843,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="280" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="280" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <f>IF(B280="", "", SUBTOTAL(3, $B$2:B280) * 1)</f>
         <v>279</v>
@@ -12871,7 +12874,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="281" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="281" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <f>IF(B281="", "", SUBTOTAL(3, $B$2:B281) * 1)</f>
         <v>280</v>
@@ -12904,7 +12907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="282" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="282" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <f>IF(B282="", "", SUBTOTAL(3, $B$2:B282) * 1)</f>
         <v>281</v>
@@ -12937,7 +12940,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="283" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="283" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <f>IF(B283="", "", SUBTOTAL(3, $B$2:B283) * 1)</f>
         <v>282</v>
@@ -12970,7 +12973,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="284" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="284" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <f>IF(B284="", "", SUBTOTAL(3, $B$2:B284) * 1)</f>
         <v>283</v>
@@ -13003,7 +13006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="285" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="285" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <f>IF(B285="", "", SUBTOTAL(3, $B$2:B285) * 1)</f>
         <v>284</v>
@@ -13036,7 +13039,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="286" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="286" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <f>IF(B286="", "", SUBTOTAL(3, $B$2:B286) * 1)</f>
         <v>285</v>
@@ -13069,7 +13072,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="287" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="287" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <f>IF(B287="", "", SUBTOTAL(3, $B$2:B287) * 1)</f>
         <v>286</v>
@@ -13102,7 +13105,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="288" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="288" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <f>IF(B288="", "", SUBTOTAL(3, $B$2:B288) * 1)</f>
         <v>287</v>
@@ -13133,7 +13136,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="289" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="289" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <f>IF(B289="", "", SUBTOTAL(3, $B$2:B289) * 1)</f>
         <v>288</v>
@@ -13166,7 +13169,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="290" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="290" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <f>IF(B290="", "", SUBTOTAL(3, $B$2:B290) * 1)</f>
         <v>289</v>
@@ -13199,7 +13202,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="291" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="291" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <f>IF(B291="", "", SUBTOTAL(3, $B$2:B291) * 1)</f>
         <v>290</v>
@@ -13232,7 +13235,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="292" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="292" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <f>IF(B292="", "", SUBTOTAL(3, $B$2:B292) * 1)</f>
         <v>291</v>
@@ -13265,7 +13268,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="293" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="293" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <f>IF(B293="", "", SUBTOTAL(3, $B$2:B293) * 1)</f>
         <v>292</v>
@@ -13294,7 +13297,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="294" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="294" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <f>IF(B294="", "", SUBTOTAL(3, $B$2:B294) * 1)</f>
         <v>293</v>
@@ -13325,7 +13328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="295" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="295" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <f>IF(B295="", "", SUBTOTAL(3, $B$2:B295) * 1)</f>
         <v>294</v>
@@ -13356,7 +13359,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="296" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="296" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <f>IF(B296="", "", SUBTOTAL(3, $B$2:B296) * 1)</f>
         <v>295</v>
@@ -13389,7 +13392,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="297" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="297" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <f>IF(B297="", "", SUBTOTAL(3, $B$2:B297) * 1)</f>
         <v>296</v>
@@ -13420,7 +13423,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="298" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="298" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <f>IF(B298="", "", SUBTOTAL(3, $B$2:B298) * 1)</f>
         <v>297</v>
@@ -13453,7 +13456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="299" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="299" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <f>IF(B299="", "", SUBTOTAL(3, $B$2:B299) * 1)</f>
         <v>298</v>
@@ -13486,7 +13489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="300" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="300" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
         <f>IF(B300="", "", SUBTOTAL(3, $B$2:B300) * 1)</f>
         <v>299</v>
@@ -13519,7 +13522,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="301" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="301" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
         <f>IF(B301="", "", SUBTOTAL(3, $B$2:B301) * 1)</f>
         <v>300</v>
@@ -13550,7 +13553,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="302" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="302" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <f>IF(B302="", "", SUBTOTAL(3, $B$2:B302) * 1)</f>
         <v>301</v>
@@ -13581,7 +13584,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="303" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="303" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
         <f>IF(B303="", "", SUBTOTAL(3, $B$2:B303) * 1)</f>
         <v>302</v>
@@ -13612,7 +13615,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="304" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="304" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
         <f>IF(B304="", "", SUBTOTAL(3, $B$2:B304) * 1)</f>
         <v>303</v>
@@ -13645,7 +13648,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="305" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="305" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <f>IF(B305="", "", SUBTOTAL(3, $B$2:B305) * 1)</f>
         <v>304</v>
@@ -13678,7 +13681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="306" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="306" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <f>IF(B306="", "", SUBTOTAL(3, $B$2:B306) * 1)</f>
         <v>305</v>
@@ -13709,7 +13712,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="307" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="307" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <f>IF(B307="", "", SUBTOTAL(3, $B$2:B307) * 1)</f>
         <v>306</v>
@@ -13742,7 +13745,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="308" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="308" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <f>IF(B308="", "", SUBTOTAL(3, $B$2:B308) * 1)</f>
         <v>307</v>
@@ -13773,7 +13776,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="309" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="309" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <f>IF(B309="", "", SUBTOTAL(3, $B$2:B309) * 1)</f>
         <v>308</v>
@@ -13802,7 +13805,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="310" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="310" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <f>IF(B310="", "", SUBTOTAL(3, $B$2:B310) * 1)</f>
         <v>309</v>
@@ -13835,7 +13838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="311" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="311" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
         <f>IF(B311="", "", SUBTOTAL(3, $B$2:B311) * 1)</f>
         <v>310</v>
@@ -13866,7 +13869,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="312" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="312" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <f>IF(B312="", "", SUBTOTAL(3, $B$2:B312) * 1)</f>
         <v>311</v>
@@ -13897,7 +13900,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="313" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="313" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <f>IF(B313="", "", SUBTOTAL(3, $B$2:B313) * 1)</f>
         <v>312</v>
@@ -13930,7 +13933,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="314" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="314" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
         <f>IF(B314="", "", SUBTOTAL(3, $B$2:B314) * 1)</f>
         <v>313</v>
@@ -13961,7 +13964,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="315" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="315" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
         <f>IF(B315="", "", SUBTOTAL(3, $B$2:B315) * 1)</f>
         <v>314</v>
@@ -13994,7 +13997,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="316" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="316" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
         <f>IF(B316="", "", SUBTOTAL(3, $B$2:B316) * 1)</f>
         <v>315</v>
@@ -14027,7 +14030,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="317" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="317" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
         <f>IF(B317="", "", SUBTOTAL(3, $B$2:B317) * 1)</f>
         <v>316</v>
@@ -14060,7 +14063,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="318" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="318" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
         <f>IF(B318="", "", SUBTOTAL(3, $B$2:B318) * 1)</f>
         <v>317</v>
@@ -14093,7 +14096,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="319" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="319" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
         <f>IF(B319="", "", SUBTOTAL(3, $B$2:B319) * 1)</f>
         <v>318</v>
@@ -14126,7 +14129,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="320" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="320" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
         <f>IF(B320="", "", SUBTOTAL(3, $B$2:B320) * 1)</f>
         <v>319</v>
@@ -14159,7 +14162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="321" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="321" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
         <f>IF(B321="", "", SUBTOTAL(3, $B$2:B321) * 1)</f>
         <v>320</v>
@@ -14192,7 +14195,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="322" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="322" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
         <f>IF(B322="", "", SUBTOTAL(3, $B$2:B322) * 1)</f>
         <v>321</v>
@@ -14223,7 +14226,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="323" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="323" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
         <f>IF(B323="", "", SUBTOTAL(3, $B$2:B323) * 1)</f>
         <v>322</v>
@@ -14256,7 +14259,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="324" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="324" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
         <f>IF(B324="", "", SUBTOTAL(3, $B$2:B324) * 1)</f>
         <v>323</v>
@@ -14289,7 +14292,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="325" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="325" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
         <f>IF(B325="", "", SUBTOTAL(3, $B$2:B325) * 1)</f>
         <v>324</v>
@@ -14323,7 +14326,7 @@
       </c>
       <c r="K325" s="8"/>
     </row>
-    <row r="326" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="326" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
         <f>IF(B326="", "", SUBTOTAL(3, $B$2:B326) * 1)</f>
         <v>325</v>
@@ -14354,7 +14357,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="327" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="327" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
         <f>IF(B327="", "", SUBTOTAL(3, $B$2:B327) * 1)</f>
         <v>326</v>
@@ -14387,7 +14390,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="328" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="328" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
         <f>IF(B328="", "", SUBTOTAL(3, $B$2:B328) * 1)</f>
         <v>327</v>
@@ -14420,7 +14423,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="329" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="329" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
         <f>IF(B329="", "", SUBTOTAL(3, $B$2:B329) * 1)</f>
         <v>328</v>
@@ -14453,7 +14456,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="330" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="330" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
         <f>IF(B330="", "", SUBTOTAL(3, $B$2:B330) * 1)</f>
         <v>329</v>
@@ -14486,7 +14489,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="331" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="331" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2">
         <f>IF(B331="", "", SUBTOTAL(3, $B$2:B331) * 1)</f>
         <v>330</v>
@@ -14517,7 +14520,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="332" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="332" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
         <f>IF(B332="", "", SUBTOTAL(3, $B$2:B332) * 1)</f>
         <v>331</v>
@@ -14548,7 +14551,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="333" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="333" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
         <f>IF(B333="", "", SUBTOTAL(3, $B$2:B333) * 1)</f>
         <v>332</v>
@@ -14579,7 +14582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="334" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="334" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
         <f>IF(B334="", "", SUBTOTAL(3, $B$2:B334) * 1)</f>
         <v>333</v>
@@ -14612,7 +14615,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="335" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="335" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
         <f>IF(B335="", "", SUBTOTAL(3, $B$2:B335) * 1)</f>
         <v>334</v>
@@ -14643,7 +14646,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="336" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="336" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
         <f>IF(B336="", "", SUBTOTAL(3, $B$2:B336) * 1)</f>
         <v>335</v>
@@ -14674,7 +14677,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="337" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="337" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
         <f>IF(B337="", "", SUBTOTAL(3, $B$2:B337) * 1)</f>
         <v>336</v>
@@ -14707,7 +14710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="338" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="338" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
         <f>IF(B338="", "", SUBTOTAL(3, $B$2:B338) * 1)</f>
         <v>337</v>
@@ -14738,7 +14741,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="339" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="339" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
         <f>IF(B339="", "", SUBTOTAL(3, $B$2:B339) * 1)</f>
         <v>338</v>
@@ -14771,7 +14774,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="340" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="340" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2">
         <f>IF(B340="", "", SUBTOTAL(3, $B$2:B340) * 1)</f>
         <v>339</v>
@@ -14804,7 +14807,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="341" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="341" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2">
         <f>IF(B341="", "", SUBTOTAL(3, $B$2:B341) * 1)</f>
         <v>340</v>
@@ -14837,7 +14840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="342" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="342" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2">
         <f>IF(B342="", "", SUBTOTAL(3, $B$2:B342) * 1)</f>
         <v>341</v>
@@ -14870,7 +14873,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="343" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="343" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2">
         <f>IF(B343="", "", SUBTOTAL(3, $B$2:B343) * 1)</f>
         <v>342</v>
@@ -14903,7 +14906,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="344" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="344" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2">
         <f>IF(B344="", "", SUBTOTAL(3, $B$2:B344) * 1)</f>
         <v>343</v>
@@ -14932,16 +14935,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="345" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="345" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2">
         <f>IF(B345="", "", SUBTOTAL(3, $B$2:B345) * 1)</f>
         <v>344</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>608</v>
+        <v>1229</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>478</v>
+        <v>387</v>
       </c>
       <c r="D345" s="2"/>
       <c r="E345" s="4" t="s">
@@ -14961,16 +14964,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="346" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="346" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2">
         <f>IF(B346="", "", SUBTOTAL(3, $B$2:B346) * 1)</f>
         <v>345</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>387</v>
+        <v>278</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" s="4" t="s">
@@ -14990,16 +14993,16 @@
         <v>9</v>
       </c>
     </row>
-    <row r="347" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="347" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2">
         <f>IF(B347="", "", SUBTOTAL(3, $B$2:B347) * 1)</f>
         <v>346</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" s="4" t="s">
@@ -15019,42 +15022,42 @@
         <v>9</v>
       </c>
     </row>
-    <row r="348" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="348" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2">
         <f>IF(B348="", "", SUBTOTAL(3, $B$2:B348) * 1)</f>
         <v>347</v>
       </c>
-      <c r="B348" s="4" t="s">
-        <v>1231</v>
-      </c>
-      <c r="C348" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="D348" s="2"/>
-      <c r="E348" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="F348" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G348" s="2">
-        <v>2026</v>
+      <c r="B348" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="C348" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D348" s="3"/>
+      <c r="E348" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F348" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G348" s="2" t="s">
+        <v>604</v>
       </c>
       <c r="H348" s="3" t="s">
-        <v>23</v>
+        <v>197</v>
       </c>
       <c r="I348" s="2"/>
       <c r="J348" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="349" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="349" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2">
         <f>IF(B349="", "", SUBTOTAL(3, $B$2:B349) * 1)</f>
         <v>348</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="C349" s="3" t="s">
         <v>60</v>
@@ -15064,7 +15067,7 @@
         <v>20</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>26</v>
+        <v>356</v>
       </c>
       <c r="G349" s="2" t="s">
         <v>604</v>
@@ -15077,16 +15080,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="350" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="350" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2">
         <f>IF(B350="", "", SUBTOTAL(3, $B$2:B350) * 1)</f>
         <v>349</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>553</v>
+        <v>520</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>60</v>
+        <v>521</v>
       </c>
       <c r="D350" s="3"/>
       <c r="E350" s="3" t="s">
@@ -15106,16 +15109,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="351" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="351" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2">
         <f>IF(B351="", "", SUBTOTAL(3, $B$2:B351) * 1)</f>
         <v>350</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>520</v>
+        <v>565</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>521</v>
+        <v>566</v>
       </c>
       <c r="D351" s="3"/>
       <c r="E351" s="3" t="s">
@@ -15135,16 +15138,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="352" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="352" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2">
         <f>IF(B352="", "", SUBTOTAL(3, $B$2:B352) * 1)</f>
         <v>351</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>565</v>
+        <v>535</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>566</v>
+        <v>536</v>
       </c>
       <c r="D352" s="3"/>
       <c r="E352" s="3" t="s">
@@ -15164,16 +15167,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="353" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="353" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2">
         <f>IF(B353="", "", SUBTOTAL(3, $B$2:B353) * 1)</f>
         <v>352</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>535</v>
+        <v>578</v>
       </c>
       <c r="C353" s="3" t="s">
-        <v>536</v>
+        <v>579</v>
       </c>
       <c r="D353" s="3"/>
       <c r="E353" s="3" t="s">
@@ -15193,16 +15196,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="354" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="354" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2">
         <f>IF(B354="", "", SUBTOTAL(3, $B$2:B354) * 1)</f>
         <v>353</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
       <c r="C354" s="3" t="s">
-        <v>579</v>
+        <v>563</v>
       </c>
       <c r="D354" s="3"/>
       <c r="E354" s="3" t="s">
@@ -15222,16 +15225,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="355" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="355" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2">
         <f>IF(B355="", "", SUBTOTAL(3, $B$2:B355) * 1)</f>
         <v>354</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>562</v>
+        <v>597</v>
       </c>
       <c r="C355" s="3" t="s">
-        <v>563</v>
+        <v>226</v>
       </c>
       <c r="D355" s="3"/>
       <c r="E355" s="3" t="s">
@@ -15251,16 +15254,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="356" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="356" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2">
         <f>IF(B356="", "", SUBTOTAL(3, $B$2:B356) * 1)</f>
         <v>355</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>597</v>
+        <v>570</v>
       </c>
       <c r="C356" s="3" t="s">
-        <v>226</v>
+        <v>310</v>
       </c>
       <c r="D356" s="3"/>
       <c r="E356" s="3" t="s">
@@ -15280,16 +15283,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="357" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="357" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2">
         <f>IF(B357="", "", SUBTOTAL(3, $B$2:B357) * 1)</f>
         <v>356</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>570</v>
+        <v>529</v>
       </c>
       <c r="C357" s="3" t="s">
-        <v>310</v>
+        <v>24</v>
       </c>
       <c r="D357" s="3"/>
       <c r="E357" s="3" t="s">
@@ -15309,16 +15312,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="358" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="358" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2">
         <f>IF(B358="", "", SUBTOTAL(3, $B$2:B358) * 1)</f>
         <v>357</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>529</v>
+        <v>564</v>
       </c>
       <c r="C358" s="3" t="s">
-        <v>24</v>
+        <v>341</v>
       </c>
       <c r="D358" s="3"/>
       <c r="E358" s="3" t="s">
@@ -15338,13 +15341,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="359" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="359" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2">
         <f>IF(B359="", "", SUBTOTAL(3, $B$2:B359) * 1)</f>
         <v>358</v>
       </c>
       <c r="B359" s="3" t="s">
-        <v>564</v>
+        <v>599</v>
       </c>
       <c r="C359" s="3" t="s">
         <v>341</v>
@@ -15367,16 +15370,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="360" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="360" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2">
         <f>IF(B360="", "", SUBTOTAL(3, $B$2:B360) * 1)</f>
         <v>359</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>599</v>
+        <v>560</v>
       </c>
       <c r="C360" s="3" t="s">
-        <v>341</v>
+        <v>561</v>
       </c>
       <c r="D360" s="3"/>
       <c r="E360" s="3" t="s">
@@ -15396,16 +15399,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="361" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="361" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2">
         <f>IF(B361="", "", SUBTOTAL(3, $B$2:B361) * 1)</f>
         <v>360</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>560</v>
+        <v>532</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>561</v>
+        <v>304</v>
       </c>
       <c r="D361" s="3"/>
       <c r="E361" s="3" t="s">
@@ -15425,23 +15428,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="362" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="362" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2">
         <f>IF(B362="", "", SUBTOTAL(3, $B$2:B362) * 1)</f>
         <v>361</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>532</v>
+        <v>568</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="D362" s="3"/>
       <c r="E362" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F362" s="3" t="s">
-        <v>356</v>
+        <v>62</v>
       </c>
       <c r="G362" s="2" t="s">
         <v>604</v>
@@ -15454,23 +15457,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="363" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="363" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2">
         <f>IF(B363="", "", SUBTOTAL(3, $B$2:B363) * 1)</f>
         <v>362</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>275</v>
+        <v>572</v>
       </c>
       <c r="D363" s="3"/>
       <c r="E363" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F363" s="3" t="s">
-        <v>62</v>
+        <v>356</v>
       </c>
       <c r="G363" s="2" t="s">
         <v>604</v>
@@ -15483,23 +15486,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="364" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="364" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2">
         <f>IF(B364="", "", SUBTOTAL(3, $B$2:B364) * 1)</f>
         <v>363</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>571</v>
+        <v>539</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>572</v>
+        <v>307</v>
       </c>
       <c r="D364" s="3"/>
       <c r="E364" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F364" s="3" t="s">
-        <v>356</v>
+        <v>26</v>
       </c>
       <c r="G364" s="2" t="s">
         <v>604</v>
@@ -15512,23 +15515,23 @@
         <v>10</v>
       </c>
     </row>
-    <row r="365" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="365" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2">
         <f>IF(B365="", "", SUBTOTAL(3, $B$2:B365) * 1)</f>
         <v>364</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>307</v>
+        <v>74</v>
       </c>
       <c r="D365" s="3"/>
       <c r="E365" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F365" s="3" t="s">
-        <v>26</v>
+        <v>356</v>
       </c>
       <c r="G365" s="2" t="s">
         <v>604</v>
@@ -15541,16 +15544,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="366" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="366" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2">
         <f>IF(B366="", "", SUBTOTAL(3, $B$2:B366) * 1)</f>
         <v>365</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="D366" s="3"/>
       <c r="E366" s="3" t="s">
@@ -15570,13 +15573,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="367" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="367" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2">
         <f>IF(B367="", "", SUBTOTAL(3, $B$2:B367) * 1)</f>
         <v>366</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>530</v>
+        <v>590</v>
       </c>
       <c r="C367" s="3" t="s">
         <v>153</v>
@@ -15599,16 +15602,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="368" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="368" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2">
         <f>IF(B368="", "", SUBTOTAL(3, $B$2:B368) * 1)</f>
         <v>367</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>153</v>
+        <v>353</v>
       </c>
       <c r="D368" s="3"/>
       <c r="E368" s="3" t="s">
@@ -15628,16 +15631,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="369" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="369" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2">
         <f>IF(B369="", "", SUBTOTAL(3, $B$2:B369) * 1)</f>
         <v>368</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>595</v>
+        <v>546</v>
       </c>
       <c r="C369" s="3" t="s">
-        <v>353</v>
+        <v>234</v>
       </c>
       <c r="D369" s="3"/>
       <c r="E369" s="3" t="s">
@@ -15657,16 +15660,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="370" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="370" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2">
         <f>IF(B370="", "", SUBTOTAL(3, $B$2:B370) * 1)</f>
         <v>369</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="C370" s="3" t="s">
-        <v>234</v>
+        <v>543</v>
       </c>
       <c r="D370" s="3"/>
       <c r="E370" s="3" t="s">
@@ -15686,16 +15689,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="371" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="371" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2">
         <f>IF(B371="", "", SUBTOTAL(3, $B$2:B371) * 1)</f>
         <v>370</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="C371" s="3" t="s">
-        <v>543</v>
+        <v>140</v>
       </c>
       <c r="D371" s="3"/>
       <c r="E371" s="3" t="s">
@@ -15715,16 +15718,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="372" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="372" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2">
         <f>IF(B372="", "", SUBTOTAL(3, $B$2:B372) * 1)</f>
         <v>371</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="C372" s="3" t="s">
-        <v>140</v>
+        <v>556</v>
       </c>
       <c r="D372" s="3"/>
       <c r="E372" s="3" t="s">
@@ -15744,16 +15747,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="373" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="373" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2">
         <f>IF(B373="", "", SUBTOTAL(3, $B$2:B373) * 1)</f>
         <v>372</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="C373" s="3" t="s">
-        <v>556</v>
+        <v>212</v>
       </c>
       <c r="D373" s="3"/>
       <c r="E373" s="3" t="s">
@@ -15773,16 +15776,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="374" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="374" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2">
         <f>IF(B374="", "", SUBTOTAL(3, $B$2:B374) * 1)</f>
         <v>373</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="C374" s="3" t="s">
-        <v>212</v>
+        <v>552</v>
       </c>
       <c r="D374" s="3"/>
       <c r="E374" s="3" t="s">
@@ -15802,13 +15805,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="375" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="375" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2">
         <f>IF(B375="", "", SUBTOTAL(3, $B$2:B375) * 1)</f>
         <v>374</v>
       </c>
       <c r="B375" s="3" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="C375" s="3" t="s">
         <v>552</v>
@@ -15831,13 +15834,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="376" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="376" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2">
         <f>IF(B376="", "", SUBTOTAL(3, $B$2:B376) * 1)</f>
         <v>375</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="C376" s="3" t="s">
         <v>552</v>
@@ -15860,16 +15863,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="377" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="377" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2">
         <f>IF(B377="", "", SUBTOTAL(3, $B$2:B377) * 1)</f>
         <v>376</v>
       </c>
       <c r="B377" s="3" t="s">
-        <v>584</v>
+        <v>518</v>
       </c>
       <c r="C377" s="3" t="s">
-        <v>552</v>
+        <v>519</v>
       </c>
       <c r="D377" s="3"/>
       <c r="E377" s="3" t="s">
@@ -15889,16 +15892,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="378" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="378" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2">
         <f>IF(B378="", "", SUBTOTAL(3, $B$2:B378) * 1)</f>
         <v>377</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>518</v>
+        <v>548</v>
       </c>
       <c r="C378" s="3" t="s">
-        <v>519</v>
+        <v>549</v>
       </c>
       <c r="D378" s="3"/>
       <c r="E378" s="3" t="s">
@@ -15918,16 +15921,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="379" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="379" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2">
         <f>IF(B379="", "", SUBTOTAL(3, $B$2:B379) * 1)</f>
         <v>378</v>
       </c>
       <c r="B379" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C379" s="3" t="s">
-        <v>549</v>
+        <v>88</v>
       </c>
       <c r="D379" s="3"/>
       <c r="E379" s="3" t="s">
@@ -15947,16 +15950,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="380" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="380" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2">
         <f>IF(B380="", "", SUBTOTAL(3, $B$2:B380) * 1)</f>
         <v>379</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>88</v>
+        <v>363</v>
       </c>
       <c r="D380" s="3"/>
       <c r="E380" s="3" t="s">
@@ -15976,16 +15979,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="381" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="381" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2">
         <f>IF(B381="", "", SUBTOTAL(3, $B$2:B381) * 1)</f>
         <v>380</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>547</v>
+        <v>594</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>363</v>
+        <v>134</v>
       </c>
       <c r="D381" s="3"/>
       <c r="E381" s="3" t="s">
@@ -16005,16 +16008,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="382" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="382" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2">
         <f>IF(B382="", "", SUBTOTAL(3, $B$2:B382) * 1)</f>
         <v>381</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>594</v>
+        <v>537</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="D382" s="3"/>
       <c r="E382" s="3" t="s">
@@ -16034,16 +16037,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="383" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="383" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2">
         <f>IF(B383="", "", SUBTOTAL(3, $B$2:B383) * 1)</f>
         <v>382</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>537</v>
+        <v>586</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>43</v>
+        <v>146</v>
       </c>
       <c r="D383" s="3"/>
       <c r="E383" s="3" t="s">
@@ -16063,16 +16066,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="384" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="384" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2">
         <f>IF(B384="", "", SUBTOTAL(3, $B$2:B384) * 1)</f>
         <v>383</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>586</v>
+        <v>527</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>146</v>
+        <v>368</v>
       </c>
       <c r="D384" s="3"/>
       <c r="E384" s="3" t="s">
@@ -16092,16 +16095,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="385" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="385" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2">
         <f>IF(B385="", "", SUBTOTAL(3, $B$2:B385) * 1)</f>
         <v>384</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>527</v>
+        <v>587</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="D385" s="3"/>
       <c r="E385" s="3" t="s">
@@ -16121,16 +16124,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="386" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="386" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2">
         <f>IF(B386="", "", SUBTOTAL(3, $B$2:B386) * 1)</f>
         <v>385</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>587</v>
+        <v>544</v>
       </c>
       <c r="C386" s="3" t="s">
-        <v>375</v>
+        <v>63</v>
       </c>
       <c r="D386" s="3"/>
       <c r="E386" s="3" t="s">
@@ -16150,13 +16153,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="387" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="387" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2">
         <f>IF(B387="", "", SUBTOTAL(3, $B$2:B387) * 1)</f>
         <v>386</v>
       </c>
       <c r="B387" s="3" t="s">
-        <v>544</v>
+        <v>216</v>
       </c>
       <c r="C387" s="3" t="s">
         <v>63</v>
@@ -16179,13 +16182,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="388" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="388" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2">
         <f>IF(B388="", "", SUBTOTAL(3, $B$2:B388) * 1)</f>
         <v>387</v>
       </c>
       <c r="B388" s="3" t="s">
-        <v>216</v>
+        <v>577</v>
       </c>
       <c r="C388" s="3" t="s">
         <v>63</v>
@@ -16208,16 +16211,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="389" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="389" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2">
         <f>IF(B389="", "", SUBTOTAL(3, $B$2:B389) * 1)</f>
         <v>388</v>
       </c>
       <c r="B389" s="3" t="s">
-        <v>577</v>
+        <v>557</v>
       </c>
       <c r="C389" s="3" t="s">
-        <v>63</v>
+        <v>558</v>
       </c>
       <c r="D389" s="3"/>
       <c r="E389" s="3" t="s">
@@ -16237,16 +16240,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="390" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="390" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2">
         <f>IF(B390="", "", SUBTOTAL(3, $B$2:B390) * 1)</f>
         <v>389</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>557</v>
+        <v>531</v>
       </c>
       <c r="C390" s="3" t="s">
-        <v>558</v>
+        <v>138</v>
       </c>
       <c r="D390" s="3"/>
       <c r="E390" s="3" t="s">
@@ -16266,16 +16269,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="391" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="391" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2">
         <f>IF(B391="", "", SUBTOTAL(3, $B$2:B391) * 1)</f>
         <v>390</v>
       </c>
       <c r="B391" s="3" t="s">
-        <v>531</v>
+        <v>592</v>
       </c>
       <c r="C391" s="3" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="D391" s="3"/>
       <c r="E391" s="3" t="s">
@@ -16295,16 +16298,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="392" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="392" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2">
         <f>IF(B392="", "", SUBTOTAL(3, $B$2:B392) * 1)</f>
         <v>391</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="C392" s="3" t="s">
-        <v>148</v>
+        <v>190</v>
       </c>
       <c r="D392" s="3"/>
       <c r="E392" s="3" t="s">
@@ -16324,16 +16327,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="393" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="393" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2">
         <f>IF(B393="", "", SUBTOTAL(3, $B$2:B393) * 1)</f>
         <v>392</v>
       </c>
       <c r="B393" s="3" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C393" s="3" t="s">
-        <v>190</v>
+        <v>49</v>
       </c>
       <c r="D393" s="3"/>
       <c r="E393" s="3" t="s">
@@ -16353,13 +16356,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="394" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="394" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2">
         <f>IF(B394="", "", SUBTOTAL(3, $B$2:B394) * 1)</f>
         <v>393</v>
       </c>
       <c r="B394" s="3" t="s">
-        <v>581</v>
+        <v>591</v>
       </c>
       <c r="C394" s="3" t="s">
         <v>49</v>
@@ -16382,16 +16385,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="395" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="395" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2">
         <f>IF(B395="", "", SUBTOTAL(3, $B$2:B395) * 1)</f>
         <v>394</v>
       </c>
       <c r="B395" s="3" t="s">
-        <v>591</v>
+        <v>573</v>
       </c>
       <c r="C395" s="3" t="s">
-        <v>49</v>
+        <v>574</v>
       </c>
       <c r="D395" s="3"/>
       <c r="E395" s="3" t="s">
@@ -16411,74 +16414,74 @@
         <v>10</v>
       </c>
     </row>
-    <row r="396" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="396" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2">
         <f>IF(B396="", "", SUBTOTAL(3, $B$2:B396) * 1)</f>
         <v>395</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>573</v>
+        <v>522</v>
       </c>
       <c r="C396" s="3" t="s">
-        <v>574</v>
+        <v>523</v>
       </c>
       <c r="D396" s="3"/>
       <c r="E396" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F396" s="3" t="s">
-        <v>356</v>
+        <v>14</v>
       </c>
       <c r="G396" s="2" t="s">
         <v>604</v>
       </c>
       <c r="H396" s="3" t="s">
-        <v>197</v>
+        <v>524</v>
       </c>
       <c r="I396" s="2"/>
       <c r="J396" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="397" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="397" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2">
         <f>IF(B397="", "", SUBTOTAL(3, $B$2:B397) * 1)</f>
         <v>396</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>522</v>
+        <v>575</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>523</v>
+        <v>576</v>
       </c>
       <c r="D397" s="3"/>
       <c r="E397" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F397" s="3" t="s">
-        <v>14</v>
+        <v>356</v>
       </c>
       <c r="G397" s="2" t="s">
         <v>604</v>
       </c>
       <c r="H397" s="3" t="s">
-        <v>524</v>
+        <v>197</v>
       </c>
       <c r="I397" s="2"/>
       <c r="J397" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="398" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="398" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2">
         <f>IF(B398="", "", SUBTOTAL(3, $B$2:B398) * 1)</f>
         <v>397</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>576</v>
+        <v>19</v>
       </c>
       <c r="D398" s="3"/>
       <c r="E398" s="3" t="s">
@@ -16498,16 +16501,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="399" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="399" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2">
         <f>IF(B399="", "", SUBTOTAL(3, $B$2:B399) * 1)</f>
         <v>398</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>580</v>
+        <v>588</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>19</v>
+        <v>589</v>
       </c>
       <c r="D399" s="3"/>
       <c r="E399" s="3" t="s">
@@ -16527,16 +16530,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="400" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="400" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2">
         <f>IF(B400="", "", SUBTOTAL(3, $B$2:B400) * 1)</f>
         <v>399</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>588</v>
+        <v>554</v>
       </c>
       <c r="C400" s="3" t="s">
-        <v>589</v>
+        <v>80</v>
       </c>
       <c r="D400" s="3"/>
       <c r="E400" s="3" t="s">
@@ -16556,16 +16559,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="401" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="401" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2">
         <f>IF(B401="", "", SUBTOTAL(3, $B$2:B401) * 1)</f>
         <v>400</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
       <c r="C401" s="3" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="D401" s="3"/>
       <c r="E401" s="3" t="s">
@@ -16585,16 +16588,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="402" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="402" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2">
         <f>IF(B402="", "", SUBTOTAL(3, $B$2:B402) * 1)</f>
         <v>401</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>541</v>
+        <v>525</v>
       </c>
       <c r="C402" s="3" t="s">
-        <v>46</v>
+        <v>526</v>
       </c>
       <c r="D402" s="3"/>
       <c r="E402" s="3" t="s">
@@ -16614,13 +16617,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="403" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="403" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2">
         <f>IF(B403="", "", SUBTOTAL(3, $B$2:B403) * 1)</f>
         <v>402</v>
       </c>
       <c r="B403" s="3" t="s">
-        <v>525</v>
+        <v>596</v>
       </c>
       <c r="C403" s="3" t="s">
         <v>526</v>
@@ -16643,16 +16646,16 @@
         <v>10</v>
       </c>
     </row>
-    <row r="404" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="404" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2">
         <f>IF(B404="", "", SUBTOTAL(3, $B$2:B404) * 1)</f>
         <v>403</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>596</v>
+        <v>545</v>
       </c>
       <c r="C404" s="3" t="s">
-        <v>526</v>
+        <v>178</v>
       </c>
       <c r="D404" s="3"/>
       <c r="E404" s="3" t="s">
@@ -16672,74 +16675,74 @@
         <v>10</v>
       </c>
     </row>
-    <row r="405" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="405" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2">
         <f>IF(B405="", "", SUBTOTAL(3, $B$2:B405) * 1)</f>
         <v>404</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
       <c r="C405" s="3" t="s">
-        <v>178</v>
+        <v>583</v>
       </c>
       <c r="D405" s="3"/>
-      <c r="E405" s="3" t="s">
+      <c r="E405" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F405" s="3" t="s">
+      <c r="F405" s="5" t="s">
         <v>356</v>
       </c>
       <c r="G405" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="H405" s="3" t="s">
+      <c r="H405" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="I405" s="2"/>
+      <c r="I405" s="5"/>
       <c r="J405" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="406" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="406" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2">
         <f>IF(B406="", "", SUBTOTAL(3, $B$2:B406) * 1)</f>
         <v>405</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>582</v>
+        <v>559</v>
       </c>
       <c r="C406" s="3" t="s">
-        <v>583</v>
+        <v>125</v>
       </c>
       <c r="D406" s="3"/>
-      <c r="E406" s="5" t="s">
+      <c r="E406" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F406" s="5" t="s">
+      <c r="F406" s="3" t="s">
         <v>356</v>
       </c>
       <c r="G406" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="H406" s="5" t="s">
+      <c r="H406" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="I406" s="5"/>
+      <c r="I406" s="2"/>
       <c r="J406" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="407" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="407" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2">
         <f>IF(B407="", "", SUBTOTAL(3, $B$2:B407) * 1)</f>
         <v>406</v>
       </c>
       <c r="B407" s="3" t="s">
-        <v>559</v>
+        <v>528</v>
       </c>
       <c r="C407" s="3" t="s">
-        <v>125</v>
+        <v>32</v>
       </c>
       <c r="D407" s="3"/>
       <c r="E407" s="3" t="s">
@@ -16759,129 +16762,115 @@
         <v>10</v>
       </c>
     </row>
-    <row r="408" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="408" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2">
         <f>IF(B408="", "", SUBTOTAL(3, $B$2:B408) * 1)</f>
         <v>407</v>
       </c>
-      <c r="B408" s="3" t="s">
-        <v>528</v>
+      <c r="B408" s="4" t="s">
+        <v>706</v>
       </c>
       <c r="C408" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D408" s="3"/>
+      <c r="D408" s="4" t="s">
+        <v>707</v>
+      </c>
       <c r="E408" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F408" s="3" t="s">
-        <v>356</v>
+        <v>14</v>
       </c>
       <c r="G408" s="2" t="s">
         <v>604</v>
       </c>
       <c r="H408" s="3" t="s">
-        <v>197</v>
+        <v>593</v>
       </c>
       <c r="I408" s="2"/>
       <c r="J408" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="409" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="409" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2">
         <f>IF(B409="", "", SUBTOTAL(3, $B$2:B409) * 1)</f>
         <v>408</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>706</v>
+        <v>853</v>
       </c>
       <c r="C409" s="3" t="s">
-        <v>32</v>
+        <v>355</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>707</v>
+        <v>854</v>
       </c>
       <c r="E409" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G409" s="2" t="s">
-        <v>604</v>
+        <v>356</v>
+      </c>
+      <c r="G409" s="3">
+        <v>2022</v>
       </c>
       <c r="H409" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="I409" s="2"/>
+        <v>357</v>
+      </c>
+      <c r="I409" s="3" t="s">
+        <v>994</v>
+      </c>
       <c r="J409" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="410" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="410" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2">
         <f>IF(B410="", "", SUBTOTAL(3, $B$2:B410) * 1)</f>
         <v>409</v>
       </c>
-      <c r="B410" s="4" t="s">
-        <v>853</v>
+      <c r="B410" s="3" t="s">
+        <v>567</v>
       </c>
       <c r="C410" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="D410" s="4" t="s">
-        <v>854</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="D410" s="3"/>
       <c r="E410" s="3" t="s">
         <v>20</v>
       </c>
       <c r="F410" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="G410" s="3">
-        <v>2022</v>
+      <c r="G410" s="2" t="s">
+        <v>604</v>
       </c>
       <c r="H410" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="I410" s="3" t="s">
-        <v>994</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="I410" s="2"/>
       <c r="J410" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="411" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A411" s="2">
+    <row r="411" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A411" s="2" t="str">
         <f>IF(B411="", "", SUBTOTAL(3, $B$2:B411) * 1)</f>
-        <v>410</v>
-      </c>
-      <c r="B411" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="C411" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D411" s="3"/>
-      <c r="E411" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F411" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="G411" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="H411" s="3" t="s">
-        <v>197</v>
-      </c>
+        <v/>
+      </c>
+      <c r="B411" s="2"/>
+      <c r="C411" s="2"/>
+      <c r="D411" s="2"/>
+      <c r="E411" s="2"/>
+      <c r="F411" s="2"/>
+      <c r="G411" s="2"/>
+      <c r="H411" s="2"/>
       <c r="I411" s="2"/>
-      <c r="J411" s="3">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="412" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="J411" s="2"/>
+    </row>
+    <row r="412" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="str">
         <f>IF(B412="", "", SUBTOTAL(3, $B$2:B412) * 1)</f>
         <v/>
@@ -16896,7 +16885,7 @@
       <c r="I412" s="2"/>
       <c r="J412" s="2"/>
     </row>
-    <row r="413" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="413" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="str">
         <f>IF(B413="", "", SUBTOTAL(3, $B$2:B413) * 1)</f>
         <v/>
@@ -16911,7 +16900,7 @@
       <c r="I413" s="2"/>
       <c r="J413" s="2"/>
     </row>
-    <row r="414" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="414" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="str">
         <f>IF(B414="", "", SUBTOTAL(3, $B$2:B414) * 1)</f>
         <v/>
@@ -16926,7 +16915,7 @@
       <c r="I414" s="2"/>
       <c r="J414" s="2"/>
     </row>
-    <row r="415" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="415" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="str">
         <f>IF(B415="", "", SUBTOTAL(3, $B$2:B415) * 1)</f>
         <v/>
@@ -16941,7 +16930,7 @@
       <c r="I415" s="2"/>
       <c r="J415" s="2"/>
     </row>
-    <row r="416" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="416" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="str">
         <f>IF(B416="", "", SUBTOTAL(3, $B$2:B416) * 1)</f>
         <v/>
@@ -16956,7 +16945,7 @@
       <c r="I416" s="2"/>
       <c r="J416" s="2"/>
     </row>
-    <row r="417" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="417" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="str">
         <f>IF(B417="", "", SUBTOTAL(3, $B$2:B417) * 1)</f>
         <v/>
@@ -16971,7 +16960,7 @@
       <c r="I417" s="2"/>
       <c r="J417" s="2"/>
     </row>
-    <row r="418" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="418" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="str">
         <f>IF(B418="", "", SUBTOTAL(3, $B$2:B418) * 1)</f>
         <v/>
@@ -16986,7 +16975,7 @@
       <c r="I418" s="2"/>
       <c r="J418" s="2"/>
     </row>
-    <row r="419" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="419" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="str">
         <f>IF(B419="", "", SUBTOTAL(3, $B$2:B419) * 1)</f>
         <v/>
@@ -17001,7 +16990,7 @@
       <c r="I419" s="2"/>
       <c r="J419" s="2"/>
     </row>
-    <row r="420" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="420" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="str">
         <f>IF(B420="", "", SUBTOTAL(3, $B$2:B420) * 1)</f>
         <v/>
@@ -17016,7 +17005,7 @@
       <c r="I420" s="2"/>
       <c r="J420" s="2"/>
     </row>
-    <row r="421" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="421" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="str">
         <f>IF(B421="", "", SUBTOTAL(3, $B$2:B421) * 1)</f>
         <v/>
@@ -17031,7 +17020,7 @@
       <c r="I421" s="2"/>
       <c r="J421" s="2"/>
     </row>
-    <row r="422" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="422" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="str">
         <f>IF(B422="", "", SUBTOTAL(3, $B$2:B422) * 1)</f>
         <v/>
@@ -17046,7 +17035,7 @@
       <c r="I422" s="2"/>
       <c r="J422" s="2"/>
     </row>
-    <row r="423" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="423" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="str">
         <f>IF(B423="", "", SUBTOTAL(3, $B$2:B423) * 1)</f>
         <v/>
@@ -17061,7 +17050,7 @@
       <c r="I423" s="2"/>
       <c r="J423" s="2"/>
     </row>
-    <row r="424" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="424" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="str">
         <f>IF(B424="", "", SUBTOTAL(3, $B$2:B424) * 1)</f>
         <v/>
@@ -17076,7 +17065,7 @@
       <c r="I424" s="2"/>
       <c r="J424" s="2"/>
     </row>
-    <row r="425" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="425" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="str">
         <f>IF(B425="", "", SUBTOTAL(3, $B$2:B425) * 1)</f>
         <v/>
@@ -17091,7 +17080,7 @@
       <c r="I425" s="2"/>
       <c r="J425" s="2"/>
     </row>
-    <row r="426" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="426" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="str">
         <f>IF(B426="", "", SUBTOTAL(3, $B$2:B426) * 1)</f>
         <v/>
@@ -17106,7 +17095,7 @@
       <c r="I426" s="2"/>
       <c r="J426" s="2"/>
     </row>
-    <row r="427" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="427" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="str">
         <f>IF(B427="", "", SUBTOTAL(3, $B$2:B427) * 1)</f>
         <v/>
@@ -17121,7 +17110,7 @@
       <c r="I427" s="2"/>
       <c r="J427" s="2"/>
     </row>
-    <row r="428" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="428" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="str">
         <f>IF(B428="", "", SUBTOTAL(3, $B$2:B428) * 1)</f>
         <v/>
@@ -17136,7 +17125,7 @@
       <c r="I428" s="2"/>
       <c r="J428" s="2"/>
     </row>
-    <row r="429" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="429" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="str">
         <f>IF(B429="", "", SUBTOTAL(3, $B$2:B429) * 1)</f>
         <v/>
@@ -17151,7 +17140,7 @@
       <c r="I429" s="2"/>
       <c r="J429" s="2"/>
     </row>
-    <row r="430" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="430" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="str">
         <f>IF(B430="", "", SUBTOTAL(3, $B$2:B430) * 1)</f>
         <v/>
@@ -17166,7 +17155,7 @@
       <c r="I430" s="2"/>
       <c r="J430" s="2"/>
     </row>
-    <row r="431" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="431" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="str">
         <f>IF(B431="", "", SUBTOTAL(3, $B$2:B431) * 1)</f>
         <v/>
@@ -17181,7 +17170,7 @@
       <c r="I431" s="2"/>
       <c r="J431" s="2"/>
     </row>
-    <row r="432" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="432" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="str">
         <f>IF(B432="", "", SUBTOTAL(3, $B$2:B432) * 1)</f>
         <v/>
@@ -17196,7 +17185,7 @@
       <c r="I432" s="2"/>
       <c r="J432" s="2"/>
     </row>
-    <row r="433" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="433" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="str">
         <f>IF(B433="", "", SUBTOTAL(3, $B$2:B433) * 1)</f>
         <v/>
@@ -17211,7 +17200,7 @@
       <c r="I433" s="2"/>
       <c r="J433" s="2"/>
     </row>
-    <row r="434" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="434" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="str">
         <f>IF(B434="", "", SUBTOTAL(3, $B$2:B434) * 1)</f>
         <v/>
@@ -17226,7 +17215,7 @@
       <c r="I434" s="2"/>
       <c r="J434" s="2"/>
     </row>
-    <row r="435" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="435" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="str">
         <f>IF(B435="", "", SUBTOTAL(3, $B$2:B435) * 1)</f>
         <v/>
@@ -17241,7 +17230,7 @@
       <c r="I435" s="2"/>
       <c r="J435" s="2"/>
     </row>
-    <row r="436" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="436" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="str">
         <f>IF(B436="", "", SUBTOTAL(3, $B$2:B436) * 1)</f>
         <v/>
@@ -17256,7 +17245,7 @@
       <c r="I436" s="2"/>
       <c r="J436" s="2"/>
     </row>
-    <row r="437" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="437" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="str">
         <f>IF(B437="", "", SUBTOTAL(3, $B$2:B437) * 1)</f>
         <v/>
@@ -17271,7 +17260,7 @@
       <c r="I437" s="2"/>
       <c r="J437" s="2"/>
     </row>
-    <row r="438" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="438" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="str">
         <f>IF(B438="", "", SUBTOTAL(3, $B$2:B438) * 1)</f>
         <v/>
@@ -17286,7 +17275,7 @@
       <c r="I438" s="2"/>
       <c r="J438" s="2"/>
     </row>
-    <row r="439" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="439" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="str">
         <f>IF(B439="", "", SUBTOTAL(3, $B$2:B439) * 1)</f>
         <v/>
@@ -17301,7 +17290,7 @@
       <c r="I439" s="2"/>
       <c r="J439" s="2"/>
     </row>
-    <row r="440" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="440" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="str">
         <f>IF(B440="", "", SUBTOTAL(3, $B$2:B440) * 1)</f>
         <v/>
@@ -17316,7 +17305,7 @@
       <c r="I440" s="2"/>
       <c r="J440" s="2"/>
     </row>
-    <row r="441" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="441" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="str">
         <f>IF(B441="", "", SUBTOTAL(3, $B$2:B441) * 1)</f>
         <v/>
@@ -17331,7 +17320,7 @@
       <c r="I441" s="2"/>
       <c r="J441" s="2"/>
     </row>
-    <row r="442" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="442" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="str">
         <f>IF(B442="", "", SUBTOTAL(3, $B$2:B442) * 1)</f>
         <v/>
@@ -17346,7 +17335,7 @@
       <c r="I442" s="2"/>
       <c r="J442" s="2"/>
     </row>
-    <row r="443" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="443" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="str">
         <f>IF(B443="", "", SUBTOTAL(3, $B$2:B443) * 1)</f>
         <v/>
@@ -17361,7 +17350,7 @@
       <c r="I443" s="2"/>
       <c r="J443" s="2"/>
     </row>
-    <row r="444" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="444" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="str">
         <f>IF(B444="", "", SUBTOTAL(3, $B$2:B444) * 1)</f>
         <v/>
@@ -17376,7 +17365,7 @@
       <c r="I444" s="2"/>
       <c r="J444" s="2"/>
     </row>
-    <row r="445" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="445" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="str">
         <f>IF(B445="", "", SUBTOTAL(3, $B$2:B445) * 1)</f>
         <v/>
@@ -17391,7 +17380,7 @@
       <c r="I445" s="2"/>
       <c r="J445" s="2"/>
     </row>
-    <row r="446" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="446" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="str">
         <f>IF(B446="", "", SUBTOTAL(3, $B$2:B446) * 1)</f>
         <v/>
@@ -17406,7 +17395,7 @@
       <c r="I446" s="2"/>
       <c r="J446" s="2"/>
     </row>
-    <row r="447" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="447" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="str">
         <f>IF(B447="", "", SUBTOTAL(3, $B$2:B447) * 1)</f>
         <v/>
@@ -17421,7 +17410,7 @@
       <c r="I447" s="2"/>
       <c r="J447" s="2"/>
     </row>
-    <row r="448" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="448" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="str">
         <f>IF(B448="", "", SUBTOTAL(3, $B$2:B448) * 1)</f>
         <v/>
@@ -17436,7 +17425,7 @@
       <c r="I448" s="2"/>
       <c r="J448" s="2"/>
     </row>
-    <row r="449" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="449" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="str">
         <f>IF(B449="", "", SUBTOTAL(3, $B$2:B449) * 1)</f>
         <v/>
@@ -17451,7 +17440,7 @@
       <c r="I449" s="2"/>
       <c r="J449" s="2"/>
     </row>
-    <row r="450" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="450" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="str">
         <f>IF(B450="", "", SUBTOTAL(3, $B$2:B450) * 1)</f>
         <v/>
@@ -17466,7 +17455,7 @@
       <c r="I450" s="2"/>
       <c r="J450" s="2"/>
     </row>
-    <row r="451" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="451" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="str">
         <f>IF(B451="", "", SUBTOTAL(3, $B$2:B451) * 1)</f>
         <v/>
@@ -17481,7 +17470,7 @@
       <c r="I451" s="2"/>
       <c r="J451" s="2"/>
     </row>
-    <row r="452" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="452" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="str">
         <f>IF(B452="", "", SUBTOTAL(3, $B$2:B452) * 1)</f>
         <v/>
@@ -17496,7 +17485,7 @@
       <c r="I452" s="2"/>
       <c r="J452" s="2"/>
     </row>
-    <row r="453" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="453" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="str">
         <f>IF(B453="", "", SUBTOTAL(3, $B$2:B453) * 1)</f>
         <v/>
@@ -17511,7 +17500,7 @@
       <c r="I453" s="2"/>
       <c r="J453" s="2"/>
     </row>
-    <row r="454" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="454" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="str">
         <f>IF(B454="", "", SUBTOTAL(3, $B$2:B454) * 1)</f>
         <v/>
@@ -17526,7 +17515,7 @@
       <c r="I454" s="2"/>
       <c r="J454" s="2"/>
     </row>
-    <row r="455" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="455" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="str">
         <f>IF(B455="", "", SUBTOTAL(3, $B$2:B455) * 1)</f>
         <v/>
@@ -17541,7 +17530,7 @@
       <c r="I455" s="2"/>
       <c r="J455" s="2"/>
     </row>
-    <row r="456" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="456" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="str">
         <f>IF(B456="", "", SUBTOTAL(3, $B$2:B456) * 1)</f>
         <v/>
@@ -17556,7 +17545,7 @@
       <c r="I456" s="2"/>
       <c r="J456" s="2"/>
     </row>
-    <row r="457" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="457" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="str">
         <f>IF(B457="", "", SUBTOTAL(3, $B$2:B457) * 1)</f>
         <v/>
@@ -17571,7 +17560,7 @@
       <c r="I457" s="2"/>
       <c r="J457" s="2"/>
     </row>
-    <row r="458" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="458" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="str">
         <f>IF(B458="", "", SUBTOTAL(3, $B$2:B458) * 1)</f>
         <v/>
@@ -17586,7 +17575,7 @@
       <c r="I458" s="2"/>
       <c r="J458" s="2"/>
     </row>
-    <row r="459" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="459" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="str">
         <f>IF(B459="", "", SUBTOTAL(3, $B$2:B459) * 1)</f>
         <v/>
@@ -17601,7 +17590,7 @@
       <c r="I459" s="2"/>
       <c r="J459" s="2"/>
     </row>
-    <row r="460" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="460" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="str">
         <f>IF(B460="", "", SUBTOTAL(3, $B$2:B460) * 1)</f>
         <v/>
@@ -17616,7 +17605,7 @@
       <c r="I460" s="2"/>
       <c r="J460" s="2"/>
     </row>
-    <row r="461" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="461" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="str">
         <f>IF(B461="", "", SUBTOTAL(3, $B$2:B461) * 1)</f>
         <v/>
@@ -17631,7 +17620,7 @@
       <c r="I461" s="2"/>
       <c r="J461" s="2"/>
     </row>
-    <row r="462" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="462" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="str">
         <f>IF(B462="", "", SUBTOTAL(3, $B$2:B462) * 1)</f>
         <v/>
@@ -17646,7 +17635,7 @@
       <c r="I462" s="2"/>
       <c r="J462" s="2"/>
     </row>
-    <row r="463" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="463" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="str">
         <f>IF(B463="", "", SUBTOTAL(3, $B$2:B463) * 1)</f>
         <v/>
@@ -17661,7 +17650,7 @@
       <c r="I463" s="2"/>
       <c r="J463" s="2"/>
     </row>
-    <row r="464" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="464" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="str">
         <f>IF(B464="", "", SUBTOTAL(3, $B$2:B464) * 1)</f>
         <v/>
@@ -17676,7 +17665,7 @@
       <c r="I464" s="2"/>
       <c r="J464" s="2"/>
     </row>
-    <row r="465" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="465" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="str">
         <f>IF(B465="", "", SUBTOTAL(3, $B$2:B465) * 1)</f>
         <v/>
@@ -17691,7 +17680,7 @@
       <c r="I465" s="2"/>
       <c r="J465" s="2"/>
     </row>
-    <row r="466" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="466" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="str">
         <f>IF(B466="", "", SUBTOTAL(3, $B$2:B466) * 1)</f>
         <v/>
@@ -17706,7 +17695,7 @@
       <c r="I466" s="2"/>
       <c r="J466" s="2"/>
     </row>
-    <row r="467" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="467" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="str">
         <f>IF(B467="", "", SUBTOTAL(3, $B$2:B467) * 1)</f>
         <v/>
@@ -17721,7 +17710,7 @@
       <c r="I467" s="2"/>
       <c r="J467" s="2"/>
     </row>
-    <row r="468" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="468" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="str">
         <f>IF(B468="", "", SUBTOTAL(3, $B$2:B468) * 1)</f>
         <v/>
@@ -17736,7 +17725,7 @@
       <c r="I468" s="2"/>
       <c r="J468" s="2"/>
     </row>
-    <row r="469" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="469" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="str">
         <f>IF(B469="", "", SUBTOTAL(3, $B$2:B469) * 1)</f>
         <v/>
@@ -17751,7 +17740,7 @@
       <c r="I469" s="2"/>
       <c r="J469" s="2"/>
     </row>
-    <row r="470" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="470" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="str">
         <f>IF(B470="", "", SUBTOTAL(3, $B$2:B470) * 1)</f>
         <v/>
@@ -17766,7 +17755,7 @@
       <c r="I470" s="2"/>
       <c r="J470" s="2"/>
     </row>
-    <row r="471" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="471" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="str">
         <f>IF(B471="", "", SUBTOTAL(3, $B$2:B471) * 1)</f>
         <v/>
@@ -17781,7 +17770,7 @@
       <c r="I471" s="2"/>
       <c r="J471" s="2"/>
     </row>
-    <row r="472" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="472" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="str">
         <f>IF(B472="", "", SUBTOTAL(3, $B$2:B472) * 1)</f>
         <v/>
@@ -17796,7 +17785,7 @@
       <c r="I472" s="2"/>
       <c r="J472" s="2"/>
     </row>
-    <row r="473" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="473" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="str">
         <f>IF(B473="", "", SUBTOTAL(3, $B$2:B473) * 1)</f>
         <v/>
@@ -17811,7 +17800,7 @@
       <c r="I473" s="2"/>
       <c r="J473" s="2"/>
     </row>
-    <row r="474" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="474" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="str">
         <f>IF(B474="", "", SUBTOTAL(3, $B$2:B474) * 1)</f>
         <v/>
@@ -17826,7 +17815,7 @@
       <c r="I474" s="2"/>
       <c r="J474" s="2"/>
     </row>
-    <row r="475" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="475" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="str">
         <f>IF(B475="", "", SUBTOTAL(3, $B$2:B475) * 1)</f>
         <v/>
@@ -17841,7 +17830,7 @@
       <c r="I475" s="2"/>
       <c r="J475" s="2"/>
     </row>
-    <row r="476" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="476" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="str">
         <f>IF(B476="", "", SUBTOTAL(3, $B$2:B476) * 1)</f>
         <v/>
@@ -17856,7 +17845,7 @@
       <c r="I476" s="2"/>
       <c r="J476" s="2"/>
     </row>
-    <row r="477" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="477" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="str">
         <f>IF(B477="", "", SUBTOTAL(3, $B$2:B477) * 1)</f>
         <v/>
@@ -17871,7 +17860,7 @@
       <c r="I477" s="2"/>
       <c r="J477" s="2"/>
     </row>
-    <row r="478" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="478" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="str">
         <f>IF(B478="", "", SUBTOTAL(3, $B$2:B478) * 1)</f>
         <v/>
@@ -17886,7 +17875,7 @@
       <c r="I478" s="2"/>
       <c r="J478" s="2"/>
     </row>
-    <row r="479" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="479" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="str">
         <f>IF(B479="", "", SUBTOTAL(3, $B$2:B479) * 1)</f>
         <v/>
@@ -17901,7 +17890,7 @@
       <c r="I479" s="2"/>
       <c r="J479" s="2"/>
     </row>
-    <row r="480" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="480" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="str">
         <f>IF(B480="", "", SUBTOTAL(3, $B$2:B480) * 1)</f>
         <v/>
@@ -17916,7 +17905,7 @@
       <c r="I480" s="2"/>
       <c r="J480" s="2"/>
     </row>
-    <row r="481" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="481" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="str">
         <f>IF(B481="", "", SUBTOTAL(3, $B$2:B481) * 1)</f>
         <v/>
@@ -17931,7 +17920,7 @@
       <c r="I481" s="2"/>
       <c r="J481" s="2"/>
     </row>
-    <row r="482" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="482" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="str">
         <f>IF(B482="", "", SUBTOTAL(3, $B$2:B482) * 1)</f>
         <v/>
@@ -17946,7 +17935,7 @@
       <c r="I482" s="2"/>
       <c r="J482" s="2"/>
     </row>
-    <row r="483" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="483" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="str">
         <f>IF(B483="", "", SUBTOTAL(3, $B$2:B483) * 1)</f>
         <v/>
@@ -17961,7 +17950,7 @@
       <c r="I483" s="2"/>
       <c r="J483" s="2"/>
     </row>
-    <row r="484" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="484" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="str">
         <f>IF(B484="", "", SUBTOTAL(3, $B$2:B484) * 1)</f>
         <v/>
@@ -17976,7 +17965,7 @@
       <c r="I484" s="2"/>
       <c r="J484" s="2"/>
     </row>
-    <row r="485" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="485" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="str">
         <f>IF(B485="", "", SUBTOTAL(3, $B$2:B485) * 1)</f>
         <v/>
@@ -17991,7 +17980,7 @@
       <c r="I485" s="2"/>
       <c r="J485" s="2"/>
     </row>
-    <row r="486" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="486" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="str">
         <f>IF(B486="", "", SUBTOTAL(3, $B$2:B486) * 1)</f>
         <v/>
@@ -18006,7 +17995,7 @@
       <c r="I486" s="2"/>
       <c r="J486" s="2"/>
     </row>
-    <row r="487" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="487" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="str">
         <f>IF(B487="", "", SUBTOTAL(3, $B$2:B487) * 1)</f>
         <v/>
@@ -18021,7 +18010,7 @@
       <c r="I487" s="2"/>
       <c r="J487" s="2"/>
     </row>
-    <row r="488" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="488" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="str">
         <f>IF(B488="", "", SUBTOTAL(3, $B$2:B488) * 1)</f>
         <v/>
@@ -18036,7 +18025,7 @@
       <c r="I488" s="2"/>
       <c r="J488" s="2"/>
     </row>
-    <row r="489" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="489" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="str">
         <f>IF(B489="", "", SUBTOTAL(3, $B$2:B489) * 1)</f>
         <v/>
@@ -18051,7 +18040,7 @@
       <c r="I489" s="2"/>
       <c r="J489" s="2"/>
     </row>
-    <row r="490" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="490" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="str">
         <f>IF(B490="", "", SUBTOTAL(3, $B$2:B490) * 1)</f>
         <v/>
@@ -18066,7 +18055,7 @@
       <c r="I490" s="2"/>
       <c r="J490" s="2"/>
     </row>
-    <row r="491" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="491" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="str">
         <f>IF(B491="", "", SUBTOTAL(3, $B$2:B491) * 1)</f>
         <v/>
@@ -18081,7 +18070,7 @@
       <c r="I491" s="2"/>
       <c r="J491" s="2"/>
     </row>
-    <row r="492" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="492" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="str">
         <f>IF(B492="", "", SUBTOTAL(3, $B$2:B492) * 1)</f>
         <v/>
@@ -18096,7 +18085,7 @@
       <c r="I492" s="2"/>
       <c r="J492" s="2"/>
     </row>
-    <row r="493" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="493" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="str">
         <f>IF(B493="", "", SUBTOTAL(3, $B$2:B493) * 1)</f>
         <v/>
@@ -18111,7 +18100,7 @@
       <c r="I493" s="2"/>
       <c r="J493" s="2"/>
     </row>
-    <row r="494" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="494" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="str">
         <f>IF(B494="", "", SUBTOTAL(3, $B$2:B494) * 1)</f>
         <v/>
@@ -18126,7 +18115,7 @@
       <c r="I494" s="2"/>
       <c r="J494" s="2"/>
     </row>
-    <row r="495" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="495" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="str">
         <f>IF(B495="", "", SUBTOTAL(3, $B$2:B495) * 1)</f>
         <v/>
@@ -18141,7 +18130,7 @@
       <c r="I495" s="2"/>
       <c r="J495" s="2"/>
     </row>
-    <row r="496" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="496" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="str">
         <f>IF(B496="", "", SUBTOTAL(3, $B$2:B496) * 1)</f>
         <v/>
@@ -18156,7 +18145,7 @@
       <c r="I496" s="2"/>
       <c r="J496" s="2"/>
     </row>
-    <row r="497" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="497" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="str">
         <f>IF(B497="", "", SUBTOTAL(3, $B$2:B497) * 1)</f>
         <v/>
@@ -18171,7 +18160,7 @@
       <c r="I497" s="2"/>
       <c r="J497" s="2"/>
     </row>
-    <row r="498" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="498" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="str">
         <f>IF(B498="", "", SUBTOTAL(3, $B$2:B498) * 1)</f>
         <v/>
@@ -18186,7 +18175,7 @@
       <c r="I498" s="2"/>
       <c r="J498" s="2"/>
     </row>
-    <row r="499" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="499" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="str">
         <f>IF(B499="", "", SUBTOTAL(3, $B$2:B499) * 1)</f>
         <v/>
@@ -18201,7 +18190,7 @@
       <c r="I499" s="2"/>
       <c r="J499" s="2"/>
     </row>
-    <row r="500" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="500" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="str">
         <f>IF(B500="", "", SUBTOTAL(3, $B$2:B500) * 1)</f>
         <v/>
@@ -18216,7 +18205,7 @@
       <c r="I500" s="2"/>
       <c r="J500" s="2"/>
     </row>
-    <row r="501" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="501" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="str">
         <f>IF(B501="", "", SUBTOTAL(3, $B$2:B501) * 1)</f>
         <v/>
@@ -18231,7 +18220,7 @@
       <c r="I501" s="2"/>
       <c r="J501" s="2"/>
     </row>
-    <row r="502" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="502" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="str">
         <f>IF(B502="", "", SUBTOTAL(3, $B$2:B502) * 1)</f>
         <v/>
@@ -18246,7 +18235,7 @@
       <c r="I502" s="2"/>
       <c r="J502" s="2"/>
     </row>
-    <row r="503" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="503" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="str">
         <f>IF(B503="", "", SUBTOTAL(3, $B$2:B503) * 1)</f>
         <v/>
@@ -18261,7 +18250,7 @@
       <c r="I503" s="2"/>
       <c r="J503" s="2"/>
     </row>
-    <row r="504" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="504" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="str">
         <f>IF(B504="", "", SUBTOTAL(3, $B$2:B504) * 1)</f>
         <v/>
@@ -18276,7 +18265,7 @@
       <c r="I504" s="2"/>
       <c r="J504" s="2"/>
     </row>
-    <row r="505" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="505" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="str">
         <f>IF(B505="", "", SUBTOTAL(3, $B$2:B505) * 1)</f>
         <v/>
@@ -18291,7 +18280,7 @@
       <c r="I505" s="2"/>
       <c r="J505" s="2"/>
     </row>
-    <row r="506" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="506" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="str">
         <f>IF(B506="", "", SUBTOTAL(3, $B$2:B506) * 1)</f>
         <v/>
@@ -18306,7 +18295,7 @@
       <c r="I506" s="2"/>
       <c r="J506" s="2"/>
     </row>
-    <row r="507" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="507" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="str">
         <f>IF(B507="", "", SUBTOTAL(3, $B$2:B507) * 1)</f>
         <v/>
@@ -18321,7 +18310,7 @@
       <c r="I507" s="2"/>
       <c r="J507" s="2"/>
     </row>
-    <row r="508" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="508" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="str">
         <f>IF(B508="", "", SUBTOTAL(3, $B$2:B508) * 1)</f>
         <v/>
@@ -18336,7 +18325,7 @@
       <c r="I508" s="2"/>
       <c r="J508" s="2"/>
     </row>
-    <row r="509" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="509" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="str">
         <f>IF(B509="", "", SUBTOTAL(3, $B$2:B509) * 1)</f>
         <v/>
@@ -18351,7 +18340,7 @@
       <c r="I509" s="2"/>
       <c r="J509" s="2"/>
     </row>
-    <row r="510" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="510" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="str">
         <f>IF(B510="", "", SUBTOTAL(3, $B$2:B510) * 1)</f>
         <v/>
@@ -18366,7 +18355,7 @@
       <c r="I510" s="2"/>
       <c r="J510" s="2"/>
     </row>
-    <row r="511" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="511" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="str">
         <f>IF(B511="", "", SUBTOTAL(3, $B$2:B511) * 1)</f>
         <v/>
@@ -18381,7 +18370,7 @@
       <c r="I511" s="2"/>
       <c r="J511" s="2"/>
     </row>
-    <row r="512" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="512" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="str">
         <f>IF(B512="", "", SUBTOTAL(3, $B$2:B512) * 1)</f>
         <v/>
@@ -18396,7 +18385,7 @@
       <c r="I512" s="2"/>
       <c r="J512" s="2"/>
     </row>
-    <row r="513" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="513" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="str">
         <f>IF(B513="", "", SUBTOTAL(3, $B$2:B513) * 1)</f>
         <v/>
@@ -18411,7 +18400,7 @@
       <c r="I513" s="2"/>
       <c r="J513" s="2"/>
     </row>
-    <row r="514" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="514" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="str">
         <f>IF(B514="", "", SUBTOTAL(3, $B$2:B514) * 1)</f>
         <v/>
@@ -18426,7 +18415,7 @@
       <c r="I514" s="2"/>
       <c r="J514" s="2"/>
     </row>
-    <row r="515" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="515" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="str">
         <f>IF(B515="", "", SUBTOTAL(3, $B$2:B515) * 1)</f>
         <v/>
@@ -18441,7 +18430,7 @@
       <c r="I515" s="2"/>
       <c r="J515" s="2"/>
     </row>
-    <row r="516" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="516" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="str">
         <f>IF(B516="", "", SUBTOTAL(3, $B$2:B516) * 1)</f>
         <v/>
@@ -18456,7 +18445,7 @@
       <c r="I516" s="2"/>
       <c r="J516" s="2"/>
     </row>
-    <row r="517" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="517" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="str">
         <f>IF(B517="", "", SUBTOTAL(3, $B$2:B517) * 1)</f>
         <v/>
@@ -18471,7 +18460,7 @@
       <c r="I517" s="2"/>
       <c r="J517" s="2"/>
     </row>
-    <row r="518" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="518" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="str">
         <f>IF(B518="", "", SUBTOTAL(3, $B$2:B518) * 1)</f>
         <v/>
@@ -18486,7 +18475,7 @@
       <c r="I518" s="2"/>
       <c r="J518" s="2"/>
     </row>
-    <row r="519" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="519" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="str">
         <f>IF(B519="", "", SUBTOTAL(3, $B$2:B519) * 1)</f>
         <v/>
@@ -18501,7 +18490,7 @@
       <c r="I519" s="2"/>
       <c r="J519" s="2"/>
     </row>
-    <row r="520" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="520" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="str">
         <f>IF(B520="", "", SUBTOTAL(3, $B$2:B520) * 1)</f>
         <v/>
@@ -18516,7 +18505,7 @@
       <c r="I520" s="2"/>
       <c r="J520" s="2"/>
     </row>
-    <row r="521" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="521" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="str">
         <f>IF(B521="", "", SUBTOTAL(3, $B$2:B521) * 1)</f>
         <v/>
@@ -18531,7 +18520,7 @@
       <c r="I521" s="2"/>
       <c r="J521" s="2"/>
     </row>
-    <row r="522" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="522" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="str">
         <f>IF(B522="", "", SUBTOTAL(3, $B$2:B522) * 1)</f>
         <v/>
@@ -18546,7 +18535,7 @@
       <c r="I522" s="2"/>
       <c r="J522" s="2"/>
     </row>
-    <row r="523" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="523" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="str">
         <f>IF(B523="", "", SUBTOTAL(3, $B$2:B523) * 1)</f>
         <v/>
@@ -18561,7 +18550,7 @@
       <c r="I523" s="2"/>
       <c r="J523" s="2"/>
     </row>
-    <row r="524" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="524" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="str">
         <f>IF(B524="", "", SUBTOTAL(3, $B$2:B524) * 1)</f>
         <v/>
@@ -18576,7 +18565,7 @@
       <c r="I524" s="2"/>
       <c r="J524" s="2"/>
     </row>
-    <row r="525" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="525" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="str">
         <f>IF(B525="", "", SUBTOTAL(3, $B$2:B525) * 1)</f>
         <v/>
@@ -18591,7 +18580,7 @@
       <c r="I525" s="2"/>
       <c r="J525" s="2"/>
     </row>
-    <row r="526" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="526" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="str">
         <f>IF(B526="", "", SUBTOTAL(3, $B$2:B526) * 1)</f>
         <v/>
@@ -18606,7 +18595,7 @@
       <c r="I526" s="2"/>
       <c r="J526" s="2"/>
     </row>
-    <row r="527" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="527" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="str">
         <f>IF(B527="", "", SUBTOTAL(3, $B$2:B527) * 1)</f>
         <v/>
@@ -18621,7 +18610,7 @@
       <c r="I527" s="2"/>
       <c r="J527" s="2"/>
     </row>
-    <row r="528" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="528" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="str">
         <f>IF(B528="", "", SUBTOTAL(3, $B$2:B528) * 1)</f>
         <v/>
@@ -18636,7 +18625,7 @@
       <c r="I528" s="2"/>
       <c r="J528" s="2"/>
     </row>
-    <row r="529" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="529" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="str">
         <f>IF(B529="", "", SUBTOTAL(3, $B$2:B529) * 1)</f>
         <v/>
@@ -18651,7 +18640,7 @@
       <c r="I529" s="2"/>
       <c r="J529" s="2"/>
     </row>
-    <row r="530" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="530" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="str">
         <f>IF(B530="", "", SUBTOTAL(3, $B$2:B530) * 1)</f>
         <v/>
@@ -18666,7 +18655,7 @@
       <c r="I530" s="2"/>
       <c r="J530" s="2"/>
     </row>
-    <row r="531" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="531" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="str">
         <f>IF(B531="", "", SUBTOTAL(3, $B$2:B531) * 1)</f>
         <v/>
@@ -18681,7 +18670,7 @@
       <c r="I531" s="2"/>
       <c r="J531" s="2"/>
     </row>
-    <row r="532" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="532" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="str">
         <f>IF(B532="", "", SUBTOTAL(3, $B$2:B532) * 1)</f>
         <v/>
@@ -18696,7 +18685,7 @@
       <c r="I532" s="2"/>
       <c r="J532" s="2"/>
     </row>
-    <row r="533" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="533" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="str">
         <f>IF(B533="", "", SUBTOTAL(3, $B$2:B533) * 1)</f>
         <v/>
@@ -18711,7 +18700,7 @@
       <c r="I533" s="2"/>
       <c r="J533" s="2"/>
     </row>
-    <row r="534" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="534" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="str">
         <f>IF(B534="", "", SUBTOTAL(3, $B$2:B534) * 1)</f>
         <v/>
@@ -18726,7 +18715,7 @@
       <c r="I534" s="2"/>
       <c r="J534" s="2"/>
     </row>
-    <row r="535" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="535" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="str">
         <f>IF(B535="", "", SUBTOTAL(3, $B$2:B535) * 1)</f>
         <v/>
@@ -18741,7 +18730,7 @@
       <c r="I535" s="2"/>
       <c r="J535" s="2"/>
     </row>
-    <row r="536" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="536" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="str">
         <f>IF(B536="", "", SUBTOTAL(3, $B$2:B536) * 1)</f>
         <v/>
@@ -18756,7 +18745,7 @@
       <c r="I536" s="2"/>
       <c r="J536" s="2"/>
     </row>
-    <row r="537" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="537" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="str">
         <f>IF(B537="", "", SUBTOTAL(3, $B$2:B537) * 1)</f>
         <v/>
@@ -18771,7 +18760,7 @@
       <c r="I537" s="2"/>
       <c r="J537" s="2"/>
     </row>
-    <row r="538" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="538" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="str">
         <f>IF(B538="", "", SUBTOTAL(3, $B$2:B538) * 1)</f>
         <v/>
@@ -18786,7 +18775,7 @@
       <c r="I538" s="2"/>
       <c r="J538" s="2"/>
     </row>
-    <row r="539" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="539" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="str">
         <f>IF(B539="", "", SUBTOTAL(3, $B$2:B539) * 1)</f>
         <v/>
@@ -18801,7 +18790,7 @@
       <c r="I539" s="2"/>
       <c r="J539" s="2"/>
     </row>
-    <row r="540" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="540" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="str">
         <f>IF(B540="", "", SUBTOTAL(3, $B$2:B540) * 1)</f>
         <v/>
@@ -18816,7 +18805,7 @@
       <c r="I540" s="2"/>
       <c r="J540" s="2"/>
     </row>
-    <row r="541" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="541" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="str">
         <f>IF(B541="", "", SUBTOTAL(3, $B$2:B541) * 1)</f>
         <v/>
@@ -18831,7 +18820,7 @@
       <c r="I541" s="2"/>
       <c r="J541" s="2"/>
     </row>
-    <row r="542" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="542" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="str">
         <f>IF(B542="", "", SUBTOTAL(3, $B$2:B542) * 1)</f>
         <v/>
@@ -18846,7 +18835,7 @@
       <c r="I542" s="2"/>
       <c r="J542" s="2"/>
     </row>
-    <row r="543" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="543" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="str">
         <f>IF(B543="", "", SUBTOTAL(3, $B$2:B543) * 1)</f>
         <v/>
@@ -18861,7 +18850,7 @@
       <c r="I543" s="2"/>
       <c r="J543" s="2"/>
     </row>
-    <row r="544" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="544" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="str">
         <f>IF(B544="", "", SUBTOTAL(3, $B$2:B544) * 1)</f>
         <v/>
@@ -18876,7 +18865,7 @@
       <c r="I544" s="2"/>
       <c r="J544" s="2"/>
     </row>
-    <row r="545" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="545" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="str">
         <f>IF(B545="", "", SUBTOTAL(3, $B$2:B545) * 1)</f>
         <v/>
@@ -18891,7 +18880,7 @@
       <c r="I545" s="2"/>
       <c r="J545" s="2"/>
     </row>
-    <row r="546" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="546" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="str">
         <f>IF(B546="", "", SUBTOTAL(3, $B$2:B546) * 1)</f>
         <v/>
@@ -18906,7 +18895,7 @@
       <c r="I546" s="2"/>
       <c r="J546" s="2"/>
     </row>
-    <row r="547" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="547" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="str">
         <f>IF(B547="", "", SUBTOTAL(3, $B$2:B547) * 1)</f>
         <v/>
@@ -18921,7 +18910,7 @@
       <c r="I547" s="2"/>
       <c r="J547" s="2"/>
     </row>
-    <row r="548" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="548" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="str">
         <f>IF(B548="", "", SUBTOTAL(3, $B$2:B548) * 1)</f>
         <v/>
@@ -18936,7 +18925,7 @@
       <c r="I548" s="2"/>
       <c r="J548" s="2"/>
     </row>
-    <row r="549" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="549" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="str">
         <f>IF(B549="", "", SUBTOTAL(3, $B$2:B549) * 1)</f>
         <v/>
@@ -18951,7 +18940,7 @@
       <c r="I549" s="2"/>
       <c r="J549" s="2"/>
     </row>
-    <row r="550" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="550" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="str">
         <f>IF(B550="", "", SUBTOTAL(3, $B$2:B550) * 1)</f>
         <v/>
@@ -18966,7 +18955,7 @@
       <c r="I550" s="2"/>
       <c r="J550" s="2"/>
     </row>
-    <row r="551" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="551" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="str">
         <f>IF(B551="", "", SUBTOTAL(3, $B$2:B551) * 1)</f>
         <v/>
@@ -18981,7 +18970,7 @@
       <c r="I551" s="2"/>
       <c r="J551" s="2"/>
     </row>
-    <row r="552" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="552" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="str">
         <f>IF(B552="", "", SUBTOTAL(3, $B$2:B552) * 1)</f>
         <v/>
@@ -18996,7 +18985,7 @@
       <c r="I552" s="2"/>
       <c r="J552" s="2"/>
     </row>
-    <row r="553" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="553" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="str">
         <f>IF(B553="", "", SUBTOTAL(3, $B$2:B553) * 1)</f>
         <v/>
@@ -19011,7 +19000,7 @@
       <c r="I553" s="2"/>
       <c r="J553" s="2"/>
     </row>
-    <row r="554" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="554" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="str">
         <f>IF(B554="", "", SUBTOTAL(3, $B$2:B554) * 1)</f>
         <v/>
@@ -19026,7 +19015,7 @@
       <c r="I554" s="2"/>
       <c r="J554" s="2"/>
     </row>
-    <row r="555" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="555" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="str">
         <f>IF(B555="", "", SUBTOTAL(3, $B$2:B555) * 1)</f>
         <v/>
@@ -19041,7 +19030,7 @@
       <c r="I555" s="2"/>
       <c r="J555" s="2"/>
     </row>
-    <row r="556" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="556" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="str">
         <f>IF(B556="", "", SUBTOTAL(3, $B$2:B556) * 1)</f>
         <v/>
@@ -19056,7 +19045,7 @@
       <c r="I556" s="2"/>
       <c r="J556" s="2"/>
     </row>
-    <row r="557" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="557" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="str">
         <f>IF(B557="", "", SUBTOTAL(3, $B$2:B557) * 1)</f>
         <v/>
@@ -19071,7 +19060,7 @@
       <c r="I557" s="2"/>
       <c r="J557" s="2"/>
     </row>
-    <row r="558" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="558" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="str">
         <f>IF(B558="", "", SUBTOTAL(3, $B$2:B558) * 1)</f>
         <v/>
@@ -19086,7 +19075,7 @@
       <c r="I558" s="2"/>
       <c r="J558" s="2"/>
     </row>
-    <row r="559" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="559" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="str">
         <f>IF(B559="", "", SUBTOTAL(3, $B$2:B559) * 1)</f>
         <v/>
@@ -19101,7 +19090,7 @@
       <c r="I559" s="2"/>
       <c r="J559" s="2"/>
     </row>
-    <row r="560" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="560" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="str">
         <f>IF(B560="", "", SUBTOTAL(3, $B$2:B560) * 1)</f>
         <v/>
@@ -19116,7 +19105,7 @@
       <c r="I560" s="2"/>
       <c r="J560" s="2"/>
     </row>
-    <row r="561" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="561" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="str">
         <f>IF(B561="", "", SUBTOTAL(3, $B$2:B561) * 1)</f>
         <v/>
@@ -19131,7 +19120,7 @@
       <c r="I561" s="2"/>
       <c r="J561" s="2"/>
     </row>
-    <row r="562" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="562" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="str">
         <f>IF(B562="", "", SUBTOTAL(3, $B$2:B562) * 1)</f>
         <v/>
@@ -19146,7 +19135,7 @@
       <c r="I562" s="2"/>
       <c r="J562" s="2"/>
     </row>
-    <row r="563" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="563" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="str">
         <f>IF(B563="", "", SUBTOTAL(3, $B$2:B563) * 1)</f>
         <v/>
@@ -19161,7 +19150,7 @@
       <c r="I563" s="2"/>
       <c r="J563" s="2"/>
     </row>
-    <row r="564" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="564" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="str">
         <f>IF(B564="", "", SUBTOTAL(3, $B$2:B564) * 1)</f>
         <v/>
@@ -19176,7 +19165,7 @@
       <c r="I564" s="2"/>
       <c r="J564" s="2"/>
     </row>
-    <row r="565" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="565" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="str">
         <f>IF(B565="", "", SUBTOTAL(3, $B$2:B565) * 1)</f>
         <v/>
@@ -19191,7 +19180,7 @@
       <c r="I565" s="2"/>
       <c r="J565" s="2"/>
     </row>
-    <row r="566" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="566" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="str">
         <f>IF(B566="", "", SUBTOTAL(3, $B$2:B566) * 1)</f>
         <v/>
@@ -19206,7 +19195,7 @@
       <c r="I566" s="2"/>
       <c r="J566" s="2"/>
     </row>
-    <row r="567" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="567" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="str">
         <f>IF(B567="", "", SUBTOTAL(3, $B$2:B567) * 1)</f>
         <v/>
@@ -19221,7 +19210,7 @@
       <c r="I567" s="2"/>
       <c r="J567" s="2"/>
     </row>
-    <row r="568" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="568" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="str">
         <f>IF(B568="", "", SUBTOTAL(3, $B$2:B568) * 1)</f>
         <v/>
@@ -19236,7 +19225,7 @@
       <c r="I568" s="2"/>
       <c r="J568" s="2"/>
     </row>
-    <row r="569" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="569" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="str">
         <f>IF(B569="", "", SUBTOTAL(3, $B$2:B569) * 1)</f>
         <v/>
@@ -19251,7 +19240,7 @@
       <c r="I569" s="2"/>
       <c r="J569" s="2"/>
     </row>
-    <row r="570" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="570" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="str">
         <f>IF(B570="", "", SUBTOTAL(3, $B$2:B570) * 1)</f>
         <v/>
@@ -19266,7 +19255,7 @@
       <c r="I570" s="2"/>
       <c r="J570" s="2"/>
     </row>
-    <row r="571" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="571" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="str">
         <f>IF(B571="", "", SUBTOTAL(3, $B$2:B571) * 1)</f>
         <v/>
@@ -19281,7 +19270,7 @@
       <c r="I571" s="2"/>
       <c r="J571" s="2"/>
     </row>
-    <row r="572" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="572" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="str">
         <f>IF(B572="", "", SUBTOTAL(3, $B$2:B572) * 1)</f>
         <v/>
@@ -19296,7 +19285,7 @@
       <c r="I572" s="2"/>
       <c r="J572" s="2"/>
     </row>
-    <row r="573" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="573" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="str">
         <f>IF(B573="", "", SUBTOTAL(3, $B$2:B573) * 1)</f>
         <v/>
@@ -19311,7 +19300,7 @@
       <c r="I573" s="2"/>
       <c r="J573" s="2"/>
     </row>
-    <row r="574" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="574" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="str">
         <f>IF(B574="", "", SUBTOTAL(3, $B$2:B574) * 1)</f>
         <v/>
@@ -19326,7 +19315,7 @@
       <c r="I574" s="2"/>
       <c r="J574" s="2"/>
     </row>
-    <row r="575" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="575" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="str">
         <f>IF(B575="", "", SUBTOTAL(3, $B$2:B575) * 1)</f>
         <v/>
@@ -19341,7 +19330,7 @@
       <c r="I575" s="2"/>
       <c r="J575" s="2"/>
     </row>
-    <row r="576" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="576" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="str">
         <f>IF(B576="", "", SUBTOTAL(3, $B$2:B576) * 1)</f>
         <v/>
@@ -19356,7 +19345,7 @@
       <c r="I576" s="2"/>
       <c r="J576" s="2"/>
     </row>
-    <row r="577" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="577" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="str">
         <f>IF(B577="", "", SUBTOTAL(3, $B$2:B577) * 1)</f>
         <v/>
@@ -19371,7 +19360,7 @@
       <c r="I577" s="2"/>
       <c r="J577" s="2"/>
     </row>
-    <row r="578" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="578" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="str">
         <f>IF(B578="", "", SUBTOTAL(3, $B$2:B578) * 1)</f>
         <v/>
@@ -19386,7 +19375,7 @@
       <c r="I578" s="2"/>
       <c r="J578" s="2"/>
     </row>
-    <row r="579" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="579" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="str">
         <f>IF(B579="", "", SUBTOTAL(3, $B$2:B579) * 1)</f>
         <v/>
@@ -19401,7 +19390,7 @@
       <c r="I579" s="2"/>
       <c r="J579" s="2"/>
     </row>
-    <row r="580" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="580" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="str">
         <f>IF(B580="", "", SUBTOTAL(3, $B$2:B580) * 1)</f>
         <v/>
@@ -19416,7 +19405,7 @@
       <c r="I580" s="2"/>
       <c r="J580" s="2"/>
     </row>
-    <row r="581" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="581" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="str">
         <f>IF(B581="", "", SUBTOTAL(3, $B$2:B581) * 1)</f>
         <v/>
@@ -19431,7 +19420,7 @@
       <c r="I581" s="2"/>
       <c r="J581" s="2"/>
     </row>
-    <row r="582" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="582" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="str">
         <f>IF(B582="", "", SUBTOTAL(3, $B$2:B582) * 1)</f>
         <v/>
@@ -19446,7 +19435,7 @@
       <c r="I582" s="2"/>
       <c r="J582" s="2"/>
     </row>
-    <row r="583" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="583" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="str">
         <f>IF(B583="", "", SUBTOTAL(3, $B$2:B583) * 1)</f>
         <v/>
@@ -19461,7 +19450,7 @@
       <c r="I583" s="2"/>
       <c r="J583" s="2"/>
     </row>
-    <row r="584" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="584" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="str">
         <f>IF(B584="", "", SUBTOTAL(3, $B$2:B584) * 1)</f>
         <v/>
@@ -19476,7 +19465,7 @@
       <c r="I584" s="2"/>
       <c r="J584" s="2"/>
     </row>
-    <row r="585" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="585" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="str">
         <f>IF(B585="", "", SUBTOTAL(3, $B$2:B585) * 1)</f>
         <v/>
@@ -19491,7 +19480,7 @@
       <c r="I585" s="2"/>
       <c r="J585" s="2"/>
     </row>
-    <row r="586" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="586" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="str">
         <f>IF(B586="", "", SUBTOTAL(3, $B$2:B586) * 1)</f>
         <v/>
@@ -19506,7 +19495,7 @@
       <c r="I586" s="2"/>
       <c r="J586" s="2"/>
     </row>
-    <row r="587" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="587" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="str">
         <f>IF(B587="", "", SUBTOTAL(3, $B$2:B587) * 1)</f>
         <v/>
@@ -19521,7 +19510,7 @@
       <c r="I587" s="2"/>
       <c r="J587" s="2"/>
     </row>
-    <row r="588" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="588" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="str">
         <f>IF(B588="", "", SUBTOTAL(3, $B$2:B588) * 1)</f>
         <v/>
@@ -19536,7 +19525,7 @@
       <c r="I588" s="2"/>
       <c r="J588" s="2"/>
     </row>
-    <row r="589" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="589" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="str">
         <f>IF(B589="", "", SUBTOTAL(3, $B$2:B589) * 1)</f>
         <v/>
@@ -19551,7 +19540,7 @@
       <c r="I589" s="2"/>
       <c r="J589" s="2"/>
     </row>
-    <row r="590" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="590" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="str">
         <f>IF(B590="", "", SUBTOTAL(3, $B$2:B590) * 1)</f>
         <v/>
@@ -19566,7 +19555,7 @@
       <c r="I590" s="2"/>
       <c r="J590" s="2"/>
     </row>
-    <row r="591" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="591" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="str">
         <f>IF(B591="", "", SUBTOTAL(3, $B$2:B591) * 1)</f>
         <v/>
@@ -19581,7 +19570,7 @@
       <c r="I591" s="2"/>
       <c r="J591" s="2"/>
     </row>
-    <row r="592" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="592" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="str">
         <f>IF(B592="", "", SUBTOTAL(3, $B$2:B592) * 1)</f>
         <v/>
@@ -19596,7 +19585,7 @@
       <c r="I592" s="2"/>
       <c r="J592" s="2"/>
     </row>
-    <row r="593" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="593" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="str">
         <f>IF(B593="", "", SUBTOTAL(3, $B$2:B593) * 1)</f>
         <v/>
@@ -19611,7 +19600,7 @@
       <c r="I593" s="2"/>
       <c r="J593" s="2"/>
     </row>
-    <row r="594" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="594" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="str">
         <f>IF(B594="", "", SUBTOTAL(3, $B$2:B594) * 1)</f>
         <v/>
@@ -19626,7 +19615,7 @@
       <c r="I594" s="2"/>
       <c r="J594" s="2"/>
     </row>
-    <row r="595" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="595" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="str">
         <f>IF(B595="", "", SUBTOTAL(3, $B$2:B595) * 1)</f>
         <v/>
@@ -19641,7 +19630,7 @@
       <c r="I595" s="2"/>
       <c r="J595" s="2"/>
     </row>
-    <row r="596" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="596" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="str">
         <f>IF(B596="", "", SUBTOTAL(3, $B$2:B596) * 1)</f>
         <v/>
@@ -19656,7 +19645,7 @@
       <c r="I596" s="2"/>
       <c r="J596" s="2"/>
     </row>
-    <row r="597" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="597" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="str">
         <f>IF(B597="", "", SUBTOTAL(3, $B$2:B597) * 1)</f>
         <v/>
@@ -19671,7 +19660,7 @@
       <c r="I597" s="2"/>
       <c r="J597" s="2"/>
     </row>
-    <row r="598" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="598" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="str">
         <f>IF(B598="", "", SUBTOTAL(3, $B$2:B598) * 1)</f>
         <v/>
@@ -19686,7 +19675,7 @@
       <c r="I598" s="2"/>
       <c r="J598" s="2"/>
     </row>
-    <row r="599" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="599" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="str">
         <f>IF(B599="", "", SUBTOTAL(3, $B$2:B599) * 1)</f>
         <v/>
@@ -19701,7 +19690,7 @@
       <c r="I599" s="2"/>
       <c r="J599" s="2"/>
     </row>
-    <row r="600" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="600" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="str">
         <f>IF(B600="", "", SUBTOTAL(3, $B$2:B600) * 1)</f>
         <v/>
@@ -19716,7 +19705,7 @@
       <c r="I600" s="2"/>
       <c r="J600" s="2"/>
     </row>
-    <row r="601" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="601" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="str">
         <f>IF(B601="", "", SUBTOTAL(3, $B$2:B601) * 1)</f>
         <v/>
@@ -19731,7 +19720,7 @@
       <c r="I601" s="2"/>
       <c r="J601" s="2"/>
     </row>
-    <row r="602" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="602" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="str">
         <f>IF(B602="", "", SUBTOTAL(3, $B$2:B602) * 1)</f>
         <v/>
@@ -19746,7 +19735,7 @@
       <c r="I602" s="2"/>
       <c r="J602" s="2"/>
     </row>
-    <row r="603" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="603" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="str">
         <f>IF(B603="", "", SUBTOTAL(3, $B$2:B603) * 1)</f>
         <v/>
@@ -19761,7 +19750,7 @@
       <c r="I603" s="2"/>
       <c r="J603" s="2"/>
     </row>
-    <row r="604" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="604" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="str">
         <f>IF(B604="", "", SUBTOTAL(3, $B$2:B604) * 1)</f>
         <v/>
@@ -19776,7 +19765,7 @@
       <c r="I604" s="2"/>
       <c r="J604" s="2"/>
     </row>
-    <row r="605" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="605" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="str">
         <f>IF(B605="", "", SUBTOTAL(3, $B$2:B605) * 1)</f>
         <v/>
@@ -19791,7 +19780,7 @@
       <c r="I605" s="2"/>
       <c r="J605" s="2"/>
     </row>
-    <row r="606" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="606" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="str">
         <f>IF(B606="", "", SUBTOTAL(3, $B$2:B606) * 1)</f>
         <v/>
@@ -19806,7 +19795,7 @@
       <c r="I606" s="2"/>
       <c r="J606" s="2"/>
     </row>
-    <row r="607" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="607" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="str">
         <f>IF(B607="", "", SUBTOTAL(3, $B$2:B607) * 1)</f>
         <v/>
@@ -19821,7 +19810,7 @@
       <c r="I607" s="2"/>
       <c r="J607" s="2"/>
     </row>
-    <row r="608" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="608" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="str">
         <f>IF(B608="", "", SUBTOTAL(3, $B$2:B608) * 1)</f>
         <v/>
@@ -19836,7 +19825,7 @@
       <c r="I608" s="2"/>
       <c r="J608" s="2"/>
     </row>
-    <row r="609" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="609" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="str">
         <f>IF(B609="", "", SUBTOTAL(3, $B$2:B609) * 1)</f>
         <v/>
@@ -19851,7 +19840,7 @@
       <c r="I609" s="2"/>
       <c r="J609" s="2"/>
     </row>
-    <row r="610" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="610" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="str">
         <f>IF(B610="", "", SUBTOTAL(3, $B$2:B610) * 1)</f>
         <v/>
@@ -19866,7 +19855,7 @@
       <c r="I610" s="2"/>
       <c r="J610" s="2"/>
     </row>
-    <row r="611" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="611" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="str">
         <f>IF(B611="", "", SUBTOTAL(3, $B$2:B611) * 1)</f>
         <v/>
@@ -19881,7 +19870,7 @@
       <c r="I611" s="2"/>
       <c r="J611" s="2"/>
     </row>
-    <row r="612" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="612" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="str">
         <f>IF(B612="", "", SUBTOTAL(3, $B$2:B612) * 1)</f>
         <v/>
@@ -19896,7 +19885,7 @@
       <c r="I612" s="2"/>
       <c r="J612" s="2"/>
     </row>
-    <row r="613" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="613" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="str">
         <f>IF(B613="", "", SUBTOTAL(3, $B$2:B613) * 1)</f>
         <v/>
@@ -19911,7 +19900,7 @@
       <c r="I613" s="2"/>
       <c r="J613" s="2"/>
     </row>
-    <row r="614" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="614" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="str">
         <f>IF(B614="", "", SUBTOTAL(3, $B$2:B614) * 1)</f>
         <v/>
@@ -19926,7 +19915,7 @@
       <c r="I614" s="2"/>
       <c r="J614" s="2"/>
     </row>
-    <row r="615" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="615" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="str">
         <f>IF(B615="", "", SUBTOTAL(3, $B$2:B615) * 1)</f>
         <v/>
@@ -19941,7 +19930,7 @@
       <c r="I615" s="2"/>
       <c r="J615" s="2"/>
     </row>
-    <row r="616" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="616" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="str">
         <f>IF(B616="", "", SUBTOTAL(3, $B$2:B616) * 1)</f>
         <v/>
@@ -19956,7 +19945,7 @@
       <c r="I616" s="2"/>
       <c r="J616" s="2"/>
     </row>
-    <row r="617" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="617" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="str">
         <f>IF(B617="", "", SUBTOTAL(3, $B$2:B617) * 1)</f>
         <v/>
@@ -19971,7 +19960,7 @@
       <c r="I617" s="2"/>
       <c r="J617" s="2"/>
     </row>
-    <row r="618" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="618" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="str">
         <f>IF(B618="", "", SUBTOTAL(3, $B$2:B618) * 1)</f>
         <v/>
@@ -19986,7 +19975,7 @@
       <c r="I618" s="2"/>
       <c r="J618" s="2"/>
     </row>
-    <row r="619" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="619" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="str">
         <f>IF(B619="", "", SUBTOTAL(3, $B$2:B619) * 1)</f>
         <v/>
@@ -20001,7 +19990,7 @@
       <c r="I619" s="2"/>
       <c r="J619" s="2"/>
     </row>
-    <row r="620" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="620" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="str">
         <f>IF(B620="", "", SUBTOTAL(3, $B$2:B620) * 1)</f>
         <v/>
@@ -20016,7 +20005,7 @@
       <c r="I620" s="2"/>
       <c r="J620" s="2"/>
     </row>
-    <row r="621" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="621" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="str">
         <f>IF(B621="", "", SUBTOTAL(3, $B$2:B621) * 1)</f>
         <v/>
@@ -20031,7 +20020,7 @@
       <c r="I621" s="2"/>
       <c r="J621" s="2"/>
     </row>
-    <row r="622" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="622" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="str">
         <f>IF(B622="", "", SUBTOTAL(3, $B$2:B622) * 1)</f>
         <v/>
@@ -20046,7 +20035,7 @@
       <c r="I622" s="2"/>
       <c r="J622" s="2"/>
     </row>
-    <row r="623" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="623" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="str">
         <f>IF(B623="", "", SUBTOTAL(3, $B$2:B623) * 1)</f>
         <v/>
@@ -20061,7 +20050,7 @@
       <c r="I623" s="2"/>
       <c r="J623" s="2"/>
     </row>
-    <row r="624" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="624" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="str">
         <f>IF(B624="", "", SUBTOTAL(3, $B$2:B624) * 1)</f>
         <v/>
@@ -20076,7 +20065,7 @@
       <c r="I624" s="2"/>
       <c r="J624" s="2"/>
     </row>
-    <row r="625" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="625" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="str">
         <f>IF(B625="", "", SUBTOTAL(3, $B$2:B625) * 1)</f>
         <v/>
@@ -20091,7 +20080,7 @@
       <c r="I625" s="2"/>
       <c r="J625" s="2"/>
     </row>
-    <row r="626" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="626" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="str">
         <f>IF(B626="", "", SUBTOTAL(3, $B$2:B626) * 1)</f>
         <v/>
@@ -20106,7 +20095,7 @@
       <c r="I626" s="2"/>
       <c r="J626" s="2"/>
     </row>
-    <row r="627" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="627" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="str">
         <f>IF(B627="", "", SUBTOTAL(3, $B$2:B627) * 1)</f>
         <v/>
@@ -20121,7 +20110,7 @@
       <c r="I627" s="2"/>
       <c r="J627" s="2"/>
     </row>
-    <row r="628" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="628" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="str">
         <f>IF(B628="", "", SUBTOTAL(3, $B$2:B628) * 1)</f>
         <v/>
@@ -20136,7 +20125,7 @@
       <c r="I628" s="2"/>
       <c r="J628" s="2"/>
     </row>
-    <row r="629" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="629" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="str">
         <f>IF(B629="", "", SUBTOTAL(3, $B$2:B629) * 1)</f>
         <v/>
@@ -20151,7 +20140,7 @@
       <c r="I629" s="2"/>
       <c r="J629" s="2"/>
     </row>
-    <row r="630" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="630" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="str">
         <f>IF(B630="", "", SUBTOTAL(3, $B$2:B630) * 1)</f>
         <v/>
@@ -20166,7 +20155,7 @@
       <c r="I630" s="2"/>
       <c r="J630" s="2"/>
     </row>
-    <row r="631" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="631" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="str">
         <f>IF(B631="", "", SUBTOTAL(3, $B$2:B631) * 1)</f>
         <v/>
@@ -20181,7 +20170,7 @@
       <c r="I631" s="2"/>
       <c r="J631" s="2"/>
     </row>
-    <row r="632" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="632" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="str">
         <f>IF(B632="", "", SUBTOTAL(3, $B$2:B632) * 1)</f>
         <v/>
@@ -20196,7 +20185,7 @@
       <c r="I632" s="2"/>
       <c r="J632" s="2"/>
     </row>
-    <row r="633" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="633" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="str">
         <f>IF(B633="", "", SUBTOTAL(3, $B$2:B633) * 1)</f>
         <v/>
@@ -20211,7 +20200,7 @@
       <c r="I633" s="2"/>
       <c r="J633" s="2"/>
     </row>
-    <row r="634" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="634" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="str">
         <f>IF(B634="", "", SUBTOTAL(3, $B$2:B634) * 1)</f>
         <v/>
@@ -20226,7 +20215,7 @@
       <c r="I634" s="2"/>
       <c r="J634" s="2"/>
     </row>
-    <row r="635" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="635" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="str">
         <f>IF(B635="", "", SUBTOTAL(3, $B$2:B635) * 1)</f>
         <v/>
@@ -20241,7 +20230,7 @@
       <c r="I635" s="2"/>
       <c r="J635" s="2"/>
     </row>
-    <row r="636" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="636" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="str">
         <f>IF(B636="", "", SUBTOTAL(3, $B$2:B636) * 1)</f>
         <v/>
@@ -20256,7 +20245,7 @@
       <c r="I636" s="2"/>
       <c r="J636" s="2"/>
     </row>
-    <row r="637" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="637" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="str">
         <f>IF(B637="", "", SUBTOTAL(3, $B$2:B637) * 1)</f>
         <v/>
@@ -20271,7 +20260,7 @@
       <c r="I637" s="2"/>
       <c r="J637" s="2"/>
     </row>
-    <row r="638" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="638" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="str">
         <f>IF(B638="", "", SUBTOTAL(3, $B$2:B638) * 1)</f>
         <v/>
@@ -20286,7 +20275,7 @@
       <c r="I638" s="2"/>
       <c r="J638" s="2"/>
     </row>
-    <row r="639" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="639" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="str">
         <f>IF(B639="", "", SUBTOTAL(3, $B$2:B639) * 1)</f>
         <v/>
@@ -20301,7 +20290,7 @@
       <c r="I639" s="2"/>
       <c r="J639" s="2"/>
     </row>
-    <row r="640" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="640" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="str">
         <f>IF(B640="", "", SUBTOTAL(3, $B$2:B640) * 1)</f>
         <v/>
@@ -20316,7 +20305,7 @@
       <c r="I640" s="2"/>
       <c r="J640" s="2"/>
     </row>
-    <row r="641" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="641" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="str">
         <f>IF(B641="", "", SUBTOTAL(3, $B$2:B641) * 1)</f>
         <v/>
@@ -20331,7 +20320,7 @@
       <c r="I641" s="2"/>
       <c r="J641" s="2"/>
     </row>
-    <row r="642" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="642" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="str">
         <f>IF(B642="", "", SUBTOTAL(3, $B$2:B642) * 1)</f>
         <v/>
@@ -20346,7 +20335,7 @@
       <c r="I642" s="2"/>
       <c r="J642" s="2"/>
     </row>
-    <row r="643" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="643" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="str">
         <f>IF(B643="", "", SUBTOTAL(3, $B$2:B643) * 1)</f>
         <v/>
@@ -20361,7 +20350,7 @@
       <c r="I643" s="2"/>
       <c r="J643" s="2"/>
     </row>
-    <row r="644" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="644" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="str">
         <f>IF(B644="", "", SUBTOTAL(3, $B$2:B644) * 1)</f>
         <v/>
@@ -20376,7 +20365,7 @@
       <c r="I644" s="2"/>
       <c r="J644" s="2"/>
     </row>
-    <row r="645" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="645" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="str">
         <f>IF(B645="", "", SUBTOTAL(3, $B$2:B645) * 1)</f>
         <v/>
@@ -20391,7 +20380,7 @@
       <c r="I645" s="2"/>
       <c r="J645" s="2"/>
     </row>
-    <row r="646" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="646" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="str">
         <f>IF(B646="", "", SUBTOTAL(3, $B$2:B646) * 1)</f>
         <v/>
@@ -20406,7 +20395,7 @@
       <c r="I646" s="2"/>
       <c r="J646" s="2"/>
     </row>
-    <row r="647" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="647" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="str">
         <f>IF(B647="", "", SUBTOTAL(3, $B$2:B647) * 1)</f>
         <v/>
@@ -20421,7 +20410,7 @@
       <c r="I647" s="2"/>
       <c r="J647" s="2"/>
     </row>
-    <row r="648" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="648" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="str">
         <f>IF(B648="", "", SUBTOTAL(3, $B$2:B648) * 1)</f>
         <v/>
@@ -20436,7 +20425,7 @@
       <c r="I648" s="2"/>
       <c r="J648" s="2"/>
     </row>
-    <row r="649" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="649" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="str">
         <f>IF(B649="", "", SUBTOTAL(3, $B$2:B649) * 1)</f>
         <v/>
@@ -20451,7 +20440,7 @@
       <c r="I649" s="2"/>
       <c r="J649" s="2"/>
     </row>
-    <row r="650" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="650" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="str">
         <f>IF(B650="", "", SUBTOTAL(3, $B$2:B650) * 1)</f>
         <v/>
@@ -20466,7 +20455,7 @@
       <c r="I650" s="2"/>
       <c r="J650" s="2"/>
     </row>
-    <row r="651" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="651" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="str">
         <f>IF(B651="", "", SUBTOTAL(3, $B$2:B651) * 1)</f>
         <v/>
@@ -20481,7 +20470,7 @@
       <c r="I651" s="2"/>
       <c r="J651" s="2"/>
     </row>
-    <row r="652" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="652" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="str">
         <f>IF(B652="", "", SUBTOTAL(3, $B$2:B652) * 1)</f>
         <v/>
@@ -20496,7 +20485,7 @@
       <c r="I652" s="2"/>
       <c r="J652" s="2"/>
     </row>
-    <row r="653" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="653" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="str">
         <f>IF(B653="", "", SUBTOTAL(3, $B$2:B653) * 1)</f>
         <v/>
@@ -20511,7 +20500,7 @@
       <c r="I653" s="2"/>
       <c r="J653" s="2"/>
     </row>
-    <row r="654" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="654" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="str">
         <f>IF(B654="", "", SUBTOTAL(3, $B$2:B654) * 1)</f>
         <v/>
@@ -20526,7 +20515,7 @@
       <c r="I654" s="2"/>
       <c r="J654" s="2"/>
     </row>
-    <row r="655" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="655" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="str">
         <f>IF(B655="", "", SUBTOTAL(3, $B$2:B655) * 1)</f>
         <v/>
@@ -20541,7 +20530,7 @@
       <c r="I655" s="2"/>
       <c r="J655" s="2"/>
     </row>
-    <row r="656" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="656" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="str">
         <f>IF(B656="", "", SUBTOTAL(3, $B$2:B656) * 1)</f>
         <v/>
@@ -20556,7 +20545,7 @@
       <c r="I656" s="2"/>
       <c r="J656" s="2"/>
     </row>
-    <row r="657" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="657" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="str">
         <f>IF(B657="", "", SUBTOTAL(3, $B$2:B657) * 1)</f>
         <v/>
@@ -20571,7 +20560,7 @@
       <c r="I657" s="2"/>
       <c r="J657" s="2"/>
     </row>
-    <row r="658" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="658" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="str">
         <f>IF(B658="", "", SUBTOTAL(3, $B$2:B658) * 1)</f>
         <v/>
@@ -20586,7 +20575,7 @@
       <c r="I658" s="2"/>
       <c r="J658" s="2"/>
     </row>
-    <row r="659" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="659" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="str">
         <f>IF(B659="", "", SUBTOTAL(3, $B$2:B659) * 1)</f>
         <v/>
@@ -20601,7 +20590,7 @@
       <c r="I659" s="2"/>
       <c r="J659" s="2"/>
     </row>
-    <row r="660" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="660" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="str">
         <f>IF(B660="", "", SUBTOTAL(3, $B$2:B660) * 1)</f>
         <v/>
@@ -20616,7 +20605,7 @@
       <c r="I660" s="2"/>
       <c r="J660" s="2"/>
     </row>
-    <row r="661" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="661" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="str">
         <f>IF(B661="", "", SUBTOTAL(3, $B$2:B661) * 1)</f>
         <v/>
@@ -20631,7 +20620,7 @@
       <c r="I661" s="2"/>
       <c r="J661" s="2"/>
     </row>
-    <row r="662" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="662" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="str">
         <f>IF(B662="", "", SUBTOTAL(3, $B$2:B662) * 1)</f>
         <v/>
@@ -20646,7 +20635,7 @@
       <c r="I662" s="2"/>
       <c r="J662" s="2"/>
     </row>
-    <row r="663" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="663" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="str">
         <f>IF(B663="", "", SUBTOTAL(3, $B$2:B663) * 1)</f>
         <v/>
@@ -20661,7 +20650,7 @@
       <c r="I663" s="2"/>
       <c r="J663" s="2"/>
     </row>
-    <row r="664" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="664" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="str">
         <f>IF(B664="", "", SUBTOTAL(3, $B$2:B664) * 1)</f>
         <v/>
@@ -20676,7 +20665,7 @@
       <c r="I664" s="2"/>
       <c r="J664" s="2"/>
     </row>
-    <row r="665" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="665" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="str">
         <f>IF(B665="", "", SUBTOTAL(3, $B$2:B665) * 1)</f>
         <v/>
@@ -20691,7 +20680,7 @@
       <c r="I665" s="2"/>
       <c r="J665" s="2"/>
     </row>
-    <row r="666" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="666" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="str">
         <f>IF(B666="", "", SUBTOTAL(3, $B$2:B666) * 1)</f>
         <v/>
@@ -20706,7 +20695,7 @@
       <c r="I666" s="2"/>
       <c r="J666" s="2"/>
     </row>
-    <row r="667" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="667" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="str">
         <f>IF(B667="", "", SUBTOTAL(3, $B$2:B667) * 1)</f>
         <v/>
@@ -20721,7 +20710,7 @@
       <c r="I667" s="2"/>
       <c r="J667" s="2"/>
     </row>
-    <row r="668" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="668" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="str">
         <f>IF(B668="", "", SUBTOTAL(3, $B$2:B668) * 1)</f>
         <v/>
@@ -20736,7 +20725,7 @@
       <c r="I668" s="2"/>
       <c r="J668" s="2"/>
     </row>
-    <row r="669" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="669" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="str">
         <f>IF(B669="", "", SUBTOTAL(3, $B$2:B669) * 1)</f>
         <v/>
@@ -20751,7 +20740,7 @@
       <c r="I669" s="2"/>
       <c r="J669" s="2"/>
     </row>
-    <row r="670" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="670" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="str">
         <f>IF(B670="", "", SUBTOTAL(3, $B$2:B670) * 1)</f>
         <v/>
@@ -20766,7 +20755,7 @@
       <c r="I670" s="2"/>
       <c r="J670" s="2"/>
     </row>
-    <row r="671" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="671" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="str">
         <f>IF(B671="", "", SUBTOTAL(3, $B$2:B671) * 1)</f>
         <v/>
@@ -20781,7 +20770,7 @@
       <c r="I671" s="2"/>
       <c r="J671" s="2"/>
     </row>
-    <row r="672" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="672" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="str">
         <f>IF(B672="", "", SUBTOTAL(3, $B$2:B672) * 1)</f>
         <v/>
@@ -20796,7 +20785,7 @@
       <c r="I672" s="2"/>
       <c r="J672" s="2"/>
     </row>
-    <row r="673" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="673" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="str">
         <f>IF(B673="", "", SUBTOTAL(3, $B$2:B673) * 1)</f>
         <v/>
@@ -20811,7 +20800,7 @@
       <c r="I673" s="2"/>
       <c r="J673" s="2"/>
     </row>
-    <row r="674" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="674" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="str">
         <f>IF(B674="", "", SUBTOTAL(3, $B$2:B674) * 1)</f>
         <v/>
@@ -20826,7 +20815,7 @@
       <c r="I674" s="2"/>
       <c r="J674" s="2"/>
     </row>
-    <row r="675" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="675" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="str">
         <f>IF(B675="", "", SUBTOTAL(3, $B$2:B675) * 1)</f>
         <v/>
@@ -20841,7 +20830,7 @@
       <c r="I675" s="2"/>
       <c r="J675" s="2"/>
     </row>
-    <row r="676" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="676" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="str">
         <f>IF(B676="", "", SUBTOTAL(3, $B$2:B676) * 1)</f>
         <v/>
@@ -20856,7 +20845,7 @@
       <c r="I676" s="2"/>
       <c r="J676" s="2"/>
     </row>
-    <row r="677" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="677" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="str">
         <f>IF(B677="", "", SUBTOTAL(3, $B$2:B677) * 1)</f>
         <v/>
@@ -20871,7 +20860,7 @@
       <c r="I677" s="2"/>
       <c r="J677" s="2"/>
     </row>
-    <row r="678" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="678" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="str">
         <f>IF(B678="", "", SUBTOTAL(3, $B$2:B678) * 1)</f>
         <v/>
@@ -20886,7 +20875,7 @@
       <c r="I678" s="2"/>
       <c r="J678" s="2"/>
     </row>
-    <row r="679" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="679" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="str">
         <f>IF(B679="", "", SUBTOTAL(3, $B$2:B679) * 1)</f>
         <v/>
@@ -20901,7 +20890,7 @@
       <c r="I679" s="2"/>
       <c r="J679" s="2"/>
     </row>
-    <row r="680" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="680" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="str">
         <f>IF(B680="", "", SUBTOTAL(3, $B$2:B680) * 1)</f>
         <v/>
@@ -20916,7 +20905,7 @@
       <c r="I680" s="2"/>
       <c r="J680" s="2"/>
     </row>
-    <row r="681" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="681" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="str">
         <f>IF(B681="", "", SUBTOTAL(3, $B$2:B681) * 1)</f>
         <v/>
@@ -20931,7 +20920,7 @@
       <c r="I681" s="2"/>
       <c r="J681" s="2"/>
     </row>
-    <row r="682" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="682" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="str">
         <f>IF(B682="", "", SUBTOTAL(3, $B$2:B682) * 1)</f>
         <v/>
@@ -20946,7 +20935,7 @@
       <c r="I682" s="2"/>
       <c r="J682" s="2"/>
     </row>
-    <row r="683" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="683" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="str">
         <f>IF(B683="", "", SUBTOTAL(3, $B$2:B683) * 1)</f>
         <v/>
@@ -20961,7 +20950,7 @@
       <c r="I683" s="2"/>
       <c r="J683" s="2"/>
     </row>
-    <row r="684" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="684" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="str">
         <f>IF(B684="", "", SUBTOTAL(3, $B$2:B684) * 1)</f>
         <v/>
@@ -20976,7 +20965,7 @@
       <c r="I684" s="2"/>
       <c r="J684" s="2"/>
     </row>
-    <row r="685" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="685" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="str">
         <f>IF(B685="", "", SUBTOTAL(3, $B$2:B685) * 1)</f>
         <v/>
@@ -20991,7 +20980,7 @@
       <c r="I685" s="2"/>
       <c r="J685" s="2"/>
     </row>
-    <row r="686" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="686" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="str">
         <f>IF(B686="", "", SUBTOTAL(3, $B$2:B686) * 1)</f>
         <v/>
@@ -21006,7 +20995,7 @@
       <c r="I686" s="2"/>
       <c r="J686" s="2"/>
     </row>
-    <row r="687" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="687" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="str">
         <f>IF(B687="", "", SUBTOTAL(3, $B$2:B687) * 1)</f>
         <v/>
@@ -21021,7 +21010,7 @@
       <c r="I687" s="2"/>
       <c r="J687" s="2"/>
     </row>
-    <row r="688" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="688" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="str">
         <f>IF(B688="", "", SUBTOTAL(3, $B$2:B688) * 1)</f>
         <v/>
@@ -21036,7 +21025,7 @@
       <c r="I688" s="2"/>
       <c r="J688" s="2"/>
     </row>
-    <row r="689" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="689" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="str">
         <f>IF(B689="", "", SUBTOTAL(3, $B$2:B689) * 1)</f>
         <v/>
@@ -21051,7 +21040,7 @@
       <c r="I689" s="2"/>
       <c r="J689" s="2"/>
     </row>
-    <row r="690" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="690" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="str">
         <f>IF(B690="", "", SUBTOTAL(3, $B$2:B690) * 1)</f>
         <v/>
@@ -21066,7 +21055,7 @@
       <c r="I690" s="2"/>
       <c r="J690" s="2"/>
     </row>
-    <row r="691" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="691" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="str">
         <f>IF(B691="", "", SUBTOTAL(3, $B$2:B691) * 1)</f>
         <v/>
@@ -21081,7 +21070,7 @@
       <c r="I691" s="2"/>
       <c r="J691" s="2"/>
     </row>
-    <row r="692" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="692" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="str">
         <f>IF(B692="", "", SUBTOTAL(3, $B$2:B692) * 1)</f>
         <v/>
@@ -21096,7 +21085,7 @@
       <c r="I692" s="2"/>
       <c r="J692" s="2"/>
     </row>
-    <row r="693" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="693" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="str">
         <f>IF(B693="", "", SUBTOTAL(3, $B$2:B693) * 1)</f>
         <v/>
@@ -21111,7 +21100,7 @@
       <c r="I693" s="2"/>
       <c r="J693" s="2"/>
     </row>
-    <row r="694" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="694" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="str">
         <f>IF(B694="", "", SUBTOTAL(3, $B$2:B694) * 1)</f>
         <v/>
@@ -21126,7 +21115,7 @@
       <c r="I694" s="2"/>
       <c r="J694" s="2"/>
     </row>
-    <row r="695" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="695" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="str">
         <f>IF(B695="", "", SUBTOTAL(3, $B$2:B695) * 1)</f>
         <v/>
@@ -21141,7 +21130,7 @@
       <c r="I695" s="2"/>
       <c r="J695" s="2"/>
     </row>
-    <row r="696" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="696" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="str">
         <f>IF(B696="", "", SUBTOTAL(3, $B$2:B696) * 1)</f>
         <v/>
@@ -21156,7 +21145,7 @@
       <c r="I696" s="2"/>
       <c r="J696" s="2"/>
     </row>
-    <row r="697" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="697" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="str">
         <f>IF(B697="", "", SUBTOTAL(3, $B$2:B697) * 1)</f>
         <v/>
@@ -21171,7 +21160,7 @@
       <c r="I697" s="2"/>
       <c r="J697" s="2"/>
     </row>
-    <row r="698" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="698" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="str">
         <f>IF(B698="", "", SUBTOTAL(3, $B$2:B698) * 1)</f>
         <v/>
@@ -21186,7 +21175,7 @@
       <c r="I698" s="2"/>
       <c r="J698" s="2"/>
     </row>
-    <row r="699" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="699" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="str">
         <f>IF(B699="", "", SUBTOTAL(3, $B$2:B699) * 1)</f>
         <v/>
@@ -21201,7 +21190,7 @@
       <c r="I699" s="2"/>
       <c r="J699" s="2"/>
     </row>
-    <row r="700" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="700" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="str">
         <f>IF(B700="", "", SUBTOTAL(3, $B$2:B700) * 1)</f>
         <v/>
@@ -21216,7 +21205,7 @@
       <c r="I700" s="2"/>
       <c r="J700" s="2"/>
     </row>
-    <row r="701" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="701" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="str">
         <f>IF(B701="", "", SUBTOTAL(3, $B$2:B701) * 1)</f>
         <v/>
@@ -21231,7 +21220,7 @@
       <c r="I701" s="2"/>
       <c r="J701" s="2"/>
     </row>
-    <row r="702" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="702" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="str">
         <f>IF(B702="", "", SUBTOTAL(3, $B$2:B702) * 1)</f>
         <v/>
@@ -21246,7 +21235,7 @@
       <c r="I702" s="2"/>
       <c r="J702" s="2"/>
     </row>
-    <row r="703" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="703" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="str">
         <f>IF(B703="", "", SUBTOTAL(3, $B$2:B703) * 1)</f>
         <v/>
@@ -21261,7 +21250,7 @@
       <c r="I703" s="2"/>
       <c r="J703" s="2"/>
     </row>
-    <row r="704" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="704" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="str">
         <f>IF(B704="", "", SUBTOTAL(3, $B$2:B704) * 1)</f>
         <v/>
@@ -21276,7 +21265,7 @@
       <c r="I704" s="2"/>
       <c r="J704" s="2"/>
     </row>
-    <row r="705" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="705" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="str">
         <f>IF(B705="", "", SUBTOTAL(3, $B$2:B705) * 1)</f>
         <v/>
@@ -21291,7 +21280,7 @@
       <c r="I705" s="2"/>
       <c r="J705" s="2"/>
     </row>
-    <row r="706" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="706" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="str">
         <f>IF(B706="", "", SUBTOTAL(3, $B$2:B706) * 1)</f>
         <v/>
@@ -21306,7 +21295,7 @@
       <c r="I706" s="2"/>
       <c r="J706" s="2"/>
     </row>
-    <row r="707" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="707" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="str">
         <f>IF(B707="", "", SUBTOTAL(3, $B$2:B707) * 1)</f>
         <v/>
@@ -21321,7 +21310,7 @@
       <c r="I707" s="2"/>
       <c r="J707" s="2"/>
     </row>
-    <row r="708" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="708" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="str">
         <f>IF(B708="", "", SUBTOTAL(3, $B$2:B708) * 1)</f>
         <v/>
@@ -21336,7 +21325,7 @@
       <c r="I708" s="2"/>
       <c r="J708" s="2"/>
     </row>
-    <row r="709" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="709" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="str">
         <f>IF(B709="", "", SUBTOTAL(3, $B$2:B709) * 1)</f>
         <v/>
@@ -21351,7 +21340,7 @@
       <c r="I709" s="2"/>
       <c r="J709" s="2"/>
     </row>
-    <row r="710" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="710" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="str">
         <f>IF(B710="", "", SUBTOTAL(3, $B$2:B710) * 1)</f>
         <v/>
@@ -21366,7 +21355,7 @@
       <c r="I710" s="2"/>
       <c r="J710" s="2"/>
     </row>
-    <row r="711" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="711" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="str">
         <f>IF(B711="", "", SUBTOTAL(3, $B$2:B711) * 1)</f>
         <v/>
@@ -21381,7 +21370,7 @@
       <c r="I711" s="2"/>
       <c r="J711" s="2"/>
     </row>
-    <row r="712" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="712" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="str">
         <f>IF(B712="", "", SUBTOTAL(3, $B$2:B712) * 1)</f>
         <v/>
@@ -21396,7 +21385,7 @@
       <c r="I712" s="2"/>
       <c r="J712" s="2"/>
     </row>
-    <row r="713" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="713" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="str">
         <f>IF(B713="", "", SUBTOTAL(3, $B$2:B713) * 1)</f>
         <v/>
@@ -21411,7 +21400,7 @@
       <c r="I713" s="2"/>
       <c r="J713" s="2"/>
     </row>
-    <row r="714" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="714" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="str">
         <f>IF(B714="", "", SUBTOTAL(3, $B$2:B714) * 1)</f>
         <v/>
@@ -21426,7 +21415,7 @@
       <c r="I714" s="2"/>
       <c r="J714" s="2"/>
     </row>
-    <row r="715" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="715" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="str">
         <f>IF(B715="", "", SUBTOTAL(3, $B$2:B715) * 1)</f>
         <v/>
@@ -21441,7 +21430,7 @@
       <c r="I715" s="2"/>
       <c r="J715" s="2"/>
     </row>
-    <row r="716" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="716" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="str">
         <f>IF(B716="", "", SUBTOTAL(3, $B$2:B716) * 1)</f>
         <v/>
@@ -21456,7 +21445,7 @@
       <c r="I716" s="2"/>
       <c r="J716" s="2"/>
     </row>
-    <row r="717" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="717" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="str">
         <f>IF(B717="", "", SUBTOTAL(3, $B$2:B717) * 1)</f>
         <v/>
@@ -21471,7 +21460,7 @@
       <c r="I717" s="2"/>
       <c r="J717" s="2"/>
     </row>
-    <row r="718" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="718" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="str">
         <f>IF(B718="", "", SUBTOTAL(3, $B$2:B718) * 1)</f>
         <v/>
@@ -21486,7 +21475,7 @@
       <c r="I718" s="2"/>
       <c r="J718" s="2"/>
     </row>
-    <row r="719" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="719" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="str">
         <f>IF(B719="", "", SUBTOTAL(3, $B$2:B719) * 1)</f>
         <v/>
@@ -21501,7 +21490,7 @@
       <c r="I719" s="2"/>
       <c r="J719" s="2"/>
     </row>
-    <row r="720" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="720" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="str">
         <f>IF(B720="", "", SUBTOTAL(3, $B$2:B720) * 1)</f>
         <v/>
@@ -21516,7 +21505,7 @@
       <c r="I720" s="2"/>
       <c r="J720" s="2"/>
     </row>
-    <row r="721" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="721" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="str">
         <f>IF(B721="", "", SUBTOTAL(3, $B$2:B721) * 1)</f>
         <v/>
@@ -21531,7 +21520,7 @@
       <c r="I721" s="2"/>
       <c r="J721" s="2"/>
     </row>
-    <row r="722" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="722" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="str">
         <f>IF(B722="", "", SUBTOTAL(3, $B$2:B722) * 1)</f>
         <v/>
@@ -21546,7 +21535,7 @@
       <c r="I722" s="2"/>
       <c r="J722" s="2"/>
     </row>
-    <row r="723" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="723" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="str">
         <f>IF(B723="", "", SUBTOTAL(3, $B$2:B723) * 1)</f>
         <v/>
@@ -21561,7 +21550,7 @@
       <c r="I723" s="2"/>
       <c r="J723" s="2"/>
     </row>
-    <row r="724" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="724" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="str">
         <f>IF(B724="", "", SUBTOTAL(3, $B$2:B724) * 1)</f>
         <v/>
@@ -21576,7 +21565,7 @@
       <c r="I724" s="2"/>
       <c r="J724" s="2"/>
     </row>
-    <row r="725" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="725" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="str">
         <f>IF(B725="", "", SUBTOTAL(3, $B$2:B725) * 1)</f>
         <v/>
@@ -21591,7 +21580,7 @@
       <c r="I725" s="2"/>
       <c r="J725" s="2"/>
     </row>
-    <row r="726" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="726" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="str">
         <f>IF(B726="", "", SUBTOTAL(3, $B$2:B726) * 1)</f>
         <v/>
@@ -21606,7 +21595,7 @@
       <c r="I726" s="2"/>
       <c r="J726" s="2"/>
     </row>
-    <row r="727" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="727" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="str">
         <f>IF(B727="", "", SUBTOTAL(3, $B$2:B727) * 1)</f>
         <v/>
@@ -21621,7 +21610,7 @@
       <c r="I727" s="2"/>
       <c r="J727" s="2"/>
     </row>
-    <row r="728" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="728" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="str">
         <f>IF(B728="", "", SUBTOTAL(3, $B$2:B728) * 1)</f>
         <v/>
@@ -21636,7 +21625,7 @@
       <c r="I728" s="2"/>
       <c r="J728" s="2"/>
     </row>
-    <row r="729" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="729" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="str">
         <f>IF(B729="", "", SUBTOTAL(3, $B$2:B729) * 1)</f>
         <v/>
@@ -21651,7 +21640,7 @@
       <c r="I729" s="2"/>
       <c r="J729" s="2"/>
     </row>
-    <row r="730" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="730" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="str">
         <f>IF(B730="", "", SUBTOTAL(3, $B$2:B730) * 1)</f>
         <v/>
@@ -21666,7 +21655,7 @@
       <c r="I730" s="2"/>
       <c r="J730" s="2"/>
     </row>
-    <row r="731" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="731" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="str">
         <f>IF(B731="", "", SUBTOTAL(3, $B$2:B731) * 1)</f>
         <v/>
@@ -21681,7 +21670,7 @@
       <c r="I731" s="2"/>
       <c r="J731" s="2"/>
     </row>
-    <row r="732" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="732" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="str">
         <f>IF(B732="", "", SUBTOTAL(3, $B$2:B732) * 1)</f>
         <v/>
@@ -21696,7 +21685,7 @@
       <c r="I732" s="2"/>
       <c r="J732" s="2"/>
     </row>
-    <row r="733" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="733" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="str">
         <f>IF(B733="", "", SUBTOTAL(3, $B$2:B733) * 1)</f>
         <v/>
@@ -21711,7 +21700,7 @@
       <c r="I733" s="2"/>
       <c r="J733" s="2"/>
     </row>
-    <row r="734" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="734" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="str">
         <f>IF(B734="", "", SUBTOTAL(3, $B$2:B734) * 1)</f>
         <v/>
@@ -21726,7 +21715,7 @@
       <c r="I734" s="2"/>
       <c r="J734" s="2"/>
     </row>
-    <row r="735" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="735" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="str">
         <f>IF(B735="", "", SUBTOTAL(3, $B$2:B735) * 1)</f>
         <v/>
@@ -21741,7 +21730,7 @@
       <c r="I735" s="2"/>
       <c r="J735" s="2"/>
     </row>
-    <row r="736" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="736" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="str">
         <f>IF(B736="", "", SUBTOTAL(3, $B$2:B736) * 1)</f>
         <v/>
@@ -21756,7 +21745,7 @@
       <c r="I736" s="2"/>
       <c r="J736" s="2"/>
     </row>
-    <row r="737" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="737" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="str">
         <f>IF(B737="", "", SUBTOTAL(3, $B$2:B737) * 1)</f>
         <v/>
@@ -21771,7 +21760,7 @@
       <c r="I737" s="2"/>
       <c r="J737" s="2"/>
     </row>
-    <row r="738" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="738" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="str">
         <f>IF(B738="", "", SUBTOTAL(3, $B$2:B738) * 1)</f>
         <v/>
@@ -21786,7 +21775,7 @@
       <c r="I738" s="2"/>
       <c r="J738" s="2"/>
     </row>
-    <row r="739" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="739" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="str">
         <f>IF(B739="", "", SUBTOTAL(3, $B$2:B739) * 1)</f>
         <v/>
@@ -21801,7 +21790,7 @@
       <c r="I739" s="2"/>
       <c r="J739" s="2"/>
     </row>
-    <row r="740" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="740" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="str">
         <f>IF(B740="", "", SUBTOTAL(3, $B$2:B740) * 1)</f>
         <v/>
@@ -21816,7 +21805,7 @@
       <c r="I740" s="2"/>
       <c r="J740" s="2"/>
     </row>
-    <row r="741" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="741" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="str">
         <f>IF(B741="", "", SUBTOTAL(3, $B$2:B741) * 1)</f>
         <v/>
@@ -21831,7 +21820,7 @@
       <c r="I741" s="2"/>
       <c r="J741" s="2"/>
     </row>
-    <row r="742" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="742" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="str">
         <f>IF(B742="", "", SUBTOTAL(3, $B$2:B742) * 1)</f>
         <v/>
@@ -21846,7 +21835,7 @@
       <c r="I742" s="2"/>
       <c r="J742" s="2"/>
     </row>
-    <row r="743" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="743" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="str">
         <f>IF(B743="", "", SUBTOTAL(3, $B$2:B743) * 1)</f>
         <v/>
@@ -21861,7 +21850,7 @@
       <c r="I743" s="2"/>
       <c r="J743" s="2"/>
     </row>
-    <row r="744" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="744" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="str">
         <f>IF(B744="", "", SUBTOTAL(3, $B$2:B744) * 1)</f>
         <v/>
@@ -21876,7 +21865,7 @@
       <c r="I744" s="2"/>
       <c r="J744" s="2"/>
     </row>
-    <row r="745" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="745" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="str">
         <f>IF(B745="", "", SUBTOTAL(3, $B$2:B745) * 1)</f>
         <v/>
@@ -21891,7 +21880,7 @@
       <c r="I745" s="2"/>
       <c r="J745" s="2"/>
     </row>
-    <row r="746" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="746" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="str">
         <f>IF(B746="", "", SUBTOTAL(3, $B$2:B746) * 1)</f>
         <v/>
@@ -21906,7 +21895,7 @@
       <c r="I746" s="2"/>
       <c r="J746" s="2"/>
     </row>
-    <row r="747" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="747" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="str">
         <f>IF(B747="", "", SUBTOTAL(3, $B$2:B747) * 1)</f>
         <v/>
@@ -21921,7 +21910,7 @@
       <c r="I747" s="2"/>
       <c r="J747" s="2"/>
     </row>
-    <row r="748" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="748" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="str">
         <f>IF(B748="", "", SUBTOTAL(3, $B$2:B748) * 1)</f>
         <v/>
@@ -21936,7 +21925,7 @@
       <c r="I748" s="2"/>
       <c r="J748" s="2"/>
     </row>
-    <row r="749" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="749" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="str">
         <f>IF(B749="", "", SUBTOTAL(3, $B$2:B749) * 1)</f>
         <v/>
@@ -21951,7 +21940,7 @@
       <c r="I749" s="2"/>
       <c r="J749" s="2"/>
     </row>
-    <row r="750" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="750" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="str">
         <f>IF(B750="", "", SUBTOTAL(3, $B$2:B750) * 1)</f>
         <v/>
@@ -21966,7 +21955,7 @@
       <c r="I750" s="2"/>
       <c r="J750" s="2"/>
     </row>
-    <row r="751" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="751" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="str">
         <f>IF(B751="", "", SUBTOTAL(3, $B$2:B751) * 1)</f>
         <v/>
@@ -21981,7 +21970,7 @@
       <c r="I751" s="2"/>
       <c r="J751" s="2"/>
     </row>
-    <row r="752" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="752" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="str">
         <f>IF(B752="", "", SUBTOTAL(3, $B$2:B752) * 1)</f>
         <v/>
@@ -21996,7 +21985,7 @@
       <c r="I752" s="2"/>
       <c r="J752" s="2"/>
     </row>
-    <row r="753" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="753" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="str">
         <f>IF(B753="", "", SUBTOTAL(3, $B$2:B753) * 1)</f>
         <v/>
@@ -22011,7 +22000,7 @@
       <c r="I753" s="2"/>
       <c r="J753" s="2"/>
     </row>
-    <row r="754" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="754" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="str">
         <f>IF(B754="", "", SUBTOTAL(3, $B$2:B754) * 1)</f>
         <v/>
@@ -22026,7 +22015,7 @@
       <c r="I754" s="2"/>
       <c r="J754" s="2"/>
     </row>
-    <row r="755" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="755" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="str">
         <f>IF(B755="", "", SUBTOTAL(3, $B$2:B755) * 1)</f>
         <v/>
@@ -22041,7 +22030,7 @@
       <c r="I755" s="2"/>
       <c r="J755" s="2"/>
     </row>
-    <row r="756" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="756" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="str">
         <f>IF(B756="", "", SUBTOTAL(3, $B$2:B756) * 1)</f>
         <v/>
@@ -22056,7 +22045,7 @@
       <c r="I756" s="2"/>
       <c r="J756" s="2"/>
     </row>
-    <row r="757" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="757" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="str">
         <f>IF(B757="", "", SUBTOTAL(3, $B$2:B757) * 1)</f>
         <v/>
@@ -22071,7 +22060,7 @@
       <c r="I757" s="2"/>
       <c r="J757" s="2"/>
     </row>
-    <row r="758" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="758" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="str">
         <f>IF(B758="", "", SUBTOTAL(3, $B$2:B758) * 1)</f>
         <v/>
@@ -22086,7 +22075,7 @@
       <c r="I758" s="2"/>
       <c r="J758" s="2"/>
     </row>
-    <row r="759" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="759" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="str">
         <f>IF(B759="", "", SUBTOTAL(3, $B$2:B759) * 1)</f>
         <v/>
@@ -22101,7 +22090,7 @@
       <c r="I759" s="2"/>
       <c r="J759" s="2"/>
     </row>
-    <row r="760" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="760" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="str">
         <f>IF(B760="", "", SUBTOTAL(3, $B$2:B760) * 1)</f>
         <v/>
@@ -22116,7 +22105,7 @@
       <c r="I760" s="2"/>
       <c r="J760" s="2"/>
     </row>
-    <row r="761" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="761" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="str">
         <f>IF(B761="", "", SUBTOTAL(3, $B$2:B761) * 1)</f>
         <v/>
@@ -22131,7 +22120,7 @@
       <c r="I761" s="2"/>
       <c r="J761" s="2"/>
     </row>
-    <row r="762" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="762" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="str">
         <f>IF(B762="", "", SUBTOTAL(3, $B$2:B762) * 1)</f>
         <v/>
@@ -22146,7 +22135,7 @@
       <c r="I762" s="2"/>
       <c r="J762" s="2"/>
     </row>
-    <row r="763" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="763" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="str">
         <f>IF(B763="", "", SUBTOTAL(3, $B$2:B763) * 1)</f>
         <v/>
@@ -22161,7 +22150,7 @@
       <c r="I763" s="2"/>
       <c r="J763" s="2"/>
     </row>
-    <row r="764" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="764" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="str">
         <f>IF(B764="", "", SUBTOTAL(3, $B$2:B764) * 1)</f>
         <v/>
@@ -22176,7 +22165,7 @@
       <c r="I764" s="2"/>
       <c r="J764" s="2"/>
     </row>
-    <row r="765" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="765" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="str">
         <f>IF(B765="", "", SUBTOTAL(3, $B$2:B765) * 1)</f>
         <v/>
@@ -22191,7 +22180,7 @@
       <c r="I765" s="2"/>
       <c r="J765" s="2"/>
     </row>
-    <row r="766" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="766" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="str">
         <f>IF(B766="", "", SUBTOTAL(3, $B$2:B766) * 1)</f>
         <v/>
@@ -22206,7 +22195,7 @@
       <c r="I766" s="2"/>
       <c r="J766" s="2"/>
     </row>
-    <row r="767" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="767" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="str">
         <f>IF(B767="", "", SUBTOTAL(3, $B$2:B767) * 1)</f>
         <v/>
@@ -22221,7 +22210,7 @@
       <c r="I767" s="2"/>
       <c r="J767" s="2"/>
     </row>
-    <row r="768" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="768" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="str">
         <f>IF(B768="", "", SUBTOTAL(3, $B$2:B768) * 1)</f>
         <v/>
@@ -22236,7 +22225,7 @@
       <c r="I768" s="2"/>
       <c r="J768" s="2"/>
     </row>
-    <row r="769" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="769" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="str">
         <f>IF(B769="", "", SUBTOTAL(3, $B$2:B769) * 1)</f>
         <v/>
@@ -22251,7 +22240,7 @@
       <c r="I769" s="2"/>
       <c r="J769" s="2"/>
     </row>
-    <row r="770" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="770" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="str">
         <f>IF(B770="", "", SUBTOTAL(3, $B$2:B770) * 1)</f>
         <v/>
@@ -22266,7 +22255,7 @@
       <c r="I770" s="2"/>
       <c r="J770" s="2"/>
     </row>
-    <row r="771" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="771" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="str">
         <f>IF(B771="", "", SUBTOTAL(3, $B$2:B771) * 1)</f>
         <v/>
@@ -22281,7 +22270,7 @@
       <c r="I771" s="2"/>
       <c r="J771" s="2"/>
     </row>
-    <row r="772" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="772" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="str">
         <f>IF(B772="", "", SUBTOTAL(3, $B$2:B772) * 1)</f>
         <v/>
@@ -22296,7 +22285,7 @@
       <c r="I772" s="2"/>
       <c r="J772" s="2"/>
     </row>
-    <row r="773" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="773" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="str">
         <f>IF(B773="", "", SUBTOTAL(3, $B$2:B773) * 1)</f>
         <v/>
@@ -22311,7 +22300,7 @@
       <c r="I773" s="2"/>
       <c r="J773" s="2"/>
     </row>
-    <row r="774" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="774" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="str">
         <f>IF(B774="", "", SUBTOTAL(3, $B$2:B774) * 1)</f>
         <v/>
@@ -22326,7 +22315,7 @@
       <c r="I774" s="2"/>
       <c r="J774" s="2"/>
     </row>
-    <row r="775" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="775" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="str">
         <f>IF(B775="", "", SUBTOTAL(3, $B$2:B775) * 1)</f>
         <v/>
@@ -22341,7 +22330,7 @@
       <c r="I775" s="2"/>
       <c r="J775" s="2"/>
     </row>
-    <row r="776" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="776" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="str">
         <f>IF(B776="", "", SUBTOTAL(3, $B$2:B776) * 1)</f>
         <v/>
@@ -22356,7 +22345,7 @@
       <c r="I776" s="2"/>
       <c r="J776" s="2"/>
     </row>
-    <row r="777" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="777" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="str">
         <f>IF(B777="", "", SUBTOTAL(3, $B$2:B777) * 1)</f>
         <v/>
@@ -22371,7 +22360,7 @@
       <c r="I777" s="2"/>
       <c r="J777" s="2"/>
     </row>
-    <row r="778" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="778" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="str">
         <f>IF(B778="", "", SUBTOTAL(3, $B$2:B778) * 1)</f>
         <v/>
@@ -22386,7 +22375,7 @@
       <c r="I778" s="2"/>
       <c r="J778" s="2"/>
     </row>
-    <row r="779" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="779" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="str">
         <f>IF(B779="", "", SUBTOTAL(3, $B$2:B779) * 1)</f>
         <v/>
@@ -22401,7 +22390,7 @@
       <c r="I779" s="2"/>
       <c r="J779" s="2"/>
     </row>
-    <row r="780" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="780" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="str">
         <f>IF(B780="", "", SUBTOTAL(3, $B$2:B780) * 1)</f>
         <v/>
@@ -22416,7 +22405,7 @@
       <c r="I780" s="2"/>
       <c r="J780" s="2"/>
     </row>
-    <row r="781" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="781" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="str">
         <f>IF(B781="", "", SUBTOTAL(3, $B$2:B781) * 1)</f>
         <v/>
@@ -22431,7 +22420,7 @@
       <c r="I781" s="2"/>
       <c r="J781" s="2"/>
     </row>
-    <row r="782" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="782" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="str">
         <f>IF(B782="", "", SUBTOTAL(3, $B$2:B782) * 1)</f>
         <v/>
@@ -22446,7 +22435,7 @@
       <c r="I782" s="2"/>
       <c r="J782" s="2"/>
     </row>
-    <row r="783" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="783" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="str">
         <f>IF(B783="", "", SUBTOTAL(3, $B$2:B783) * 1)</f>
         <v/>
@@ -22461,7 +22450,7 @@
       <c r="I783" s="2"/>
       <c r="J783" s="2"/>
     </row>
-    <row r="784" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="784" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="str">
         <f>IF(B784="", "", SUBTOTAL(3, $B$2:B784) * 1)</f>
         <v/>
@@ -22476,7 +22465,7 @@
       <c r="I784" s="2"/>
       <c r="J784" s="2"/>
     </row>
-    <row r="785" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="785" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="str">
         <f>IF(B785="", "", SUBTOTAL(3, $B$2:B785) * 1)</f>
         <v/>
@@ -22491,7 +22480,7 @@
       <c r="I785" s="2"/>
       <c r="J785" s="2"/>
     </row>
-    <row r="786" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="786" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="str">
         <f>IF(B786="", "", SUBTOTAL(3, $B$2:B786) * 1)</f>
         <v/>
@@ -22506,7 +22495,7 @@
       <c r="I786" s="2"/>
       <c r="J786" s="2"/>
     </row>
-    <row r="787" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="787" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="str">
         <f>IF(B787="", "", SUBTOTAL(3, $B$2:B787) * 1)</f>
         <v/>
@@ -22521,7 +22510,7 @@
       <c r="I787" s="2"/>
       <c r="J787" s="2"/>
     </row>
-    <row r="788" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="788" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="str">
         <f>IF(B788="", "", SUBTOTAL(3, $B$2:B788) * 1)</f>
         <v/>
@@ -22536,7 +22525,7 @@
       <c r="I788" s="2"/>
       <c r="J788" s="2"/>
     </row>
-    <row r="789" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="789" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="str">
         <f>IF(B789="", "", SUBTOTAL(3, $B$2:B789) * 1)</f>
         <v/>
@@ -22551,7 +22540,7 @@
       <c r="I789" s="2"/>
       <c r="J789" s="2"/>
     </row>
-    <row r="790" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="790" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="str">
         <f>IF(B790="", "", SUBTOTAL(3, $B$2:B790) * 1)</f>
         <v/>
@@ -22566,7 +22555,7 @@
       <c r="I790" s="2"/>
       <c r="J790" s="2"/>
     </row>
-    <row r="791" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="791" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="str">
         <f>IF(B791="", "", SUBTOTAL(3, $B$2:B791) * 1)</f>
         <v/>
@@ -22581,7 +22570,7 @@
       <c r="I791" s="2"/>
       <c r="J791" s="2"/>
     </row>
-    <row r="792" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="792" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="str">
         <f>IF(B792="", "", SUBTOTAL(3, $B$2:B792) * 1)</f>
         <v/>
@@ -22596,7 +22585,7 @@
       <c r="I792" s="2"/>
       <c r="J792" s="2"/>
     </row>
-    <row r="793" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="793" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="str">
         <f>IF(B793="", "", SUBTOTAL(3, $B$2:B793) * 1)</f>
         <v/>
@@ -22611,7 +22600,7 @@
       <c r="I793" s="2"/>
       <c r="J793" s="2"/>
     </row>
-    <row r="794" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="794" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="str">
         <f>IF(B794="", "", SUBTOTAL(3, $B$2:B794) * 1)</f>
         <v/>
@@ -22626,7 +22615,7 @@
       <c r="I794" s="2"/>
       <c r="J794" s="2"/>
     </row>
-    <row r="795" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="795" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="str">
         <f>IF(B795="", "", SUBTOTAL(3, $B$2:B795) * 1)</f>
         <v/>
@@ -22641,7 +22630,7 @@
       <c r="I795" s="2"/>
       <c r="J795" s="2"/>
     </row>
-    <row r="796" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="796" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="str">
         <f>IF(B796="", "", SUBTOTAL(3, $B$2:B796) * 1)</f>
         <v/>
@@ -22656,7 +22645,7 @@
       <c r="I796" s="2"/>
       <c r="J796" s="2"/>
     </row>
-    <row r="797" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="797" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="str">
         <f>IF(B797="", "", SUBTOTAL(3, $B$2:B797) * 1)</f>
         <v/>
@@ -22671,7 +22660,7 @@
       <c r="I797" s="2"/>
       <c r="J797" s="2"/>
     </row>
-    <row r="798" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="798" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="str">
         <f>IF(B798="", "", SUBTOTAL(3, $B$2:B798) * 1)</f>
         <v/>
@@ -22686,7 +22675,7 @@
       <c r="I798" s="2"/>
       <c r="J798" s="2"/>
     </row>
-    <row r="799" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="799" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="str">
         <f>IF(B799="", "", SUBTOTAL(3, $B$2:B799) * 1)</f>
         <v/>
@@ -22701,7 +22690,7 @@
       <c r="I799" s="2"/>
       <c r="J799" s="2"/>
     </row>
-    <row r="800" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="800" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="str">
         <f>IF(B800="", "", SUBTOTAL(3, $B$2:B800) * 1)</f>
         <v/>
@@ -22716,7 +22705,7 @@
       <c r="I800" s="2"/>
       <c r="J800" s="2"/>
     </row>
-    <row r="801" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="801" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="str">
         <f>IF(B801="", "", SUBTOTAL(3, $B$2:B801) * 1)</f>
         <v/>
@@ -22731,7 +22720,7 @@
       <c r="I801" s="2"/>
       <c r="J801" s="2"/>
     </row>
-    <row r="802" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="802" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="str">
         <f>IF(B802="", "", SUBTOTAL(3, $B$2:B802) * 1)</f>
         <v/>
@@ -22746,7 +22735,7 @@
       <c r="I802" s="2"/>
       <c r="J802" s="2"/>
     </row>
-    <row r="803" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="803" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="str">
         <f>IF(B803="", "", SUBTOTAL(3, $B$2:B803) * 1)</f>
         <v/>
@@ -22761,7 +22750,7 @@
       <c r="I803" s="2"/>
       <c r="J803" s="2"/>
     </row>
-    <row r="804" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="804" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="str">
         <f>IF(B804="", "", SUBTOTAL(3, $B$2:B804) * 1)</f>
         <v/>
@@ -22776,7 +22765,7 @@
       <c r="I804" s="2"/>
       <c r="J804" s="2"/>
     </row>
-    <row r="805" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="805" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="str">
         <f>IF(B805="", "", SUBTOTAL(3, $B$2:B805) * 1)</f>
         <v/>
@@ -22791,7 +22780,7 @@
       <c r="I805" s="2"/>
       <c r="J805" s="2"/>
     </row>
-    <row r="806" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="806" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="str">
         <f>IF(B806="", "", SUBTOTAL(3, $B$2:B806) * 1)</f>
         <v/>
@@ -22806,7 +22795,7 @@
       <c r="I806" s="2"/>
       <c r="J806" s="2"/>
     </row>
-    <row r="807" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="807" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="str">
         <f>IF(B807="", "", SUBTOTAL(3, $B$2:B807) * 1)</f>
         <v/>
@@ -22821,7 +22810,7 @@
       <c r="I807" s="2"/>
       <c r="J807" s="2"/>
     </row>
-    <row r="808" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="808" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="str">
         <f>IF(B808="", "", SUBTOTAL(3, $B$2:B808) * 1)</f>
         <v/>
@@ -22836,7 +22825,7 @@
       <c r="I808" s="2"/>
       <c r="J808" s="2"/>
     </row>
-    <row r="809" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="809" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="str">
         <f>IF(B809="", "", SUBTOTAL(3, $B$2:B809) * 1)</f>
         <v/>
@@ -22851,7 +22840,7 @@
       <c r="I809" s="2"/>
       <c r="J809" s="2"/>
     </row>
-    <row r="810" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="810" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="str">
         <f>IF(B810="", "", SUBTOTAL(3, $B$2:B810) * 1)</f>
         <v/>
@@ -22866,7 +22855,7 @@
       <c r="I810" s="2"/>
       <c r="J810" s="2"/>
     </row>
-    <row r="811" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="811" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="str">
         <f>IF(B811="", "", SUBTOTAL(3, $B$2:B811) * 1)</f>
         <v/>
@@ -22881,7 +22870,7 @@
       <c r="I811" s="2"/>
       <c r="J811" s="2"/>
     </row>
-    <row r="812" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="812" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="str">
         <f>IF(B812="", "", SUBTOTAL(3, $B$2:B812) * 1)</f>
         <v/>
@@ -22896,7 +22885,7 @@
       <c r="I812" s="2"/>
       <c r="J812" s="2"/>
     </row>
-    <row r="813" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="813" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="str">
         <f>IF(B813="", "", SUBTOTAL(3, $B$2:B813) * 1)</f>
         <v/>
@@ -22911,7 +22900,7 @@
       <c r="I813" s="2"/>
       <c r="J813" s="2"/>
     </row>
-    <row r="814" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="814" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="str">
         <f>IF(B814="", "", SUBTOTAL(3, $B$2:B814) * 1)</f>
         <v/>
@@ -22926,7 +22915,7 @@
       <c r="I814" s="2"/>
       <c r="J814" s="2"/>
     </row>
-    <row r="815" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="815" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="str">
         <f>IF(B815="", "", SUBTOTAL(3, $B$2:B815) * 1)</f>
         <v/>
@@ -22941,7 +22930,7 @@
       <c r="I815" s="2"/>
       <c r="J815" s="2"/>
     </row>
-    <row r="816" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="816" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="2" t="str">
         <f>IF(B816="", "", SUBTOTAL(3, $B$2:B816) * 1)</f>
         <v/>
@@ -22956,7 +22945,7 @@
       <c r="I816" s="2"/>
       <c r="J816" s="2"/>
     </row>
-    <row r="817" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="817" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="2" t="str">
         <f>IF(B817="", "", SUBTOTAL(3, $B$2:B817) * 1)</f>
         <v/>
@@ -22971,7 +22960,7 @@
       <c r="I817" s="2"/>
       <c r="J817" s="2"/>
     </row>
-    <row r="818" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="818" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="2" t="str">
         <f>IF(B818="", "", SUBTOTAL(3, $B$2:B818) * 1)</f>
         <v/>
@@ -22986,7 +22975,7 @@
       <c r="I818" s="2"/>
       <c r="J818" s="2"/>
     </row>
-    <row r="819" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="819" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="2" t="str">
         <f>IF(B819="", "", SUBTOTAL(3, $B$2:B819) * 1)</f>
         <v/>
@@ -23001,7 +22990,7 @@
       <c r="I819" s="2"/>
       <c r="J819" s="2"/>
     </row>
-    <row r="820" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="820" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="2" t="str">
         <f>IF(B820="", "", SUBTOTAL(3, $B$2:B820) * 1)</f>
         <v/>
@@ -23016,7 +23005,7 @@
       <c r="I820" s="2"/>
       <c r="J820" s="2"/>
     </row>
-    <row r="821" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="821" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="str">
         <f>IF(B821="", "", SUBTOTAL(3, $B$2:B821) * 1)</f>
         <v/>
@@ -23031,7 +23020,7 @@
       <c r="I821" s="2"/>
       <c r="J821" s="2"/>
     </row>
-    <row r="822" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="822" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="2" t="str">
         <f>IF(B822="", "", SUBTOTAL(3, $B$2:B822) * 1)</f>
         <v/>
@@ -23046,7 +23035,7 @@
       <c r="I822" s="2"/>
       <c r="J822" s="2"/>
     </row>
-    <row r="823" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="823" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="2" t="str">
         <f>IF(B823="", "", SUBTOTAL(3, $B$2:B823) * 1)</f>
         <v/>
@@ -23061,7 +23050,7 @@
       <c r="I823" s="2"/>
       <c r="J823" s="2"/>
     </row>
-    <row r="824" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="824" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="2" t="str">
         <f>IF(B824="", "", SUBTOTAL(3, $B$2:B824) * 1)</f>
         <v/>
@@ -23076,7 +23065,7 @@
       <c r="I824" s="2"/>
       <c r="J824" s="2"/>
     </row>
-    <row r="825" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="825" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="str">
         <f>IF(B825="", "", SUBTOTAL(3, $B$2:B825) * 1)</f>
         <v/>
@@ -23091,7 +23080,7 @@
       <c r="I825" s="2"/>
       <c r="J825" s="2"/>
     </row>
-    <row r="826" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="826" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="2" t="str">
         <f>IF(B826="", "", SUBTOTAL(3, $B$2:B826) * 1)</f>
         <v/>
@@ -23106,7 +23095,7 @@
       <c r="I826" s="2"/>
       <c r="J826" s="2"/>
     </row>
-    <row r="827" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="827" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="2" t="str">
         <f>IF(B827="", "", SUBTOTAL(3, $B$2:B827) * 1)</f>
         <v/>
@@ -23121,7 +23110,7 @@
       <c r="I827" s="2"/>
       <c r="J827" s="2"/>
     </row>
-    <row r="828" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="828" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="2" t="str">
         <f>IF(B828="", "", SUBTOTAL(3, $B$2:B828) * 1)</f>
         <v/>
@@ -23136,7 +23125,7 @@
       <c r="I828" s="2"/>
       <c r="J828" s="2"/>
     </row>
-    <row r="829" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="829" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="2" t="str">
         <f>IF(B829="", "", SUBTOTAL(3, $B$2:B829) * 1)</f>
         <v/>
@@ -23151,7 +23140,7 @@
       <c r="I829" s="2"/>
       <c r="J829" s="2"/>
     </row>
-    <row r="830" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="830" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="2" t="str">
         <f>IF(B830="", "", SUBTOTAL(3, $B$2:B830) * 1)</f>
         <v/>
@@ -23166,7 +23155,7 @@
       <c r="I830" s="2"/>
       <c r="J830" s="2"/>
     </row>
-    <row r="831" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="831" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="2" t="str">
         <f>IF(B831="", "", SUBTOTAL(3, $B$2:B831) * 1)</f>
         <v/>
@@ -23181,7 +23170,7 @@
       <c r="I831" s="2"/>
       <c r="J831" s="2"/>
     </row>
-    <row r="832" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="832" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="2" t="str">
         <f>IF(B832="", "", SUBTOTAL(3, $B$2:B832) * 1)</f>
         <v/>
@@ -23196,7 +23185,7 @@
       <c r="I832" s="2"/>
       <c r="J832" s="2"/>
     </row>
-    <row r="833" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="833" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="2" t="str">
         <f>IF(B833="", "", SUBTOTAL(3, $B$2:B833) * 1)</f>
         <v/>
@@ -23211,7 +23200,7 @@
       <c r="I833" s="2"/>
       <c r="J833" s="2"/>
     </row>
-    <row r="834" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="834" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="2" t="str">
         <f>IF(B834="", "", SUBTOTAL(3, $B$2:B834) * 1)</f>
         <v/>
@@ -23226,7 +23215,7 @@
       <c r="I834" s="2"/>
       <c r="J834" s="2"/>
     </row>
-    <row r="835" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="835" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="2" t="str">
         <f>IF(B835="", "", SUBTOTAL(3, $B$2:B835) * 1)</f>
         <v/>
@@ -23241,7 +23230,7 @@
       <c r="I835" s="2"/>
       <c r="J835" s="2"/>
     </row>
-    <row r="836" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="836" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="2" t="str">
         <f>IF(B836="", "", SUBTOTAL(3, $B$2:B836) * 1)</f>
         <v/>
@@ -23256,7 +23245,7 @@
       <c r="I836" s="2"/>
       <c r="J836" s="2"/>
     </row>
-    <row r="837" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="837" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="2" t="str">
         <f>IF(B837="", "", SUBTOTAL(3, $B$2:B837) * 1)</f>
         <v/>
@@ -23271,7 +23260,7 @@
       <c r="I837" s="2"/>
       <c r="J837" s="2"/>
     </row>
-    <row r="838" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="838" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="2" t="str">
         <f>IF(B838="", "", SUBTOTAL(3, $B$2:B838) * 1)</f>
         <v/>
@@ -23286,7 +23275,7 @@
       <c r="I838" s="2"/>
       <c r="J838" s="2"/>
     </row>
-    <row r="839" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="839" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="2" t="str">
         <f>IF(B839="", "", SUBTOTAL(3, $B$2:B839) * 1)</f>
         <v/>
@@ -23301,7 +23290,7 @@
       <c r="I839" s="2"/>
       <c r="J839" s="2"/>
     </row>
-    <row r="840" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="840" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="2" t="str">
         <f>IF(B840="", "", SUBTOTAL(3, $B$2:B840) * 1)</f>
         <v/>
@@ -23316,7 +23305,7 @@
       <c r="I840" s="2"/>
       <c r="J840" s="2"/>
     </row>
-    <row r="841" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="841" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="2" t="str">
         <f>IF(B841="", "", SUBTOTAL(3, $B$2:B841) * 1)</f>
         <v/>
@@ -23331,7 +23320,7 @@
       <c r="I841" s="2"/>
       <c r="J841" s="2"/>
     </row>
-    <row r="842" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="842" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="2" t="str">
         <f>IF(B842="", "", SUBTOTAL(3, $B$2:B842) * 1)</f>
         <v/>
@@ -23346,7 +23335,7 @@
       <c r="I842" s="2"/>
       <c r="J842" s="2"/>
     </row>
-    <row r="843" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="843" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="2" t="str">
         <f>IF(B843="", "", SUBTOTAL(3, $B$2:B843) * 1)</f>
         <v/>
@@ -23361,7 +23350,7 @@
       <c r="I843" s="2"/>
       <c r="J843" s="2"/>
     </row>
-    <row r="844" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="844" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="2" t="str">
         <f>IF(B844="", "", SUBTOTAL(3, $B$2:B844) * 1)</f>
         <v/>
@@ -23376,7 +23365,7 @@
       <c r="I844" s="2"/>
       <c r="J844" s="2"/>
     </row>
-    <row r="845" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="845" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="2" t="str">
         <f>IF(B845="", "", SUBTOTAL(3, $B$2:B845) * 1)</f>
         <v/>
@@ -23391,7 +23380,7 @@
       <c r="I845" s="2"/>
       <c r="J845" s="2"/>
     </row>
-    <row r="846" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="846" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="str">
         <f>IF(B846="", "", SUBTOTAL(3, $B$2:B846) * 1)</f>
         <v/>
@@ -23406,7 +23395,7 @@
       <c r="I846" s="2"/>
       <c r="J846" s="2"/>
     </row>
-    <row r="847" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="847" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="str">
         <f>IF(B847="", "", SUBTOTAL(3, $B$2:B847) * 1)</f>
         <v/>
@@ -23421,7 +23410,7 @@
       <c r="I847" s="2"/>
       <c r="J847" s="2"/>
     </row>
-    <row r="848" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="848" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="2" t="str">
         <f>IF(B848="", "", SUBTOTAL(3, $B$2:B848) * 1)</f>
         <v/>
@@ -23436,7 +23425,7 @@
       <c r="I848" s="2"/>
       <c r="J848" s="2"/>
     </row>
-    <row r="849" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="849" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="str">
         <f>IF(B849="", "", SUBTOTAL(3, $B$2:B849) * 1)</f>
         <v/>
@@ -23451,7 +23440,7 @@
       <c r="I849" s="2"/>
       <c r="J849" s="2"/>
     </row>
-    <row r="850" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="850" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="str">
         <f>IF(B850="", "", SUBTOTAL(3, $B$2:B850) * 1)</f>
         <v/>
@@ -23466,7 +23455,7 @@
       <c r="I850" s="2"/>
       <c r="J850" s="2"/>
     </row>
-    <row r="851" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="851" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="str">
         <f>IF(B851="", "", SUBTOTAL(3, $B$2:B851) * 1)</f>
         <v/>
@@ -23481,7 +23470,7 @@
       <c r="I851" s="2"/>
       <c r="J851" s="2"/>
     </row>
-    <row r="852" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="852" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="2" t="str">
         <f>IF(B852="", "", SUBTOTAL(3, $B$2:B852) * 1)</f>
         <v/>
@@ -23496,7 +23485,7 @@
       <c r="I852" s="2"/>
       <c r="J852" s="2"/>
     </row>
-    <row r="853" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="853" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="2" t="str">
         <f>IF(B853="", "", SUBTOTAL(3, $B$2:B853) * 1)</f>
         <v/>
@@ -23511,7 +23500,7 @@
       <c r="I853" s="2"/>
       <c r="J853" s="2"/>
     </row>
-    <row r="854" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="854" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="2" t="str">
         <f>IF(B854="", "", SUBTOTAL(3, $B$2:B854) * 1)</f>
         <v/>
@@ -23526,7 +23515,7 @@
       <c r="I854" s="2"/>
       <c r="J854" s="2"/>
     </row>
-    <row r="855" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="855" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="2" t="str">
         <f>IF(B855="", "", SUBTOTAL(3, $B$2:B855) * 1)</f>
         <v/>
@@ -23541,7 +23530,7 @@
       <c r="I855" s="2"/>
       <c r="J855" s="2"/>
     </row>
-    <row r="856" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="856" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="2" t="str">
         <f>IF(B856="", "", SUBTOTAL(3, $B$2:B856) * 1)</f>
         <v/>
@@ -23556,7 +23545,7 @@
       <c r="I856" s="2"/>
       <c r="J856" s="2"/>
     </row>
-    <row r="857" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="857" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="2" t="str">
         <f>IF(B857="", "", SUBTOTAL(3, $B$2:B857) * 1)</f>
         <v/>
@@ -23571,7 +23560,7 @@
       <c r="I857" s="2"/>
       <c r="J857" s="2"/>
     </row>
-    <row r="858" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="858" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="2" t="str">
         <f>IF(B858="", "", SUBTOTAL(3, $B$2:B858) * 1)</f>
         <v/>
@@ -23586,7 +23575,7 @@
       <c r="I858" s="2"/>
       <c r="J858" s="2"/>
     </row>
-    <row r="859" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="859" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="2" t="str">
         <f>IF(B859="", "", SUBTOTAL(3, $B$2:B859) * 1)</f>
         <v/>
@@ -23601,7 +23590,7 @@
       <c r="I859" s="2"/>
       <c r="J859" s="2"/>
     </row>
-    <row r="860" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="860" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="2" t="str">
         <f>IF(B860="", "", SUBTOTAL(3, $B$2:B860) * 1)</f>
         <v/>
@@ -23616,7 +23605,7 @@
       <c r="I860" s="2"/>
       <c r="J860" s="2"/>
     </row>
-    <row r="861" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="861" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="2" t="str">
         <f>IF(B861="", "", SUBTOTAL(3, $B$2:B861) * 1)</f>
         <v/>
@@ -23631,7 +23620,7 @@
       <c r="I861" s="2"/>
       <c r="J861" s="2"/>
     </row>
-    <row r="862" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="862" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="2" t="str">
         <f>IF(B862="", "", SUBTOTAL(3, $B$2:B862) * 1)</f>
         <v/>
@@ -23646,7 +23635,7 @@
       <c r="I862" s="2"/>
       <c r="J862" s="2"/>
     </row>
-    <row r="863" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="863" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="2" t="str">
         <f>IF(B863="", "", SUBTOTAL(3, $B$2:B863) * 1)</f>
         <v/>
@@ -23661,7 +23650,7 @@
       <c r="I863" s="2"/>
       <c r="J863" s="2"/>
     </row>
-    <row r="864" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="864" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="2" t="str">
         <f>IF(B864="", "", SUBTOTAL(3, $B$2:B864) * 1)</f>
         <v/>
@@ -23676,7 +23665,7 @@
       <c r="I864" s="2"/>
       <c r="J864" s="2"/>
     </row>
-    <row r="865" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="865" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="2" t="str">
         <f>IF(B865="", "", SUBTOTAL(3, $B$2:B865) * 1)</f>
         <v/>
@@ -23691,7 +23680,7 @@
       <c r="I865" s="2"/>
       <c r="J865" s="2"/>
     </row>
-    <row r="866" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="866" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="2" t="str">
         <f>IF(B866="", "", SUBTOTAL(3, $B$2:B866) * 1)</f>
         <v/>
@@ -23706,7 +23695,7 @@
       <c r="I866" s="2"/>
       <c r="J866" s="2"/>
     </row>
-    <row r="867" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="867" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="str">
         <f>IF(B867="", "", SUBTOTAL(3, $B$2:B867) * 1)</f>
         <v/>
@@ -23721,7 +23710,7 @@
       <c r="I867" s="2"/>
       <c r="J867" s="2"/>
     </row>
-    <row r="868" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="868" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="str">
         <f>IF(B868="", "", SUBTOTAL(3, $B$2:B868) * 1)</f>
         <v/>
@@ -23736,7 +23725,7 @@
       <c r="I868" s="2"/>
       <c r="J868" s="2"/>
     </row>
-    <row r="869" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="869" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="str">
         <f>IF(B869="", "", SUBTOTAL(3, $B$2:B869) * 1)</f>
         <v/>
@@ -23751,7 +23740,7 @@
       <c r="I869" s="2"/>
       <c r="J869" s="2"/>
     </row>
-    <row r="870" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="870" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="str">
         <f>IF(B870="", "", SUBTOTAL(3, $B$2:B870) * 1)</f>
         <v/>
@@ -23766,7 +23755,7 @@
       <c r="I870" s="2"/>
       <c r="J870" s="2"/>
     </row>
-    <row r="871" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="871" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="str">
         <f>IF(B871="", "", SUBTOTAL(3, $B$2:B871) * 1)</f>
         <v/>
@@ -23781,7 +23770,7 @@
       <c r="I871" s="2"/>
       <c r="J871" s="2"/>
     </row>
-    <row r="872" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="872" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="str">
         <f>IF(B872="", "", SUBTOTAL(3, $B$2:B872) * 1)</f>
         <v/>
@@ -23796,7 +23785,7 @@
       <c r="I872" s="2"/>
       <c r="J872" s="2"/>
     </row>
-    <row r="873" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="873" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="str">
         <f>IF(B873="", "", SUBTOTAL(3, $B$2:B873) * 1)</f>
         <v/>
@@ -23811,7 +23800,7 @@
       <c r="I873" s="2"/>
       <c r="J873" s="2"/>
     </row>
-    <row r="874" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="874" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="2" t="str">
         <f>IF(B874="", "", SUBTOTAL(3, $B$2:B874) * 1)</f>
         <v/>
@@ -23826,7 +23815,7 @@
       <c r="I874" s="2"/>
       <c r="J874" s="2"/>
     </row>
-    <row r="875" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="875" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="2" t="str">
         <f>IF(B875="", "", SUBTOTAL(3, $B$2:B875) * 1)</f>
         <v/>
@@ -23841,7 +23830,7 @@
       <c r="I875" s="2"/>
       <c r="J875" s="2"/>
     </row>
-    <row r="876" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="876" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="str">
         <f>IF(B876="", "", SUBTOTAL(3, $B$2:B876) * 1)</f>
         <v/>
@@ -23856,7 +23845,7 @@
       <c r="I876" s="2"/>
       <c r="J876" s="2"/>
     </row>
-    <row r="877" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="877" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="2" t="str">
         <f>IF(B877="", "", SUBTOTAL(3, $B$2:B877) * 1)</f>
         <v/>
@@ -23871,7 +23860,7 @@
       <c r="I877" s="2"/>
       <c r="J877" s="2"/>
     </row>
-    <row r="878" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="878" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="2" t="str">
         <f>IF(B878="", "", SUBTOTAL(3, $B$2:B878) * 1)</f>
         <v/>
@@ -23886,7 +23875,7 @@
       <c r="I878" s="2"/>
       <c r="J878" s="2"/>
     </row>
-    <row r="879" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="879" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="2" t="str">
         <f>IF(B879="", "", SUBTOTAL(3, $B$2:B879) * 1)</f>
         <v/>
@@ -23901,7 +23890,7 @@
       <c r="I879" s="2"/>
       <c r="J879" s="2"/>
     </row>
-    <row r="880" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="880" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="2" t="str">
         <f>IF(B880="", "", SUBTOTAL(3, $B$2:B880) * 1)</f>
         <v/>
@@ -23916,7 +23905,7 @@
       <c r="I880" s="2"/>
       <c r="J880" s="2"/>
     </row>
-    <row r="881" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="881" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="2" t="str">
         <f>IF(B881="", "", SUBTOTAL(3, $B$2:B881) * 1)</f>
         <v/>
@@ -23931,7 +23920,7 @@
       <c r="I881" s="2"/>
       <c r="J881" s="2"/>
     </row>
-    <row r="882" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="882" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="2" t="str">
         <f>IF(B882="", "", SUBTOTAL(3, $B$2:B882) * 1)</f>
         <v/>
@@ -23946,7 +23935,7 @@
       <c r="I882" s="2"/>
       <c r="J882" s="2"/>
     </row>
-    <row r="883" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="883" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="2" t="str">
         <f>IF(B883="", "", SUBTOTAL(3, $B$2:B883) * 1)</f>
         <v/>
@@ -23961,7 +23950,7 @@
       <c r="I883" s="2"/>
       <c r="J883" s="2"/>
     </row>
-    <row r="884" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="884" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="2" t="str">
         <f>IF(B884="", "", SUBTOTAL(3, $B$2:B884) * 1)</f>
         <v/>
@@ -23976,7 +23965,7 @@
       <c r="I884" s="2"/>
       <c r="J884" s="2"/>
     </row>
-    <row r="885" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="885" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="2" t="str">
         <f>IF(B885="", "", SUBTOTAL(3, $B$2:B885) * 1)</f>
         <v/>
@@ -23991,7 +23980,7 @@
       <c r="I885" s="2"/>
       <c r="J885" s="2"/>
     </row>
-    <row r="886" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="886" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="2" t="str">
         <f>IF(B886="", "", SUBTOTAL(3, $B$2:B886) * 1)</f>
         <v/>
@@ -24006,7 +23995,7 @@
       <c r="I886" s="2"/>
       <c r="J886" s="2"/>
     </row>
-    <row r="887" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="887" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="2" t="str">
         <f>IF(B887="", "", SUBTOTAL(3, $B$2:B887) * 1)</f>
         <v/>
@@ -24021,7 +24010,7 @@
       <c r="I887" s="2"/>
       <c r="J887" s="2"/>
     </row>
-    <row r="888" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="888" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="2" t="str">
         <f>IF(B888="", "", SUBTOTAL(3, $B$2:B888) * 1)</f>
         <v/>
@@ -24036,7 +24025,7 @@
       <c r="I888" s="2"/>
       <c r="J888" s="2"/>
     </row>
-    <row r="889" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="889" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="str">
         <f>IF(B889="", "", SUBTOTAL(3, $B$2:B889) * 1)</f>
         <v/>
@@ -24051,7 +24040,7 @@
       <c r="I889" s="2"/>
       <c r="J889" s="2"/>
     </row>
-    <row r="890" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="890" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="2" t="str">
         <f>IF(B890="", "", SUBTOTAL(3, $B$2:B890) * 1)</f>
         <v/>
@@ -24066,7 +24055,7 @@
       <c r="I890" s="2"/>
       <c r="J890" s="2"/>
     </row>
-    <row r="891" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="891" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="2" t="str">
         <f>IF(B891="", "", SUBTOTAL(3, $B$2:B891) * 1)</f>
         <v/>
@@ -24081,7 +24070,7 @@
       <c r="I891" s="2"/>
       <c r="J891" s="2"/>
     </row>
-    <row r="892" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="892" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="2" t="str">
         <f>IF(B892="", "", SUBTOTAL(3, $B$2:B892) * 1)</f>
         <v/>
@@ -24096,7 +24085,7 @@
       <c r="I892" s="2"/>
       <c r="J892" s="2"/>
     </row>
-    <row r="893" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="893" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="2" t="str">
         <f>IF(B893="", "", SUBTOTAL(3, $B$2:B893) * 1)</f>
         <v/>
@@ -24111,7 +24100,7 @@
       <c r="I893" s="2"/>
       <c r="J893" s="2"/>
     </row>
-    <row r="894" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="894" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="2" t="str">
         <f>IF(B894="", "", SUBTOTAL(3, $B$2:B894) * 1)</f>
         <v/>
@@ -24126,7 +24115,7 @@
       <c r="I894" s="2"/>
       <c r="J894" s="2"/>
     </row>
-    <row r="895" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="895" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="2" t="str">
         <f>IF(B895="", "", SUBTOTAL(3, $B$2:B895) * 1)</f>
         <v/>
@@ -24141,7 +24130,7 @@
       <c r="I895" s="2"/>
       <c r="J895" s="2"/>
     </row>
-    <row r="896" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="896" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="2" t="str">
         <f>IF(B896="", "", SUBTOTAL(3, $B$2:B896) * 1)</f>
         <v/>
@@ -24156,7 +24145,7 @@
       <c r="I896" s="2"/>
       <c r="J896" s="2"/>
     </row>
-    <row r="897" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="897" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="str">
         <f>IF(B897="", "", SUBTOTAL(3, $B$2:B897) * 1)</f>
         <v/>
@@ -24171,7 +24160,7 @@
       <c r="I897" s="2"/>
       <c r="J897" s="2"/>
     </row>
-    <row r="898" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="898" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="str">
         <f>IF(B898="", "", SUBTOTAL(3, $B$2:B898) * 1)</f>
         <v/>
@@ -24186,7 +24175,7 @@
       <c r="I898" s="2"/>
       <c r="J898" s="2"/>
     </row>
-    <row r="899" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="899" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="str">
         <f>IF(B899="", "", SUBTOTAL(3, $B$2:B899) * 1)</f>
         <v/>
@@ -24201,7 +24190,7 @@
       <c r="I899" s="2"/>
       <c r="J899" s="2"/>
     </row>
-    <row r="900" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="900" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="str">
         <f>IF(B900="", "", SUBTOTAL(3, $B$2:B900) * 1)</f>
         <v/>
@@ -24216,7 +24205,7 @@
       <c r="I900" s="2"/>
       <c r="J900" s="2"/>
     </row>
-    <row r="901" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="901" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="str">
         <f>IF(B901="", "", SUBTOTAL(3, $B$2:B901) * 1)</f>
         <v/>
@@ -24231,7 +24220,7 @@
       <c r="I901" s="2"/>
       <c r="J901" s="2"/>
     </row>
-    <row r="902" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="902" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="str">
         <f>IF(B902="", "", SUBTOTAL(3, $B$2:B902) * 1)</f>
         <v/>
@@ -24246,7 +24235,7 @@
       <c r="I902" s="2"/>
       <c r="J902" s="2"/>
     </row>
-    <row r="903" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="903" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="str">
         <f>IF(B903="", "", SUBTOTAL(3, $B$2:B903) * 1)</f>
         <v/>
@@ -24261,7 +24250,7 @@
       <c r="I903" s="2"/>
       <c r="J903" s="2"/>
     </row>
-    <row r="904" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="904" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="str">
         <f>IF(B904="", "", SUBTOTAL(3, $B$2:B904) * 1)</f>
         <v/>
@@ -24276,7 +24265,7 @@
       <c r="I904" s="2"/>
       <c r="J904" s="2"/>
     </row>
-    <row r="905" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="905" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="str">
         <f>IF(B905="", "", SUBTOTAL(3, $B$2:B905) * 1)</f>
         <v/>
@@ -24291,7 +24280,7 @@
       <c r="I905" s="2"/>
       <c r="J905" s="2"/>
     </row>
-    <row r="906" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="906" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="str">
         <f>IF(B906="", "", SUBTOTAL(3, $B$2:B906) * 1)</f>
         <v/>
@@ -24306,7 +24295,7 @@
       <c r="I906" s="2"/>
       <c r="J906" s="2"/>
     </row>
-    <row r="907" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="907" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="str">
         <f>IF(B907="", "", SUBTOTAL(3, $B$2:B907) * 1)</f>
         <v/>
@@ -24321,7 +24310,7 @@
       <c r="I907" s="2"/>
       <c r="J907" s="2"/>
     </row>
-    <row r="908" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="908" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="str">
         <f>IF(B908="", "", SUBTOTAL(3, $B$2:B908) * 1)</f>
         <v/>
@@ -24336,7 +24325,7 @@
       <c r="I908" s="2"/>
       <c r="J908" s="2"/>
     </row>
-    <row r="909" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="909" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="str">
         <f>IF(B909="", "", SUBTOTAL(3, $B$2:B909) * 1)</f>
         <v/>
@@ -24351,7 +24340,7 @@
       <c r="I909" s="2"/>
       <c r="J909" s="2"/>
     </row>
-    <row r="910" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="910" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="str">
         <f>IF(B910="", "", SUBTOTAL(3, $B$2:B910) * 1)</f>
         <v/>
@@ -24366,7 +24355,7 @@
       <c r="I910" s="2"/>
       <c r="J910" s="2"/>
     </row>
-    <row r="911" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="911" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="str">
         <f>IF(B911="", "", SUBTOTAL(3, $B$2:B911) * 1)</f>
         <v/>
@@ -24381,7 +24370,7 @@
       <c r="I911" s="2"/>
       <c r="J911" s="2"/>
     </row>
-    <row r="912" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="912" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="str">
         <f>IF(B912="", "", SUBTOTAL(3, $B$2:B912) * 1)</f>
         <v/>
@@ -24396,7 +24385,7 @@
       <c r="I912" s="2"/>
       <c r="J912" s="2"/>
     </row>
-    <row r="913" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="913" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="str">
         <f>IF(B913="", "", SUBTOTAL(3, $B$2:B913) * 1)</f>
         <v/>
@@ -24411,7 +24400,7 @@
       <c r="I913" s="2"/>
       <c r="J913" s="2"/>
     </row>
-    <row r="914" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="914" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="str">
         <f>IF(B914="", "", SUBTOTAL(3, $B$2:B914) * 1)</f>
         <v/>
@@ -24426,7 +24415,7 @@
       <c r="I914" s="2"/>
       <c r="J914" s="2"/>
     </row>
-    <row r="915" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="915" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="str">
         <f>IF(B915="", "", SUBTOTAL(3, $B$2:B915) * 1)</f>
         <v/>
@@ -24441,7 +24430,7 @@
       <c r="I915" s="2"/>
       <c r="J915" s="2"/>
     </row>
-    <row r="916" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="916" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="str">
         <f>IF(B916="", "", SUBTOTAL(3, $B$2:B916) * 1)</f>
         <v/>
@@ -24456,7 +24445,7 @@
       <c r="I916" s="2"/>
       <c r="J916" s="2"/>
     </row>
-    <row r="917" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="917" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="str">
         <f>IF(B917="", "", SUBTOTAL(3, $B$2:B917) * 1)</f>
         <v/>
@@ -24471,7 +24460,7 @@
       <c r="I917" s="2"/>
       <c r="J917" s="2"/>
     </row>
-    <row r="918" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="918" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="str">
         <f>IF(B918="", "", SUBTOTAL(3, $B$2:B918) * 1)</f>
         <v/>
@@ -24486,7 +24475,7 @@
       <c r="I918" s="2"/>
       <c r="J918" s="2"/>
     </row>
-    <row r="919" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="919" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="str">
         <f>IF(B919="", "", SUBTOTAL(3, $B$2:B919) * 1)</f>
         <v/>
@@ -24501,7 +24490,7 @@
       <c r="I919" s="2"/>
       <c r="J919" s="2"/>
     </row>
-    <row r="920" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="920" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="str">
         <f>IF(B920="", "", SUBTOTAL(3, $B$2:B920) * 1)</f>
         <v/>
@@ -24516,7 +24505,7 @@
       <c r="I920" s="2"/>
       <c r="J920" s="2"/>
     </row>
-    <row r="921" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="921" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="str">
         <f>IF(B921="", "", SUBTOTAL(3, $B$2:B921) * 1)</f>
         <v/>
@@ -24531,7 +24520,7 @@
       <c r="I921" s="2"/>
       <c r="J921" s="2"/>
     </row>
-    <row r="922" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="922" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="str">
         <f>IF(B922="", "", SUBTOTAL(3, $B$2:B922) * 1)</f>
         <v/>
@@ -24546,7 +24535,7 @@
       <c r="I922" s="2"/>
       <c r="J922" s="2"/>
     </row>
-    <row r="923" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="923" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="2" t="str">
         <f>IF(B923="", "", SUBTOTAL(3, $B$2:B923) * 1)</f>
         <v/>
@@ -24561,7 +24550,7 @@
       <c r="I923" s="2"/>
       <c r="J923" s="2"/>
     </row>
-    <row r="924" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="924" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="2" t="str">
         <f>IF(B924="", "", SUBTOTAL(3, $B$2:B924) * 1)</f>
         <v/>
@@ -24576,7 +24565,7 @@
       <c r="I924" s="2"/>
       <c r="J924" s="2"/>
     </row>
-    <row r="925" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="925" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="str">
         <f>IF(B925="", "", SUBTOTAL(3, $B$2:B925) * 1)</f>
         <v/>
@@ -24591,7 +24580,7 @@
       <c r="I925" s="2"/>
       <c r="J925" s="2"/>
     </row>
-    <row r="926" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="926" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="str">
         <f>IF(B926="", "", SUBTOTAL(3, $B$2:B926) * 1)</f>
         <v/>
@@ -24606,7 +24595,7 @@
       <c r="I926" s="2"/>
       <c r="J926" s="2"/>
     </row>
-    <row r="927" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="927" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="2" t="str">
         <f>IF(B927="", "", SUBTOTAL(3, $B$2:B927) * 1)</f>
         <v/>
@@ -24621,7 +24610,7 @@
       <c r="I927" s="2"/>
       <c r="J927" s="2"/>
     </row>
-    <row r="928" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="928" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="2" t="str">
         <f>IF(B928="", "", SUBTOTAL(3, $B$2:B928) * 1)</f>
         <v/>
@@ -24636,7 +24625,7 @@
       <c r="I928" s="2"/>
       <c r="J928" s="2"/>
     </row>
-    <row r="929" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="929" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="str">
         <f>IF(B929="", "", SUBTOTAL(3, $B$2:B929) * 1)</f>
         <v/>
@@ -24651,7 +24640,7 @@
       <c r="I929" s="2"/>
       <c r="J929" s="2"/>
     </row>
-    <row r="930" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="930" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="str">
         <f>IF(B930="", "", SUBTOTAL(3, $B$2:B930) * 1)</f>
         <v/>
@@ -24666,7 +24655,7 @@
       <c r="I930" s="2"/>
       <c r="J930" s="2"/>
     </row>
-    <row r="931" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="931" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="2" t="str">
         <f>IF(B931="", "", SUBTOTAL(3, $B$2:B931) * 1)</f>
         <v/>
@@ -24681,7 +24670,7 @@
       <c r="I931" s="2"/>
       <c r="J931" s="2"/>
     </row>
-    <row r="932" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="932" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="2" t="str">
         <f>IF(B932="", "", SUBTOTAL(3, $B$2:B932) * 1)</f>
         <v/>
@@ -24696,7 +24685,7 @@
       <c r="I932" s="2"/>
       <c r="J932" s="2"/>
     </row>
-    <row r="933" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="933" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="str">
         <f>IF(B933="", "", SUBTOTAL(3, $B$2:B933) * 1)</f>
         <v/>
@@ -24711,7 +24700,7 @@
       <c r="I933" s="2"/>
       <c r="J933" s="2"/>
     </row>
-    <row r="934" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="934" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="str">
         <f>IF(B934="", "", SUBTOTAL(3, $B$2:B934) * 1)</f>
         <v/>
@@ -24726,7 +24715,7 @@
       <c r="I934" s="2"/>
       <c r="J934" s="2"/>
     </row>
-    <row r="935" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="935" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="2" t="str">
         <f>IF(B935="", "", SUBTOTAL(3, $B$2:B935) * 1)</f>
         <v/>
@@ -24741,7 +24730,7 @@
       <c r="I935" s="2"/>
       <c r="J935" s="2"/>
     </row>
-    <row r="936" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="936" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="str">
         <f>IF(B936="", "", SUBTOTAL(3, $B$2:B936) * 1)</f>
         <v/>
@@ -24756,7 +24745,7 @@
       <c r="I936" s="2"/>
       <c r="J936" s="2"/>
     </row>
-    <row r="937" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="937" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="str">
         <f>IF(B937="", "", SUBTOTAL(3, $B$2:B937) * 1)</f>
         <v/>
@@ -24771,7 +24760,7 @@
       <c r="I937" s="2"/>
       <c r="J937" s="2"/>
     </row>
-    <row r="938" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="938" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="str">
         <f>IF(B938="", "", SUBTOTAL(3, $B$2:B938) * 1)</f>
         <v/>
@@ -24786,7 +24775,7 @@
       <c r="I938" s="2"/>
       <c r="J938" s="2"/>
     </row>
-    <row r="939" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="939" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="2" t="str">
         <f>IF(B939="", "", SUBTOTAL(3, $B$2:B939) * 1)</f>
         <v/>
@@ -24801,7 +24790,7 @@
       <c r="I939" s="2"/>
       <c r="J939" s="2"/>
     </row>
-    <row r="940" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="940" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="2" t="str">
         <f>IF(B940="", "", SUBTOTAL(3, $B$2:B940) * 1)</f>
         <v/>
@@ -24816,7 +24805,7 @@
       <c r="I940" s="2"/>
       <c r="J940" s="2"/>
     </row>
-    <row r="941" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="941" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="str">
         <f>IF(B941="", "", SUBTOTAL(3, $B$2:B941) * 1)</f>
         <v/>
@@ -24831,7 +24820,7 @@
       <c r="I941" s="2"/>
       <c r="J941" s="2"/>
     </row>
-    <row r="942" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="942" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="str">
         <f>IF(B942="", "", SUBTOTAL(3, $B$2:B942) * 1)</f>
         <v/>
@@ -24846,7 +24835,7 @@
       <c r="I942" s="2"/>
       <c r="J942" s="2"/>
     </row>
-    <row r="943" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="943" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="2" t="str">
         <f>IF(B943="", "", SUBTOTAL(3, $B$2:B943) * 1)</f>
         <v/>
@@ -24861,7 +24850,7 @@
       <c r="I943" s="2"/>
       <c r="J943" s="2"/>
     </row>
-    <row r="944" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="944" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="2" t="str">
         <f>IF(B944="", "", SUBTOTAL(3, $B$2:B944) * 1)</f>
         <v/>
@@ -24876,7 +24865,7 @@
       <c r="I944" s="2"/>
       <c r="J944" s="2"/>
     </row>
-    <row r="945" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="945" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="str">
         <f>IF(B945="", "", SUBTOTAL(3, $B$2:B945) * 1)</f>
         <v/>
@@ -24891,7 +24880,7 @@
       <c r="I945" s="2"/>
       <c r="J945" s="2"/>
     </row>
-    <row r="946" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="946" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="str">
         <f>IF(B946="", "", SUBTOTAL(3, $B$2:B946) * 1)</f>
         <v/>
@@ -24906,7 +24895,7 @@
       <c r="I946" s="2"/>
       <c r="J946" s="2"/>
     </row>
-    <row r="947" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="947" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="2" t="str">
         <f>IF(B947="", "", SUBTOTAL(3, $B$2:B947) * 1)</f>
         <v/>
@@ -24921,7 +24910,7 @@
       <c r="I947" s="2"/>
       <c r="J947" s="2"/>
     </row>
-    <row r="948" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="948" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="2" t="str">
         <f>IF(B948="", "", SUBTOTAL(3, $B$2:B948) * 1)</f>
         <v/>
@@ -24936,7 +24925,7 @@
       <c r="I948" s="2"/>
       <c r="J948" s="2"/>
     </row>
-    <row r="949" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="949" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="str">
         <f>IF(B949="", "", SUBTOTAL(3, $B$2:B949) * 1)</f>
         <v/>
@@ -24951,7 +24940,7 @@
       <c r="I949" s="2"/>
       <c r="J949" s="2"/>
     </row>
-    <row r="950" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="950" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="str">
         <f>IF(B950="", "", SUBTOTAL(3, $B$2:B950) * 1)</f>
         <v/>
@@ -24966,7 +24955,7 @@
       <c r="I950" s="2"/>
       <c r="J950" s="2"/>
     </row>
-    <row r="951" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="951" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="2" t="str">
         <f>IF(B951="", "", SUBTOTAL(3, $B$2:B951) * 1)</f>
         <v/>
@@ -24981,7 +24970,7 @@
       <c r="I951" s="2"/>
       <c r="J951" s="2"/>
     </row>
-    <row r="952" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="952" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="2" t="str">
         <f>IF(B952="", "", SUBTOTAL(3, $B$2:B952) * 1)</f>
         <v/>
@@ -24996,7 +24985,7 @@
       <c r="I952" s="2"/>
       <c r="J952" s="2"/>
     </row>
-    <row r="953" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="953" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="str">
         <f>IF(B953="", "", SUBTOTAL(3, $B$2:B953) * 1)</f>
         <v/>
@@ -25011,7 +25000,7 @@
       <c r="I953" s="2"/>
       <c r="J953" s="2"/>
     </row>
-    <row r="954" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="954" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="str">
         <f>IF(B954="", "", SUBTOTAL(3, $B$2:B954) * 1)</f>
         <v/>
@@ -25026,7 +25015,7 @@
       <c r="I954" s="2"/>
       <c r="J954" s="2"/>
     </row>
-    <row r="955" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="955" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="2" t="str">
         <f>IF(B955="", "", SUBTOTAL(3, $B$2:B955) * 1)</f>
         <v/>
@@ -25041,7 +25030,7 @@
       <c r="I955" s="2"/>
       <c r="J955" s="2"/>
     </row>
-    <row r="956" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="956" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="2" t="str">
         <f>IF(B956="", "", SUBTOTAL(3, $B$2:B956) * 1)</f>
         <v/>
@@ -25056,7 +25045,7 @@
       <c r="I956" s="2"/>
       <c r="J956" s="2"/>
     </row>
-    <row r="957" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="957" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="str">
         <f>IF(B957="", "", SUBTOTAL(3, $B$2:B957) * 1)</f>
         <v/>
@@ -25071,7 +25060,7 @@
       <c r="I957" s="2"/>
       <c r="J957" s="2"/>
     </row>
-    <row r="958" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="958" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="str">
         <f>IF(B958="", "", SUBTOTAL(3, $B$2:B958) * 1)</f>
         <v/>
@@ -25086,7 +25075,7 @@
       <c r="I958" s="2"/>
       <c r="J958" s="2"/>
     </row>
-    <row r="959" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="959" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="2" t="str">
         <f>IF(B959="", "", SUBTOTAL(3, $B$2:B959) * 1)</f>
         <v/>
@@ -25101,7 +25090,7 @@
       <c r="I959" s="2"/>
       <c r="J959" s="2"/>
     </row>
-    <row r="960" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="960" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="2" t="str">
         <f>IF(B960="", "", SUBTOTAL(3, $B$2:B960) * 1)</f>
         <v/>
@@ -25116,7 +25105,7 @@
       <c r="I960" s="2"/>
       <c r="J960" s="2"/>
     </row>
-    <row r="961" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="961" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="2" t="str">
         <f>IF(B961="", "", SUBTOTAL(3, $B$2:B961) * 1)</f>
         <v/>
@@ -25131,7 +25120,7 @@
       <c r="I961" s="2"/>
       <c r="J961" s="2"/>
     </row>
-    <row r="962" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="962" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="str">
         <f>IF(B962="", "", SUBTOTAL(3, $B$2:B962) * 1)</f>
         <v/>
@@ -25146,7 +25135,7 @@
       <c r="I962" s="2"/>
       <c r="J962" s="2"/>
     </row>
-    <row r="963" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="963" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="2" t="str">
         <f>IF(B963="", "", SUBTOTAL(3, $B$2:B963) * 1)</f>
         <v/>
@@ -25161,7 +25150,7 @@
       <c r="I963" s="2"/>
       <c r="J963" s="2"/>
     </row>
-    <row r="964" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="964" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="str">
         <f>IF(B964="", "", SUBTOTAL(3, $B$2:B964) * 1)</f>
         <v/>
@@ -25176,7 +25165,7 @@
       <c r="I964" s="2"/>
       <c r="J964" s="2"/>
     </row>
-    <row r="965" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="965" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="str">
         <f>IF(B965="", "", SUBTOTAL(3, $B$2:B965) * 1)</f>
         <v/>
@@ -25191,7 +25180,7 @@
       <c r="I965" s="2"/>
       <c r="J965" s="2"/>
     </row>
-    <row r="966" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="966" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="str">
         <f>IF(B966="", "", SUBTOTAL(3, $B$2:B966) * 1)</f>
         <v/>
@@ -25206,7 +25195,7 @@
       <c r="I966" s="2"/>
       <c r="J966" s="2"/>
     </row>
-    <row r="967" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="967" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="2" t="str">
         <f>IF(B967="", "", SUBTOTAL(3, $B$2:B967) * 1)</f>
         <v/>
@@ -25221,7 +25210,7 @@
       <c r="I967" s="2"/>
       <c r="J967" s="2"/>
     </row>
-    <row r="968" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="968" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="str">
         <f>IF(B968="", "", SUBTOTAL(3, $B$2:B968) * 1)</f>
         <v/>
@@ -25236,7 +25225,7 @@
       <c r="I968" s="2"/>
       <c r="J968" s="2"/>
     </row>
-    <row r="969" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="969" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="str">
         <f>IF(B969="", "", SUBTOTAL(3, $B$2:B969) * 1)</f>
         <v/>
@@ -25251,7 +25240,7 @@
       <c r="I969" s="2"/>
       <c r="J969" s="2"/>
     </row>
-    <row r="970" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="970" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="str">
         <f>IF(B970="", "", SUBTOTAL(3, $B$2:B970) * 1)</f>
         <v/>
@@ -25266,7 +25255,7 @@
       <c r="I970" s="2"/>
       <c r="J970" s="2"/>
     </row>
-    <row r="971" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="971" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="2" t="str">
         <f>IF(B971="", "", SUBTOTAL(3, $B$2:B971) * 1)</f>
         <v/>
@@ -25281,7 +25270,7 @@
       <c r="I971" s="2"/>
       <c r="J971" s="2"/>
     </row>
-    <row r="972" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="972" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="str">
         <f>IF(B972="", "", SUBTOTAL(3, $B$2:B972) * 1)</f>
         <v/>
@@ -25296,7 +25285,7 @@
       <c r="I972" s="2"/>
       <c r="J972" s="2"/>
     </row>
-    <row r="973" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="973" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="str">
         <f>IF(B973="", "", SUBTOTAL(3, $B$2:B973) * 1)</f>
         <v/>
@@ -25311,7 +25300,7 @@
       <c r="I973" s="2"/>
       <c r="J973" s="2"/>
     </row>
-    <row r="974" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="974" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="str">
         <f>IF(B974="", "", SUBTOTAL(3, $B$2:B974) * 1)</f>
         <v/>
@@ -25326,7 +25315,7 @@
       <c r="I974" s="2"/>
       <c r="J974" s="2"/>
     </row>
-    <row r="975" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="975" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="2" t="str">
         <f>IF(B975="", "", SUBTOTAL(3, $B$2:B975) * 1)</f>
         <v/>
@@ -25341,7 +25330,7 @@
       <c r="I975" s="2"/>
       <c r="J975" s="2"/>
     </row>
-    <row r="976" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="976" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="str">
         <f>IF(B976="", "", SUBTOTAL(3, $B$2:B976) * 1)</f>
         <v/>
@@ -25356,7 +25345,7 @@
       <c r="I976" s="2"/>
       <c r="J976" s="2"/>
     </row>
-    <row r="977" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="977" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="2" t="str">
         <f>IF(B977="", "", SUBTOTAL(3, $B$2:B977) * 1)</f>
         <v/>
@@ -25371,7 +25360,7 @@
       <c r="I977" s="2"/>
       <c r="J977" s="2"/>
     </row>
-    <row r="978" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="978" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="str">
         <f>IF(B978="", "", SUBTOTAL(3, $B$2:B978) * 1)</f>
         <v/>
@@ -25386,7 +25375,7 @@
       <c r="I978" s="2"/>
       <c r="J978" s="2"/>
     </row>
-    <row r="979" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="979" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="2" t="str">
         <f>IF(B979="", "", SUBTOTAL(3, $B$2:B979) * 1)</f>
         <v/>
@@ -25401,7 +25390,7 @@
       <c r="I979" s="2"/>
       <c r="J979" s="2"/>
     </row>
-    <row r="980" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="980" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="str">
         <f>IF(B980="", "", SUBTOTAL(3, $B$2:B980) * 1)</f>
         <v/>
@@ -25416,7 +25405,7 @@
       <c r="I980" s="2"/>
       <c r="J980" s="2"/>
     </row>
-    <row r="981" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="981" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="2" t="str">
         <f>IF(B981="", "", SUBTOTAL(3, $B$2:B981) * 1)</f>
         <v/>
@@ -25431,7 +25420,7 @@
       <c r="I981" s="2"/>
       <c r="J981" s="2"/>
     </row>
-    <row r="982" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="982" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="str">
         <f>IF(B982="", "", SUBTOTAL(3, $B$2:B982) * 1)</f>
         <v/>
@@ -25446,7 +25435,7 @@
       <c r="I982" s="2"/>
       <c r="J982" s="2"/>
     </row>
-    <row r="983" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="983" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="2" t="str">
         <f>IF(B983="", "", SUBTOTAL(3, $B$2:B983) * 1)</f>
         <v/>
@@ -25461,7 +25450,7 @@
       <c r="I983" s="2"/>
       <c r="J983" s="2"/>
     </row>
-    <row r="984" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="984" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="2" t="str">
         <f>IF(B984="", "", SUBTOTAL(3, $B$2:B984) * 1)</f>
         <v/>
@@ -25476,7 +25465,7 @@
       <c r="I984" s="2"/>
       <c r="J984" s="2"/>
     </row>
-    <row r="985" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="985" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="2" t="str">
         <f>IF(B985="", "", SUBTOTAL(3, $B$2:B985) * 1)</f>
         <v/>
@@ -25491,7 +25480,7 @@
       <c r="I985" s="2"/>
       <c r="J985" s="2"/>
     </row>
-    <row r="986" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="986" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="str">
         <f>IF(B986="", "", SUBTOTAL(3, $B$2:B986) * 1)</f>
         <v/>
@@ -25506,23 +25495,8 @@
       <c r="I986" s="2"/>
       <c r="J986" s="2"/>
     </row>
-    <row r="987" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A987" s="2" t="str">
-        <f>IF(B987="", "", SUBTOTAL(3, $B$2:B987) * 1)</f>
-        <v/>
-      </c>
-      <c r="B987" s="2"/>
-      <c r="C987" s="2"/>
-      <c r="D987" s="2"/>
-      <c r="E987" s="2"/>
-      <c r="F987" s="2"/>
-      <c r="G987" s="2"/>
-      <c r="H987" s="2"/>
-      <c r="I987" s="2"/>
-      <c r="J987" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J987">
+  <autoFilter ref="A1:J986">
     <sortState ref="A2:J987">
       <sortCondition ref="J1:J987"/>
     </sortState>
@@ -25535,13 +25509,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:C13"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>918</v>
       </c>
@@ -25549,7 +25523,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>0</v>
       </c>
@@ -25557,7 +25531,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.5">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1</v>
       </c>
@@ -25565,7 +25539,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>2</v>
       </c>
@@ -25573,7 +25547,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>3</v>
       </c>
@@ -25581,7 +25555,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.5">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>4</v>
       </c>
@@ -25589,7 +25563,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>5</v>
       </c>
@@ -25597,7 +25571,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.5">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>6</v>
       </c>
@@ -25605,7 +25579,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.5">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>7</v>
       </c>
@@ -25613,7 +25587,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.5">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>8</v>
       </c>
@@ -25621,7 +25595,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.5">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>9</v>
       </c>
@@ -25629,7 +25603,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.5">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>10</v>
       </c>
